--- a/data/processed/sam_auto_dashboard_2024_refresh/sam_occ_segment_major_totals_2030.xlsx
+++ b/data/processed/sam_auto_dashboard_2024_refresh/sam_occ_segment_major_totals_2030.xlsx
@@ -5454,13 +5454,13 @@
         <v>72</v>
       </c>
       <c r="I56">
-        <v>461535.0669579583</v>
+        <v>459733.062936165</v>
       </c>
       <c r="J56">
-        <v>461535.0669579583</v>
+        <v>459733.062936165</v>
       </c>
       <c r="K56">
-        <v>724614.5651099992</v>
+        <v>723327.8401110603</v>
       </c>
       <c r="L56">
         <v>0.5</v>
@@ -5469,7 +5469,7 @@
         <v>0.5</v>
       </c>
       <c r="N56">
-        <v>0.04313066043848116</v>
+        <v>0.04312270622844992</v>
       </c>
       <c r="O56" t="s">
         <v>90</v>
@@ -5484,7 +5484,7 @@
         <v>105</v>
       </c>
       <c r="S56">
-        <v>57201.19675615015</v>
+        <v>57194.01818879037</v>
       </c>
       <c r="T56">
         <v>684650</v>
@@ -5493,7 +5493,7 @@
         <v>66882.7</v>
       </c>
       <c r="V56">
-        <v>47403.85754861776</v>
+        <v>47214.85657301771</v>
       </c>
       <c r="W56">
         <v>463381.8901036561</v>
@@ -5502,16 +5502,16 @@
         <v>730335</v>
       </c>
       <c r="Y56">
-        <v>-1846.823145697766</v>
+        <v>-3648.827167491079</v>
       </c>
       <c r="Z56">
-        <v>-5720.434890000848</v>
+        <v>-7007.159888939699</v>
       </c>
       <c r="AA56">
-        <v>-0.003985531556454746</v>
+        <v>-0.007874341327139168</v>
       </c>
       <c r="AB56">
-        <v>-0.007832617757605548</v>
+        <v>-0.009594446232125941</v>
       </c>
     </row>
     <row r="57" spans="1:28">
@@ -5540,22 +5540,22 @@
         <v>73</v>
       </c>
       <c r="I57">
-        <v>28824.81716001232</v>
+        <v>28704.37777639307</v>
       </c>
       <c r="J57">
-        <v>28824.81716001232</v>
+        <v>28704.37777639307</v>
       </c>
       <c r="K57">
-        <v>53960.15737008391</v>
+        <v>53954.37487134382</v>
       </c>
       <c r="L57">
-        <v>0.03122711492975029</v>
+        <v>0.03121852667400902</v>
       </c>
       <c r="M57">
         <v>0.03082867419651592</v>
       </c>
       <c r="N57">
-        <v>0.01187205658429399</v>
+        <v>0.01187618438600924</v>
       </c>
       <c r="O57" t="s">
         <v>91</v>
@@ -5570,7 +5570,7 @@
         <v>106</v>
       </c>
       <c r="S57">
-        <v>125277.9333450583</v>
+        <v>125276.3764339265</v>
       </c>
       <c r="T57">
         <v>48080</v>
@@ -5579,7 +5579,7 @@
         <v>7123.1</v>
       </c>
       <c r="V57">
-        <v>2223.237888226506</v>
+        <v>2213.940097780086</v>
       </c>
       <c r="W57">
         <v>28570.89863714271</v>
@@ -5588,16 +5588,16 @@
         <v>53626.36264113485</v>
       </c>
       <c r="Y57">
-        <v>253.9185228696115</v>
+        <v>133.4791392503612</v>
       </c>
       <c r="Z57">
-        <v>333.7947289490548</v>
+        <v>328.0122302089658</v>
       </c>
       <c r="AA57">
-        <v>0.008887313139654367</v>
+        <v>0.004671856525955952</v>
       </c>
       <c r="AB57">
-        <v>0.006224452163253991</v>
+        <v>0.006116622758921922</v>
       </c>
     </row>
     <row r="58" spans="1:28">
@@ -5626,22 +5626,22 @@
         <v>74</v>
       </c>
       <c r="I58">
-        <v>18175.46486185895</v>
+        <v>18090.36577595027</v>
       </c>
       <c r="J58">
-        <v>18175.46486185895</v>
+        <v>18090.36577595027</v>
       </c>
       <c r="K58">
-        <v>37855.81824280611</v>
+        <v>37874.44270424985</v>
       </c>
       <c r="L58">
-        <v>0.01969023175384697</v>
+        <v>0.01967485834106972</v>
       </c>
       <c r="M58">
         <v>0.01920477569343602</v>
       </c>
       <c r="N58">
-        <v>0.005000762758333851</v>
+        <v>0.004996416054900536</v>
       </c>
       <c r="O58" t="s">
         <v>91</v>
@@ -5656,7 +5656,7 @@
         <v>106</v>
       </c>
       <c r="S58">
-        <v>81344.71288079067</v>
+        <v>81344.93182546212</v>
       </c>
       <c r="T58">
         <v>31580</v>
@@ -5665,7 +5665,7 @@
         <v>6576.299999999999</v>
       </c>
       <c r="V58">
-        <v>1572.233817702655</v>
+        <v>1564.743595894107</v>
       </c>
       <c r="W58">
         <v>17798.29051968228</v>
@@ -5674,16 +5674,16 @@
         <v>37293.95644836752</v>
       </c>
       <c r="Y58">
-        <v>377.1743421766769</v>
+        <v>292.0752562679991</v>
       </c>
       <c r="Z58">
-        <v>561.8617944385915</v>
+        <v>580.4862558823297</v>
       </c>
       <c r="AA58">
-        <v>0.02119160498923073</v>
+        <v>0.01641029827808502</v>
       </c>
       <c r="AB58">
-        <v>0.01506575992323244</v>
+        <v>0.01556515615837106</v>
       </c>
     </row>
     <row r="59" spans="1:28">
@@ -5712,22 +5712,22 @@
         <v>75</v>
       </c>
       <c r="I59">
-        <v>5137.118867048732</v>
+        <v>5116.892572927963</v>
       </c>
       <c r="J59">
-        <v>5137.118867048732</v>
+        <v>5116.892572927963</v>
       </c>
       <c r="K59">
-        <v>19005.1830941334</v>
+        <v>19124.47088101878</v>
       </c>
       <c r="L59">
-        <v>0.005565253037984952</v>
+        <v>0.005565069151485472</v>
       </c>
       <c r="M59">
         <v>0.005377478458063374</v>
       </c>
       <c r="N59">
-        <v>0.003452152253655146</v>
+        <v>0.003451347793623835</v>
       </c>
       <c r="O59" t="s">
         <v>91</v>
@@ -5742,7 +5742,7 @@
         <v>106</v>
       </c>
       <c r="S59">
-        <v>110658.7087855704</v>
+        <v>110673.6762023036</v>
       </c>
       <c r="T59">
         <v>12510</v>
@@ -5751,7 +5751,7 @@
         <v>2050</v>
       </c>
       <c r="V59">
-        <v>313.3608585354988</v>
+        <v>312.1375195941749</v>
       </c>
       <c r="W59">
         <v>4983.652263778201</v>
@@ -5760,16 +5760,16 @@
         <v>18078.37726367835</v>
       </c>
       <c r="Y59">
-        <v>153.4666032705309</v>
+        <v>133.2403091497617</v>
       </c>
       <c r="Z59">
-        <v>926.8058304550468</v>
+        <v>1046.093617340426</v>
       </c>
       <c r="AA59">
-        <v>0.03079400310209143</v>
+        <v>0.02673547472767487</v>
       </c>
       <c r="AB59">
-        <v>0.05126598570974133</v>
+        <v>0.05786435375713476</v>
       </c>
     </row>
     <row r="60" spans="1:28">
@@ -5798,22 +5798,22 @@
         <v>76</v>
       </c>
       <c r="I60">
-        <v>24506.0786657742</v>
+        <v>24406.19929497023</v>
       </c>
       <c r="J60">
-        <v>24506.0786657742</v>
+        <v>24406.19929497023</v>
       </c>
       <c r="K60">
-        <v>85873.44575599946</v>
+        <v>86305.51859259649</v>
       </c>
       <c r="L60">
-        <v>0.0265484471497444</v>
+        <v>0.02654388085457221</v>
       </c>
       <c r="M60">
         <v>0.02533271212906269</v>
       </c>
       <c r="N60">
-        <v>0.01463943586978565</v>
+        <v>0.01462729477816914</v>
       </c>
       <c r="O60" t="s">
         <v>91</v>
@@ -5828,7 +5828,7 @@
         <v>106</v>
       </c>
       <c r="S60">
-        <v>97064.54581219474</v>
+        <v>97064.00208805513</v>
       </c>
       <c r="T60">
         <v>80230</v>
@@ -5837,7 +5837,7 @@
         <v>805.7</v>
       </c>
       <c r="V60">
-        <v>1636.07061810162</v>
+        <v>1629.459724721772</v>
       </c>
       <c r="W60">
         <v>23477.44005563377</v>
@@ -5846,16 +5846,16 @@
         <v>83612.77637990972</v>
       </c>
       <c r="Y60">
-        <v>1028.638610140428</v>
+        <v>928.7592393364539</v>
       </c>
       <c r="Z60">
-        <v>2260.669376089747</v>
+        <v>2692.742212686775</v>
       </c>
       <c r="AA60">
-        <v>0.04381391700725864</v>
+        <v>0.03955964692639408</v>
       </c>
       <c r="AB60">
-        <v>0.02703736766039186</v>
+        <v>0.03220491328325011</v>
       </c>
     </row>
     <row r="61" spans="1:28">
@@ -5884,22 +5884,22 @@
         <v>77</v>
       </c>
       <c r="I61">
-        <v>963.1386334114479</v>
+        <v>956.7866736459698</v>
       </c>
       <c r="J61">
-        <v>963.1386334114479</v>
+        <v>956.7866736459698</v>
       </c>
       <c r="K61">
-        <v>7548.350445242085</v>
+        <v>7600.841454794158</v>
       </c>
       <c r="L61">
-        <v>0.001043407860381691</v>
+        <v>0.00104058936672434</v>
       </c>
       <c r="M61">
         <v>0.00105205063404905</v>
       </c>
       <c r="N61">
-        <v>0.0008285984335017111</v>
+        <v>0.0008267470008991314</v>
       </c>
       <c r="O61" t="s">
         <v>91</v>
@@ -5914,7 +5914,7 @@
         <v>106</v>
       </c>
       <c r="S61">
-        <v>79862.3759431635</v>
+        <v>79877.2592654896</v>
       </c>
       <c r="T61">
         <v>6660</v>
@@ -5923,7 +5923,7 @@
         <v>254.1</v>
       </c>
       <c r="V61">
-        <v>97.04819704398427</v>
+        <v>96.41471332167198</v>
       </c>
       <c r="W61">
         <v>975.0024225807971</v>
@@ -5932,16 +5932,16 @@
         <v>7386.304347727839</v>
       </c>
       <c r="Y61">
-        <v>-11.86378916934916</v>
+        <v>-18.21574893482727</v>
       </c>
       <c r="Z61">
-        <v>162.046097514246</v>
+        <v>214.5371070663195</v>
       </c>
       <c r="AA61">
-        <v>-0.01216795865793454</v>
+        <v>-0.01868277299928223</v>
       </c>
       <c r="AB61">
-        <v>0.02193872468362264</v>
+        <v>0.0290452568654736</v>
       </c>
     </row>
     <row r="62" spans="1:28">
@@ -5970,22 +5970,22 @@
         <v>78</v>
       </c>
       <c r="I62">
-        <v>172.3984966393849</v>
+        <v>171.9582404245402</v>
       </c>
       <c r="J62">
-        <v>172.3984966393849</v>
+        <v>171.9582404245402</v>
       </c>
       <c r="K62">
-        <v>429.4471242358889</v>
+        <v>432.1289988729172</v>
       </c>
       <c r="L62">
-        <v>0.0001867664116788431</v>
+        <v>0.0001870196580231787</v>
       </c>
       <c r="M62">
         <v>0.0001785507084603568</v>
       </c>
       <c r="N62">
-        <v>0.0001931991701841817</v>
+        <v>0.0001935022450438665</v>
       </c>
       <c r="O62" t="s">
         <v>92</v>
@@ -6000,7 +6000,7 @@
         <v>107</v>
       </c>
       <c r="S62">
-        <v>106018.9733321513</v>
+        <v>105952.7076756201</v>
       </c>
       <c r="T62">
         <v>270</v>
@@ -6009,7 +6009,7 @@
         <v>143.2</v>
       </c>
       <c r="V62">
-        <v>11.48880017961752</v>
+        <v>11.46732037859452</v>
       </c>
       <c r="W62">
         <v>165.474329531414</v>
@@ -6018,16 +6018,16 @@
         <v>417.1842675378095</v>
       </c>
       <c r="Y62">
-        <v>6.924167107970931</v>
+        <v>6.483910893126222</v>
       </c>
       <c r="Z62">
-        <v>12.26285669807936</v>
+        <v>14.94473133510775</v>
       </c>
       <c r="AA62">
-        <v>0.04184435814049595</v>
+        <v>0.03918378706526382</v>
       </c>
       <c r="AB62">
-        <v>0.02939434118753765</v>
+        <v>0.03582285454653034</v>
       </c>
     </row>
     <row r="63" spans="1:28">
@@ -6056,22 +6056,22 @@
         <v>79</v>
       </c>
       <c r="I63">
-        <v>473.3892256346425</v>
+        <v>472.0024419962944</v>
       </c>
       <c r="J63">
-        <v>473.3892256346425</v>
+        <v>472.0024419962944</v>
       </c>
       <c r="K63">
-        <v>3911.445878106546</v>
+        <v>3947.452730875506</v>
       </c>
       <c r="L63">
-        <v>0.0005128420996857471</v>
+        <v>0.0005133440250977043</v>
       </c>
       <c r="M63">
         <v>0.000486878297284555</v>
       </c>
       <c r="N63">
-        <v>0.0003648414926674761</v>
+        <v>0.0003647466537310888</v>
       </c>
       <c r="O63" t="s">
         <v>91</v>
@@ -6086,7 +6086,7 @@
         <v>106</v>
       </c>
       <c r="S63">
-        <v>71168.02718380513</v>
+        <v>71151.52754086975</v>
       </c>
       <c r="T63">
         <v>4460</v>
@@ -6095,7 +6095,7 @@
         <v>188.8</v>
       </c>
       <c r="V63">
-        <v>37.91300291995386</v>
+        <v>37.80675644419833</v>
       </c>
       <c r="W63">
         <v>451.2211712923338</v>
@@ -6104,16 +6104,16 @@
         <v>3836.447313458106</v>
       </c>
       <c r="Y63">
-        <v>22.16805434230866</v>
+        <v>20.78127070396056</v>
       </c>
       <c r="Z63">
-        <v>74.99856464844015</v>
+        <v>111.0054174174002</v>
       </c>
       <c r="AA63">
-        <v>0.04912902087199847</v>
+        <v>0.0460556197849523</v>
       </c>
       <c r="AB63">
-        <v>0.01954896249593945</v>
+        <v>0.02893443030691378</v>
       </c>
     </row>
     <row r="64" spans="1:28">
@@ -6142,22 +6142,22 @@
         <v>80</v>
       </c>
       <c r="I64">
-        <v>104.2592442546106</v>
+        <v>104.1359605011699</v>
       </c>
       <c r="J64">
-        <v>104.2592442546106</v>
+        <v>104.1359605011699</v>
       </c>
       <c r="K64">
-        <v>992.879661219897</v>
+        <v>1003.549624041445</v>
       </c>
       <c r="L64">
-        <v>0.0001129483453357052</v>
+        <v>0.0001132569842117592</v>
       </c>
       <c r="M64">
         <v>0.0001043188817419327</v>
       </c>
       <c r="N64">
-        <v>0.000210093727818095</v>
+        <v>0.0002101774943030526</v>
       </c>
       <c r="O64" t="s">
         <v>91</v>
@@ -6172,7 +6172,7 @@
         <v>106</v>
       </c>
       <c r="S64">
-        <v>91572.77887035288</v>
+        <v>91545.61334872335</v>
       </c>
       <c r="T64">
         <v>430</v>
@@ -6181,7 +6181,7 @@
         <v>415</v>
       </c>
       <c r="V64">
-        <v>5.738705453052486</v>
+        <v>5.732771526121634</v>
       </c>
       <c r="W64">
         <v>96.67896119015307</v>
@@ -6190,16 +6190,16 @@
         <v>958.301441289023</v>
       </c>
       <c r="Y64">
-        <v>7.580283064457547</v>
+        <v>7.456999311016816</v>
       </c>
       <c r="Z64">
-        <v>34.57821993087396</v>
+        <v>45.24818275242239</v>
       </c>
       <c r="AA64">
-        <v>0.07840674921556369</v>
+        <v>0.07713156222634635</v>
       </c>
       <c r="AB64">
-        <v>0.03608282158520222</v>
+        <v>0.04721706636646451</v>
       </c>
     </row>
     <row r="65" spans="1:28">
@@ -6228,22 +6228,22 @@
         <v>81</v>
       </c>
       <c r="I65">
-        <v>140.1035782526109</v>
+        <v>139.5474012291971</v>
       </c>
       <c r="J65">
-        <v>140.1035782526109</v>
+        <v>139.5474012291971</v>
       </c>
       <c r="K65">
-        <v>250.5292536397545</v>
+        <v>249.9259256781486</v>
       </c>
       <c r="L65">
-        <v>0.0001517799927707043</v>
+        <v>0.0001517700296971827</v>
       </c>
       <c r="M65">
         <v>0.0001651520694948195</v>
       </c>
       <c r="N65">
-        <v>0.0002866373143206004</v>
+        <v>0.0002863227894435403</v>
       </c>
       <c r="O65" t="s">
         <v>90</v>
@@ -6267,7 +6267,7 @@
         <v>483</v>
       </c>
       <c r="V65">
-        <v>17.83700466445545</v>
+        <v>17.7661961077817</v>
       </c>
       <c r="W65">
         <v>153.0569562340796</v>
@@ -6276,16 +6276,16 @@
         <v>268.389322677164</v>
       </c>
       <c r="Y65">
-        <v>-12.95337798146872</v>
+        <v>-13.50955500488251</v>
       </c>
       <c r="Z65">
-        <v>-17.86006903740952</v>
+        <v>-18.46339699901543</v>
       </c>
       <c r="AA65">
-        <v>-0.08463109616304081</v>
+        <v>-0.08826488738101849</v>
       </c>
       <c r="AB65">
-        <v>-0.06654537840498505</v>
+        <v>-0.06879333654127662</v>
       </c>
     </row>
     <row r="66" spans="1:28">
@@ -6314,22 +6314,22 @@
         <v>82</v>
       </c>
       <c r="I66">
-        <v>1737.170360124582</v>
+        <v>1723.521302541643</v>
       </c>
       <c r="J66">
-        <v>1737.170360124582</v>
+        <v>1723.521302541643</v>
       </c>
       <c r="K66">
-        <v>1737.170360124582</v>
+        <v>1723.521302541643</v>
       </c>
       <c r="L66">
-        <v>0.00188194839838987</v>
+        <v>0.001874480477360139</v>
       </c>
       <c r="M66">
         <v>0.00200080525753374</v>
       </c>
       <c r="N66">
-        <v>0.002307127996165559</v>
+        <v>0.002299649002665216</v>
       </c>
       <c r="O66" t="s">
         <v>93</v>
@@ -6353,7 +6353,7 @@
         <v>1236.2</v>
       </c>
       <c r="V66">
-        <v>374.9632118539056</v>
+        <v>372.0171021414935</v>
       </c>
       <c r="W66">
         <v>1854.273843930634</v>
@@ -6362,16 +6362,16 @@
         <v>1854.273843930634</v>
       </c>
       <c r="Y66">
-        <v>-117.1034838060516</v>
+        <v>-130.7525413889903</v>
       </c>
       <c r="Z66">
-        <v>-117.1034838060516</v>
+        <v>-130.7525413889903</v>
       </c>
       <c r="AA66">
-        <v>-0.06315328460753088</v>
+        <v>-0.07051414860699592</v>
       </c>
       <c r="AB66">
-        <v>-0.06315328460753088</v>
+        <v>-0.07051414860699592</v>
       </c>
     </row>
     <row r="67" spans="1:28">
@@ -6400,22 +6400,22 @@
         <v>83</v>
       </c>
       <c r="I67">
-        <v>1387.357522182019</v>
+        <v>1382.862445693955</v>
       </c>
       <c r="J67">
-        <v>1387.357522182019</v>
+        <v>1382.862445693955</v>
       </c>
       <c r="K67">
-        <v>2452.3203507564</v>
+        <v>2446.354857603264</v>
       </c>
       <c r="L67">
-        <v>0.001502981703347359</v>
+        <v>0.001503984112935084</v>
       </c>
       <c r="M67">
         <v>0.001511853167058014</v>
       </c>
       <c r="N67">
-        <v>0.002730154831813322</v>
+        <v>0.002732825349053334</v>
       </c>
       <c r="O67" t="s">
         <v>93</v>
@@ -6430,7 +6430,7 @@
         <v>105</v>
       </c>
       <c r="S67">
-        <v>36031.08572281904</v>
+        <v>36030.64853833969</v>
       </c>
       <c r="T67">
         <v>2490</v>
@@ -6439,7 +6439,7 @@
         <v>3829.4</v>
       </c>
       <c r="V67">
-        <v>196.4257762756681</v>
+        <v>195.7926526284282</v>
       </c>
       <c r="W67">
         <v>1401.130756221082</v>
@@ -6448,16 +6448,16 @@
         <v>2483.81026903287</v>
       </c>
       <c r="Y67">
-        <v>-13.7732340390628</v>
+        <v>-18.2683105271276</v>
       </c>
       <c r="Z67">
-        <v>-31.48991827646978</v>
+        <v>-37.45541142960519</v>
       </c>
       <c r="AA67">
-        <v>-0.009830084721150423</v>
+        <v>-0.01303826245053539</v>
       </c>
       <c r="AB67">
-        <v>-0.01267806912189437</v>
+        <v>-0.01507981986248464</v>
       </c>
     </row>
     <row r="68" spans="1:28">
@@ -6486,22 +6486,22 @@
         <v>84</v>
       </c>
       <c r="I68">
-        <v>58728.13021856629</v>
+        <v>58450.34932923196</v>
       </c>
       <c r="J68">
-        <v>58728.13021856629</v>
+        <v>58450.34932923196</v>
       </c>
       <c r="K68">
-        <v>66204.54937505546</v>
+        <v>65948.95114562921</v>
       </c>
       <c r="L68">
-        <v>0.06362260900959438</v>
+        <v>0.06356987787209457</v>
       </c>
       <c r="M68">
         <v>0.06390631301173946</v>
       </c>
       <c r="N68">
-        <v>0.02417885121935697</v>
+        <v>0.02415651651623467</v>
       </c>
       <c r="O68" t="s">
         <v>93</v>
@@ -6516,7 +6516,7 @@
         <v>105</v>
       </c>
       <c r="S68">
-        <v>43159.67356239633</v>
+        <v>43148.82983708271</v>
       </c>
       <c r="T68">
         <v>62520</v>
@@ -6525,7 +6525,7 @@
         <v>6089.999999999999</v>
       </c>
       <c r="V68">
-        <v>7676.461597118698</v>
+        <v>7638.851776552168</v>
       </c>
       <c r="W68">
         <v>59226.05622587141</v>
@@ -6534,16 +6534,16 @@
         <v>66907.28854568397</v>
       </c>
       <c r="Y68">
-        <v>-497.9260073051119</v>
+        <v>-775.7068966394436</v>
       </c>
       <c r="Z68">
-        <v>-702.7391706285125</v>
+        <v>-958.3374000547628</v>
       </c>
       <c r="AA68">
-        <v>-0.00840721194411735</v>
+        <v>-0.01309739236529809</v>
       </c>
       <c r="AB68">
-        <v>-0.01050317814252308</v>
+        <v>-0.01432336328201994</v>
       </c>
     </row>
     <row r="69" spans="1:28">
@@ -6572,22 +6572,22 @@
         <v>85</v>
       </c>
       <c r="I69">
-        <v>30639.4213353204</v>
+        <v>30521.10920738259</v>
       </c>
       <c r="J69">
-        <v>30639.4213353204</v>
+        <v>30521.10920738259</v>
       </c>
       <c r="K69">
-        <v>47918.69619275116</v>
+        <v>47808.57192643109</v>
       </c>
       <c r="L69">
-        <v>0.03319295057824</v>
+        <v>0.03319438133561052</v>
       </c>
       <c r="M69">
         <v>0.03500147671330239</v>
       </c>
       <c r="N69">
-        <v>0.008759886628372564</v>
+        <v>0.008765885810296404</v>
       </c>
       <c r="O69" t="s">
         <v>90</v>
@@ -6602,7 +6602,7 @@
         <v>105</v>
       </c>
       <c r="S69">
-        <v>47236.35292046557</v>
+        <v>47233.61960443966</v>
       </c>
       <c r="T69">
         <v>51090</v>
@@ -6611,7 +6611,7 @@
         <v>13969.9</v>
       </c>
       <c r="V69">
-        <v>3141.512592266485</v>
+        <v>3129.92884553282</v>
       </c>
       <c r="W69">
         <v>32438.10087165833</v>
@@ -6620,16 +6620,16 @@
         <v>51010.14449329415</v>
       </c>
       <c r="Y69">
-        <v>-1798.679536337935</v>
+        <v>-1916.991664275745</v>
       </c>
       <c r="Z69">
-        <v>-3091.448300542994</v>
+        <v>-3201.572566863062</v>
       </c>
       <c r="AA69">
-        <v>-0.05544959439686153</v>
+        <v>-0.05909691420778121</v>
       </c>
       <c r="AB69">
-        <v>-0.06060457838831252</v>
+        <v>-0.06276344830358095</v>
       </c>
     </row>
     <row r="70" spans="1:28">
@@ -6658,22 +6658,22 @@
         <v>86</v>
       </c>
       <c r="I70">
-        <v>5621.760180675571</v>
+        <v>5604.183968850458</v>
       </c>
       <c r="J70">
-        <v>5621.760180675571</v>
+        <v>5604.183968850458</v>
       </c>
       <c r="K70">
-        <v>7811.604261526092</v>
+        <v>7806.925564215795</v>
       </c>
       <c r="L70">
-        <v>0.006090284989317683</v>
+        <v>0.006095041254003316</v>
       </c>
       <c r="M70">
         <v>0.005791781839163417</v>
       </c>
       <c r="N70">
-        <v>0.006606907231991133</v>
+        <v>0.006606348219938848</v>
       </c>
       <c r="O70" t="s">
         <v>90</v>
@@ -6688,7 +6688,7 @@
         <v>105</v>
       </c>
       <c r="S70">
-        <v>62060.1711375531</v>
+        <v>62062.27091366635</v>
       </c>
       <c r="T70">
         <v>6440</v>
@@ -6697,7 +6697,7 @@
         <v>1579.5</v>
       </c>
       <c r="V70">
-        <v>514.0350297663714</v>
+        <v>512.4474353836032</v>
       </c>
       <c r="W70">
         <v>5367.613631399147</v>
@@ -6706,16 +6706,16 @@
         <v>7588.884664167177</v>
       </c>
       <c r="Y70">
-        <v>254.1465492764237</v>
+        <v>236.5703374513105</v>
       </c>
       <c r="Z70">
-        <v>222.7195973589151</v>
+        <v>218.0409000486179</v>
       </c>
       <c r="AA70">
-        <v>0.04734814514027841</v>
+        <v>0.04407365240810839</v>
       </c>
       <c r="AB70">
-        <v>0.02934813312034396</v>
+        <v>0.0287316133658155</v>
       </c>
     </row>
     <row r="71" spans="1:28">
@@ -6744,22 +6744,22 @@
         <v>87</v>
       </c>
       <c r="I71">
-        <v>54256.13988772201</v>
+        <v>54205.75874131289</v>
       </c>
       <c r="J71">
-        <v>54256.13988772201</v>
+        <v>54205.75874131289</v>
       </c>
       <c r="K71">
-        <v>62207.24536008186</v>
+        <v>62126.01778871931</v>
       </c>
       <c r="L71">
-        <v>0.05877791718550419</v>
+        <v>0.05895351358364178</v>
       </c>
       <c r="M71">
         <v>0.05611143442290052</v>
       </c>
       <c r="N71">
-        <v>0.02140187914884786</v>
+        <v>0.02151454339303531</v>
       </c>
       <c r="O71" t="s">
         <v>90</v>
@@ -6774,7 +6774,7 @@
         <v>105</v>
       </c>
       <c r="S71">
-        <v>55569.94271741188</v>
+        <v>55558.41923716066</v>
       </c>
       <c r="T71">
         <v>55630</v>
@@ -6783,7 +6783,7 @@
         <v>3288.9</v>
       </c>
       <c r="V71">
-        <v>4919.132553061549</v>
+        <v>4913.062044694335</v>
       </c>
       <c r="W71">
         <v>52002.04507862199</v>
@@ -6792,16 +6792,16 @@
         <v>59811.18550645393</v>
       </c>
       <c r="Y71">
-        <v>2254.094809100025</v>
+        <v>2203.713662690905</v>
       </c>
       <c r="Z71">
-        <v>2396.059853627929</v>
+        <v>2314.832282265372</v>
       </c>
       <c r="AA71">
-        <v>0.04334627235702086</v>
+        <v>0.04237744225941703</v>
       </c>
       <c r="AB71">
-        <v>0.04006039728755053</v>
+        <v>0.03870233072065742</v>
       </c>
     </row>
     <row r="72" spans="1:28">
@@ -6830,22 +6830,22 @@
         <v>88</v>
       </c>
       <c r="I72">
-        <v>152885.249481067</v>
+        <v>152310.0855134911</v>
       </c>
       <c r="J72">
-        <v>152885.249481067</v>
+        <v>152310.0855134911</v>
       </c>
       <c r="K72">
-        <v>239914.1514146388</v>
+        <v>238899.017738474</v>
       </c>
       <c r="L72">
-        <v>0.1656269051111922</v>
+        <v>0.1656505674627101</v>
       </c>
       <c r="M72">
         <v>0.1665861457462193</v>
       </c>
       <c r="N72">
-        <v>0.08961281632856118</v>
+        <v>0.08959420938209497</v>
       </c>
       <c r="O72" t="s">
         <v>90</v>
@@ -6860,7 +6860,7 @@
         <v>105</v>
       </c>
       <c r="S72">
-        <v>46581.63818985097</v>
+        <v>46578.97853695209</v>
       </c>
       <c r="T72">
         <v>235530</v>
@@ -6869,7 +6869,7 @@
         <v>5083.8</v>
       </c>
       <c r="V72">
-        <v>15563.56680388635</v>
+        <v>15505.39105062694</v>
       </c>
       <c r="W72">
         <v>154386.0061619324</v>
@@ -6878,16 +6878,16 @@
         <v>246100.1950558998</v>
       </c>
       <c r="Y72">
-        <v>-1500.756680865394</v>
+        <v>-2075.920648441301</v>
       </c>
       <c r="Z72">
-        <v>-6186.043641260971</v>
+        <v>-7201.177317425812</v>
       </c>
       <c r="AA72">
-        <v>-0.009720807721985371</v>
+        <v>-0.01344630060747804</v>
       </c>
       <c r="AB72">
-        <v>-0.02513628093572156</v>
+        <v>-0.02926116054394073</v>
       </c>
     </row>
     <row r="73" spans="1:28">
@@ -6916,22 +6916,22 @@
         <v>89</v>
       </c>
       <c r="I73">
-        <v>77783.06923941353</v>
+        <v>77372.9262896217</v>
       </c>
       <c r="J73">
-        <v>77783.06923941353</v>
+        <v>77372.9262896217</v>
       </c>
       <c r="K73">
-        <v>86541.57096959763</v>
+        <v>86075.77400397496</v>
       </c>
       <c r="L73">
-        <v>0.08426561144323499</v>
+        <v>0.08414983881675386</v>
       </c>
       <c r="M73">
         <v>0.08635959877397439</v>
       </c>
       <c r="N73">
-        <v>0.03108831988610242</v>
+        <v>0.03102234474530562</v>
       </c>
       <c r="O73" t="s">
         <v>93</v>
@@ -6946,7 +6946,7 @@
         <v>105</v>
       </c>
       <c r="S73">
-        <v>46885.67356728251</v>
+        <v>46860.60177846336</v>
       </c>
       <c r="T73">
         <v>84500</v>
@@ -6955,7 +6955,7 @@
         <v>13765.8</v>
       </c>
       <c r="V73">
-        <v>9102.831091561393</v>
+        <v>9057.896969689415</v>
       </c>
       <c r="W73">
         <v>80034.94821695528</v>
@@ -6964,16 +6964,16 @@
         <v>89101.11819575714</v>
       </c>
       <c r="Y73">
-        <v>-2251.878977541754</v>
+        <v>-2662.021927333582</v>
       </c>
       <c r="Z73">
-        <v>-2559.547226159513</v>
+        <v>-3025.344191782176</v>
       </c>
       <c r="AA73">
-        <v>-0.02813619584581297</v>
+        <v>-0.03326074404543236</v>
       </c>
       <c r="AB73">
-        <v>-0.02872631991594237</v>
+        <v>-0.03395405414705827</v>
       </c>
     </row>
     <row r="74" spans="1:28">
@@ -12420,13 +12420,13 @@
         <v>72</v>
       </c>
       <c r="I137">
-        <v>19921.05400685776</v>
+        <v>19649.73515071348</v>
       </c>
       <c r="J137">
-        <v>19921.05400685776</v>
+        <v>19649.73515071348</v>
       </c>
       <c r="K137">
-        <v>68658.75666000212</v>
+        <v>67725.60786988679</v>
       </c>
       <c r="L137">
         <v>0.5</v>
@@ -12459,7 +12459,7 @@
         <v>7143.3</v>
       </c>
       <c r="V137">
-        <v>1938.977691942693</v>
+        <v>1912.569389988084</v>
       </c>
       <c r="W137">
         <v>21247.66878566509</v>
@@ -12468,16 +12468,16 @@
         <v>72604</v>
       </c>
       <c r="Y137">
-        <v>-1326.614778807336</v>
+        <v>-1597.933634951612</v>
       </c>
       <c r="Z137">
-        <v>-3945.243339997876</v>
+        <v>-4878.392130113207</v>
       </c>
       <c r="AA137">
-        <v>-0.06243578023497556</v>
+        <v>-0.07520512725752158</v>
       </c>
       <c r="AB137">
-        <v>-0.05433920087044621</v>
+        <v>-0.06719178185930812</v>
       </c>
     </row>
     <row r="138" spans="1:28">
@@ -12506,16 +12506,16 @@
         <v>73</v>
       </c>
       <c r="I138">
-        <v>1262.805758244258</v>
+        <v>1245.606717784788</v>
       </c>
       <c r="J138">
-        <v>1262.805758244258</v>
+        <v>1245.606717784788</v>
       </c>
       <c r="K138">
-        <v>4352.313548986657</v>
+        <v>4293.160771977437</v>
       </c>
       <c r="L138">
-        <v>0.03169525462381511</v>
+        <v>0.03169525462381512</v>
       </c>
       <c r="M138">
         <v>0.0311411453253447</v>
@@ -12536,7 +12536,7 @@
         <v>106</v>
       </c>
       <c r="S138">
-        <v>129561.7282379142</v>
+        <v>129561.7282379141</v>
       </c>
       <c r="T138">
         <v>4610</v>
@@ -12545,7 +12545,7 @@
         <v>770.4</v>
       </c>
       <c r="V138">
-        <v>95.29645714974556</v>
+        <v>93.99854762449806</v>
       </c>
       <c r="W138">
         <v>1323.353482958374</v>
@@ -12554,16 +12554,16 @@
         <v>4521.943430402654</v>
       </c>
       <c r="Y138">
-        <v>-60.54772471411616</v>
+        <v>-77.74676517358603</v>
       </c>
       <c r="Z138">
-        <v>-169.6298814159973</v>
+        <v>-228.782658425218</v>
       </c>
       <c r="AA138">
-        <v>-0.04575325148860525</v>
+        <v>-0.05874980961230564</v>
       </c>
       <c r="AB138">
-        <v>-0.03751260581357884</v>
+        <v>-0.05059387892538189</v>
       </c>
     </row>
     <row r="139" spans="1:28">
@@ -12592,13 +12592,13 @@
         <v>74</v>
       </c>
       <c r="I139">
-        <v>857.9468768081505</v>
+        <v>846.2618944187643</v>
       </c>
       <c r="J139">
-        <v>857.9468768081505</v>
+        <v>846.2618944187643</v>
       </c>
       <c r="K139">
-        <v>2956.950260849731</v>
+        <v>2916.762021321784</v>
       </c>
       <c r="L139">
         <v>0.02153367177541924</v>
@@ -12622,7 +12622,7 @@
         <v>106</v>
       </c>
       <c r="S139">
-        <v>80296.92200650598</v>
+        <v>80296.92200650599</v>
       </c>
       <c r="T139">
         <v>3200</v>
@@ -12631,7 +12631,7 @@
         <v>742.2</v>
       </c>
       <c r="V139">
-        <v>73.57100914645045</v>
+        <v>72.56899378922471</v>
       </c>
       <c r="W139">
         <v>888.1566999720628</v>
@@ -12640,16 +12640,16 @@
         <v>3034.861362686344</v>
       </c>
       <c r="Y139">
-        <v>-30.20982316391235</v>
+        <v>-41.89480555329851</v>
       </c>
       <c r="Z139">
-        <v>-77.9111018366134</v>
+        <v>-118.0993413645597</v>
       </c>
       <c r="AA139">
-        <v>-0.03401406887417795</v>
+        <v>-0.04717051118864084</v>
       </c>
       <c r="AB139">
-        <v>-0.025672046438276</v>
+        <v>-0.03891424590809731</v>
       </c>
     </row>
     <row r="140" spans="1:28">
@@ -12678,16 +12678,16 @@
         <v>75</v>
       </c>
       <c r="I140">
-        <v>149.8324525455258</v>
+        <v>147.7917789132998</v>
       </c>
       <c r="J140">
-        <v>149.8324525455258</v>
+        <v>147.7917789132998</v>
       </c>
       <c r="K140">
-        <v>516.4038958758505</v>
+        <v>509.385393151811</v>
       </c>
       <c r="L140">
-        <v>0.003760655748785844</v>
+        <v>0.003760655748785843</v>
       </c>
       <c r="M140">
         <v>0.003692350564302524</v>
@@ -12708,7 +12708,7 @@
         <v>106</v>
       </c>
       <c r="S140">
-        <v>97939.08561392043</v>
+        <v>97939.08561392044</v>
       </c>
       <c r="T140">
         <v>470</v>
@@ -12717,7 +12717,7 @@
         <v>227.9</v>
       </c>
       <c r="V140">
-        <v>8.957540499746097</v>
+        <v>8.835541450829282</v>
       </c>
       <c r="W140">
         <v>156.9076836617272</v>
@@ -12726,16 +12726,16 @@
         <v>536.158840741241</v>
       </c>
       <c r="Y140">
-        <v>-7.075231116201451</v>
+        <v>-9.115904748427425</v>
       </c>
       <c r="Z140">
-        <v>-19.75494486539048</v>
+        <v>-26.77344758942996</v>
       </c>
       <c r="AA140">
-        <v>-0.04509168035043292</v>
+        <v>-0.05809724887711772</v>
       </c>
       <c r="AB140">
-        <v>-0.03684532150599107</v>
+        <v>-0.04993566375295724</v>
       </c>
     </row>
     <row r="141" spans="1:28">
@@ -12764,13 +12764,13 @@
         <v>76</v>
       </c>
       <c r="I141">
-        <v>1148.567459810531</v>
+        <v>1132.924311145151</v>
       </c>
       <c r="J141">
-        <v>1148.567459810531</v>
+        <v>1132.924311145151</v>
       </c>
       <c r="K141">
-        <v>3958.586413328379</v>
+        <v>3904.784825565047</v>
       </c>
       <c r="L141">
         <v>0.02882797916754656</v>
@@ -12794,7 +12794,7 @@
         <v>106</v>
       </c>
       <c r="S141">
-        <v>94899.61867896037</v>
+        <v>94899.61867896038</v>
       </c>
       <c r="T141">
         <v>3540</v>
@@ -12803,7 +12803,7 @@
         <v>79.7</v>
       </c>
       <c r="V141">
-        <v>79.46576823720859</v>
+        <v>78.3834680068431</v>
       </c>
       <c r="W141">
         <v>1160.524754630164</v>
@@ -12812,16 +12812,16 @@
         <v>3965.552180576828</v>
       </c>
       <c r="Y141">
-        <v>-11.95729481963303</v>
+        <v>-27.60044348501287</v>
       </c>
       <c r="Z141">
-        <v>-6.965767248449083</v>
+        <v>-60.76735501178155</v>
       </c>
       <c r="AA141">
-        <v>-0.01030335180006012</v>
+        <v>-0.02378272705937116</v>
       </c>
       <c r="AB141">
-        <v>-0.001756569307691179</v>
+        <v>-0.01532380668432973</v>
       </c>
     </row>
     <row r="142" spans="1:28">
@@ -12850,16 +12850,16 @@
         <v>77</v>
       </c>
       <c r="I142">
-        <v>288.4131040832826</v>
+        <v>284.4850030164436</v>
       </c>
       <c r="J142">
-        <v>288.4131040832826</v>
+        <v>284.4850030164436</v>
       </c>
       <c r="K142">
-        <v>994.0279828563869</v>
+        <v>980.5180380996451</v>
       </c>
       <c r="L142">
-        <v>0.007238901716344861</v>
+        <v>0.007238901716344862</v>
       </c>
       <c r="M142">
         <v>0.007106033161487996</v>
@@ -12889,7 +12889,7 @@
         <v>41.9</v>
       </c>
       <c r="V142">
-        <v>26.22243973827545</v>
+        <v>25.86529787456423</v>
       </c>
       <c r="W142">
         <v>301.973277990499</v>
@@ -12898,16 +12898,16 @@
         <v>1031.852863313349</v>
       </c>
       <c r="Y142">
-        <v>-13.56017390721644</v>
+        <v>-17.48827497405546</v>
       </c>
       <c r="Z142">
-        <v>-37.82488045696209</v>
+        <v>-51.33482521370388</v>
       </c>
       <c r="AA142">
-        <v>-0.04490521147252997</v>
+        <v>-0.05791331965011053</v>
       </c>
       <c r="AB142">
-        <v>-0.03665724232765499</v>
+        <v>-0.04975014077963044</v>
       </c>
     </row>
     <row r="143" spans="1:28">
@@ -12936,13 +12936,13 @@
         <v>79</v>
       </c>
       <c r="I143">
-        <v>30.65940218866674</v>
+        <v>30.24183021034507</v>
       </c>
       <c r="J143">
-        <v>30.65940218866674</v>
+        <v>30.24183021034507</v>
       </c>
       <c r="K143">
-        <v>105.6689286364142</v>
+        <v>104.2327704869426</v>
       </c>
       <c r="L143">
         <v>0.0007695225909761687</v>
@@ -12975,7 +12975,7 @@
         <v>22.5</v>
       </c>
       <c r="V143">
-        <v>2.396967130552039</v>
+        <v>2.364321148072751</v>
       </c>
       <c r="W143">
         <v>32.56574566564078</v>
@@ -12984,16 +12984,16 @@
         <v>111.2782499651607</v>
       </c>
       <c r="Y143">
-        <v>-1.906343476974044</v>
+        <v>-2.323915455295712</v>
       </c>
       <c r="Z143">
-        <v>-5.609321328746518</v>
+        <v>-7.045479478218169</v>
       </c>
       <c r="AA143">
-        <v>-0.05853830268610659</v>
+        <v>-0.07136073219866759</v>
       </c>
       <c r="AB143">
-        <v>-0.05040806564178262</v>
+        <v>-0.06331407512630711</v>
       </c>
     </row>
     <row r="144" spans="1:28">
@@ -13022,13 +13022,13 @@
         <v>81</v>
       </c>
       <c r="I144">
-        <v>22.05945045930258</v>
+        <v>21.75900727674161</v>
       </c>
       <c r="J144">
-        <v>22.05945045930258</v>
+        <v>21.75900727674161</v>
       </c>
       <c r="K144">
-        <v>76.02883063402371</v>
+        <v>74.99551434967344</v>
       </c>
       <c r="L144">
         <v>0.0005536717698699248</v>
@@ -13061,7 +13061,7 @@
         <v>161</v>
       </c>
       <c r="V144">
-        <v>2.808454470937621</v>
+        <v>2.770204152740313</v>
       </c>
       <c r="W144">
         <v>23.68417866592154</v>
@@ -13070,16 +13070,16 @@
         <v>80.92963633830203</v>
       </c>
       <c r="Y144">
-        <v>-1.624728206618954</v>
+        <v>-1.925171389179923</v>
       </c>
       <c r="Z144">
-        <v>-4.900805704278326</v>
+        <v>-5.93412198862859</v>
       </c>
       <c r="AA144">
-        <v>-0.06859972767207366</v>
+        <v>-0.08128512355592026</v>
       </c>
       <c r="AB144">
-        <v>-0.06055637867680488</v>
+        <v>-0.07332446131133934</v>
       </c>
     </row>
     <row r="145" spans="1:28">
@@ -13108,13 +13108,13 @@
         <v>83</v>
       </c>
       <c r="I145">
-        <v>118.6447244087007</v>
+        <v>117.0288183977517</v>
       </c>
       <c r="J145">
-        <v>118.6447244087007</v>
+        <v>117.0288183977517</v>
       </c>
       <c r="K145">
-        <v>408.9140694747256</v>
+        <v>403.3564729239893</v>
       </c>
       <c r="L145">
         <v>0.002977872665970828</v>
@@ -13138,7 +13138,7 @@
         <v>105</v>
       </c>
       <c r="S145">
-        <v>35930</v>
+        <v>35930.00000000001</v>
       </c>
       <c r="T145">
         <v>350</v>
@@ -13147,7 +13147,7 @@
         <v>351.3</v>
       </c>
       <c r="V145">
-        <v>16.86352633305412</v>
+        <v>16.63385009836954</v>
       </c>
       <c r="W145">
         <v>124.3419379960886</v>
@@ -13156,16 +13156,16 @@
         <v>424.8805907760874</v>
       </c>
       <c r="Y145">
-        <v>-5.697213587387878</v>
+        <v>-7.313119598336911</v>
       </c>
       <c r="Z145">
-        <v>-15.96652130136181</v>
+        <v>-21.52411785209819</v>
       </c>
       <c r="AA145">
-        <v>-0.04581892223335859</v>
+        <v>-0.05881458594096353</v>
       </c>
       <c r="AB145">
-        <v>-0.03757884367510726</v>
+        <v>-0.05065921654077491</v>
       </c>
     </row>
     <row r="146" spans="1:28">
@@ -13194,13 +13194,13 @@
         <v>84</v>
       </c>
       <c r="I146">
-        <v>397.0951060316302</v>
+        <v>391.6867882833874</v>
       </c>
       <c r="J146">
-        <v>397.0951060316302</v>
+        <v>391.6867882833874</v>
       </c>
       <c r="K146">
-        <v>1368.605107265804</v>
+        <v>1350.004243193723</v>
       </c>
       <c r="L146">
         <v>0.00996671927838084</v>
@@ -13224,7 +13224,7 @@
         <v>105</v>
       </c>
       <c r="S146">
-        <v>70247.14145513088</v>
+        <v>70247.1414551309</v>
       </c>
       <c r="T146">
         <v>1520</v>
@@ -13233,7 +13233,7 @@
         <v>825.8</v>
       </c>
       <c r="V146">
-        <v>35.45020016873566</v>
+        <v>34.96737894067434</v>
       </c>
       <c r="W146">
         <v>426.3152159865897</v>
@@ -13242,16 +13242,16 @@
         <v>1456.733454089444</v>
       </c>
       <c r="Y146">
-        <v>-29.22010995495953</v>
+        <v>-34.62842770320231</v>
       </c>
       <c r="Z146">
-        <v>-88.12834682363973</v>
+        <v>-106.7292108957201</v>
       </c>
       <c r="AA146">
-        <v>-0.06854109086239765</v>
+        <v>-0.08122728536222734</v>
       </c>
       <c r="AB146">
-        <v>-0.06049723549372722</v>
+        <v>-0.07326612194983405</v>
       </c>
     </row>
     <row r="147" spans="1:28">
@@ -13280,16 +13280,16 @@
         <v>85</v>
       </c>
       <c r="I147">
-        <v>1484.157719877564</v>
+        <v>1463.943931251908</v>
       </c>
       <c r="J147">
-        <v>1484.157719877564</v>
+        <v>1463.943931251908</v>
       </c>
       <c r="K147">
-        <v>5115.212463108545</v>
+        <v>5045.691042195408</v>
       </c>
       <c r="L147">
-        <v>0.03725098379249028</v>
+        <v>0.03725098379249027</v>
       </c>
       <c r="M147">
         <v>0.03901351539640506</v>
@@ -13310,7 +13310,7 @@
         <v>105</v>
       </c>
       <c r="S147">
-        <v>46949.81114468435</v>
+        <v>46949.81114468437</v>
       </c>
       <c r="T147">
         <v>6050</v>
@@ -13319,7 +13319,7 @@
         <v>1450.2</v>
       </c>
       <c r="V147">
-        <v>144.1180056990994</v>
+        <v>142.1551611406431</v>
       </c>
       <c r="W147">
         <v>1657.89250661452</v>
@@ -13328,16 +13328,16 @@
         <v>5665.074543681185</v>
       </c>
       <c r="Y147">
-        <v>-173.7347867369567</v>
+        <v>-193.9485753626118</v>
       </c>
       <c r="Z147">
-        <v>-549.8620805726396</v>
+        <v>-619.3835014857768</v>
       </c>
       <c r="AA147">
-        <v>-0.1047925520163727</v>
+        <v>-0.1169850123508081</v>
       </c>
       <c r="AB147">
-        <v>-0.09706175555729533</v>
+        <v>-0.1093336895587078</v>
       </c>
     </row>
     <row r="148" spans="1:28">
@@ -13366,13 +13366,13 @@
         <v>86</v>
       </c>
       <c r="I148">
-        <v>84.65436824163152</v>
+        <v>83.50140081575992</v>
       </c>
       <c r="J148">
-        <v>84.65436824163152</v>
+        <v>83.50140081575992</v>
       </c>
       <c r="K148">
-        <v>291.764866824192</v>
+        <v>287.799458102572</v>
       </c>
       <c r="L148">
         <v>0.002124746216050856</v>
@@ -13405,7 +13405,7 @@
         <v>81</v>
       </c>
       <c r="V148">
-        <v>7.997438567263997</v>
+        <v>7.888515822342608</v>
       </c>
       <c r="W148">
         <v>88.81566999720523</v>
@@ -13414,16 +13414,16 @@
         <v>303.4861362686308</v>
       </c>
       <c r="Y148">
-        <v>-4.161301755573717</v>
+        <v>-5.314269181445312</v>
       </c>
       <c r="Z148">
-        <v>-11.72126944443886</v>
+        <v>-15.68667816605887</v>
       </c>
       <c r="AA148">
-        <v>-0.04685323834977163</v>
+        <v>-0.05983481497817374</v>
       </c>
       <c r="AB148">
-        <v>-0.03862209189702087</v>
+        <v>-0.05168828586019429</v>
       </c>
     </row>
     <row r="149" spans="1:28">
@@ -13452,13 +13452,13 @@
         <v>87</v>
       </c>
       <c r="I149">
-        <v>1124.991374494884</v>
+        <v>1109.669325129672</v>
       </c>
       <c r="J149">
-        <v>1124.991374494884</v>
+        <v>1109.669325129672</v>
       </c>
       <c r="K149">
-        <v>3877.330436404405</v>
+        <v>3824.633207651414</v>
       </c>
       <c r="L149">
         <v>0.0282362412678468</v>
@@ -13482,7 +13482,7 @@
         <v>105</v>
       </c>
       <c r="S149">
-        <v>60618.98309741258</v>
+        <v>60618.98309741259</v>
       </c>
       <c r="T149">
         <v>4070</v>
@@ -13491,7 +13491,7 @@
         <v>286.3</v>
       </c>
       <c r="V149">
-        <v>106.5022895428713</v>
+        <v>105.0517598989292</v>
       </c>
       <c r="W149">
         <v>1127.959008964523</v>
@@ -13500,16 +13500,16 @@
         <v>3854.273930611667</v>
       </c>
       <c r="Y149">
-        <v>-2.967634469639052</v>
+        <v>-18.2896838348513</v>
       </c>
       <c r="Z149">
-        <v>23.05650579273788</v>
+        <v>-29.6407229602537</v>
       </c>
       <c r="AA149">
-        <v>-0.002630977230602882</v>
+        <v>-0.0162148479594497</v>
       </c>
       <c r="AB149">
-        <v>0.005982062045361381</v>
+        <v>-0.007690351929799073</v>
       </c>
     </row>
     <row r="150" spans="1:28">
@@ -13538,13 +13538,13 @@
         <v>88</v>
       </c>
       <c r="I150">
-        <v>11274.86898379907</v>
+        <v>11121.30860718406</v>
       </c>
       <c r="J150">
-        <v>11274.86898379907</v>
+        <v>11121.30860718406</v>
       </c>
       <c r="K150">
-        <v>38859.31365205767</v>
+        <v>38331.17240273827</v>
       </c>
       <c r="L150">
         <v>0.282988766054189</v>
@@ -13577,7 +13577,7 @@
         <v>668.1999999999999</v>
       </c>
       <c r="V150">
-        <v>1143.656452302629</v>
+        <v>1128.08019010516</v>
       </c>
       <c r="W150">
         <v>12161.82574495088</v>
@@ -13586,16 +13586,16 @@
         <v>41557.36825971867</v>
       </c>
       <c r="Y150">
-        <v>-886.9567611518069</v>
+        <v>-1040.517137766814</v>
       </c>
       <c r="Z150">
-        <v>-2698.054607661004</v>
+        <v>-3226.195856980397</v>
       </c>
       <c r="AA150">
-        <v>-0.07292957321971474</v>
+        <v>-0.08555599788944489</v>
       </c>
       <c r="AB150">
-        <v>-0.06492361573040741</v>
+        <v>-0.07763234276092337</v>
       </c>
     </row>
     <row r="151" spans="1:28">
@@ -13624,13 +13624,13 @@
         <v>89</v>
       </c>
       <c r="I151">
-        <v>1676.357225864561</v>
+        <v>1653.525736885404</v>
       </c>
       <c r="J151">
-        <v>1676.357225864561</v>
+        <v>1653.525736885404</v>
       </c>
       <c r="K151">
-        <v>5777.636203699336</v>
+        <v>5699.111708129066</v>
       </c>
       <c r="L151">
         <v>0.04207501333231365</v>
@@ -13663,7 +13663,7 @@
         <v>1434.9</v>
       </c>
       <c r="V151">
-        <v>195.671142956123</v>
+        <v>193.0061599351933</v>
       </c>
       <c r="W151">
         <v>1773.352877610896</v>
@@ -13672,16 +13672,16 @@
         <v>6059.606520830435</v>
       </c>
       <c r="Y151">
-        <v>-96.9956517463354</v>
+        <v>-119.8271407254924</v>
       </c>
       <c r="Z151">
-        <v>-281.9703171310994</v>
+        <v>-360.4948127013695</v>
       </c>
       <c r="AA151">
-        <v>-0.05469619327937161</v>
+        <v>-0.06757095118424847</v>
       </c>
       <c r="AB151">
-        <v>-0.04653277670122662</v>
+        <v>-0.05949145566830727</v>
       </c>
     </row>
     <row r="152" spans="1:28">
@@ -18612,13 +18612,13 @@
         <v>72</v>
       </c>
       <c r="I209">
-        <v>6121.928858063344</v>
+        <v>6105.364701206262</v>
       </c>
       <c r="J209">
-        <v>6121.928858063344</v>
+        <v>6105.364701206262</v>
       </c>
       <c r="K209">
-        <v>45546.32946851137</v>
+        <v>45426.52919430201</v>
       </c>
       <c r="L209">
         <v>0.5</v>
@@ -18642,7 +18642,7 @@
         <v>105</v>
       </c>
       <c r="S209">
-        <v>68026.51492030805</v>
+        <v>68026.51492030804</v>
       </c>
       <c r="T209">
         <v>46080</v>
@@ -18651,7 +18651,7 @@
         <v>6175</v>
       </c>
       <c r="V209">
-        <v>556.2449257629248</v>
+        <v>554.7398889657136</v>
       </c>
       <c r="W209">
         <v>6244.586842570625</v>
@@ -18660,16 +18660,16 @@
         <v>47550</v>
       </c>
       <c r="Y209">
-        <v>-122.6579845072811</v>
+        <v>-139.2221413643629</v>
       </c>
       <c r="Z209">
-        <v>-2003.670531488635</v>
+        <v>-2123.470805697987</v>
       </c>
       <c r="AA209">
-        <v>-0.01964228981028761</v>
+        <v>-0.02229485230556121</v>
       </c>
       <c r="AB209">
-        <v>-0.04213818152447182</v>
+        <v>-0.04465764049838038</v>
       </c>
     </row>
     <row r="210" spans="1:28">
@@ -18698,16 +18698,16 @@
         <v>73</v>
       </c>
       <c r="I210">
-        <v>503.1815030562501</v>
+        <v>501.820040429446</v>
       </c>
       <c r="J210">
-        <v>503.1815030562501</v>
+        <v>501.820040429446</v>
       </c>
       <c r="K210">
-        <v>3743.602882688643</v>
+        <v>3733.756103439679</v>
       </c>
       <c r="L210">
-        <v>0.04109664737393161</v>
+        <v>0.0410966473739316</v>
       </c>
       <c r="M210">
         <v>0.04050042408821026</v>
@@ -18737,7 +18737,7 @@
         <v>739.7</v>
       </c>
       <c r="V210">
-        <v>38.04177050653755</v>
+        <v>37.93884055285777</v>
       </c>
       <c r="W210">
         <v>505.8168307595363</v>
@@ -18746,16 +18746,16 @@
         <v>3851.590330788794</v>
       </c>
       <c r="Y210">
-        <v>-2.635327703286237</v>
+        <v>-3.996790330090334</v>
       </c>
       <c r="Z210">
-        <v>-107.9874481001511</v>
+        <v>-117.8342273491157</v>
       </c>
       <c r="AA210">
-        <v>-0.005210043523717903</v>
+        <v>-0.007901655474944834</v>
       </c>
       <c r="AB210">
-        <v>-0.02803710644845129</v>
+        <v>-0.03059365540700784</v>
       </c>
     </row>
     <row r="211" spans="1:28">
@@ -18784,16 +18784,16 @@
         <v>74</v>
       </c>
       <c r="I211">
-        <v>400.9819708225428</v>
+        <v>399.8970303706755</v>
       </c>
       <c r="J211">
-        <v>400.9819708225428</v>
+        <v>399.8970303706755</v>
       </c>
       <c r="K211">
-        <v>2983.252072581921</v>
+        <v>2975.405240125795</v>
       </c>
       <c r="L211">
-        <v>0.03274964313693384</v>
+        <v>0.03274964313693383</v>
       </c>
       <c r="M211">
         <v>0.03201865988125521</v>
@@ -18814,7 +18814,7 @@
         <v>106</v>
       </c>
       <c r="S211">
-        <v>84283.33179283484</v>
+        <v>84283.33179283483</v>
       </c>
       <c r="T211">
         <v>2750</v>
@@ -18823,7 +18823,7 @@
         <v>742.2</v>
       </c>
       <c r="V211">
-        <v>33.50358558392582</v>
+        <v>33.41293463718117</v>
       </c>
       <c r="W211">
         <v>399.8866044224604</v>
@@ -18832,16 +18832,16 @@
         <v>3044.974554707369</v>
       </c>
       <c r="Y211">
-        <v>1.095366400082355</v>
+        <v>0.01042594821501552</v>
       </c>
       <c r="Z211">
-        <v>-61.72248212544855</v>
+        <v>-69.56931458157442</v>
       </c>
       <c r="AA211">
-        <v>0.002739192531003501</v>
+        <v>2.607226173548195E-05</v>
       </c>
       <c r="AB211">
-        <v>-0.02027027845931548</v>
+        <v>-0.02284725646525484</v>
       </c>
     </row>
     <row r="212" spans="1:28">
@@ -18870,13 +18870,13 @@
         <v>75</v>
       </c>
       <c r="I212">
-        <v>78.71480340048694</v>
+        <v>78.50182406329932</v>
       </c>
       <c r="J212">
-        <v>78.71480340048694</v>
+        <v>78.50182406329932</v>
       </c>
       <c r="K212">
-        <v>585.6275779823152</v>
+        <v>584.0872048008639</v>
       </c>
       <c r="L212">
         <v>0.006428921768407168</v>
@@ -18909,7 +18909,7 @@
         <v>210</v>
       </c>
       <c r="V212">
-        <v>4.435961627259637</v>
+        <v>4.423959206795513</v>
       </c>
       <c r="W212">
         <v>82.09592541123284</v>
@@ -18918,16 +18918,16 @@
         <v>625.1272264630968</v>
       </c>
       <c r="Y212">
-        <v>-3.381122010745898</v>
+        <v>-3.594101347933517</v>
       </c>
       <c r="Z212">
-        <v>-39.49964848078162</v>
+        <v>-41.0400216622329</v>
       </c>
       <c r="AA212">
-        <v>-0.04118501611144849</v>
+        <v>-0.04377929026233683</v>
       </c>
       <c r="AB212">
-        <v>-0.06318657516209367</v>
+        <v>-0.06565067065536878</v>
       </c>
     </row>
     <row r="213" spans="1:28">
@@ -18956,16 +18956,16 @@
         <v>76</v>
       </c>
       <c r="I213">
-        <v>769.2461957889168</v>
+        <v>767.1648395784506</v>
       </c>
       <c r="J213">
-        <v>769.2461957889168</v>
+        <v>767.1648395784506</v>
       </c>
       <c r="K213">
-        <v>5723.088504965845</v>
+        <v>5708.035094949712</v>
       </c>
       <c r="L213">
-        <v>0.06282711001906888</v>
+        <v>0.06282711001906886</v>
       </c>
       <c r="M213">
         <v>0.06022052586938088</v>
@@ -18986,7 +18986,7 @@
         <v>106</v>
       </c>
       <c r="S213">
-        <v>99871.87453805875</v>
+        <v>99871.87453805879</v>
       </c>
       <c r="T213">
         <v>4890</v>
@@ -18995,7 +18995,7 @@
         <v>94.2</v>
       </c>
       <c r="V213">
-        <v>49.31777408405</v>
+        <v>49.18433454812752</v>
       </c>
       <c r="W213">
         <v>752.1046069932396</v>
@@ -19004,16 +19004,16 @@
         <v>5726.972010178122</v>
       </c>
       <c r="Y213">
-        <v>17.14158879567719</v>
+        <v>15.060232585211</v>
       </c>
       <c r="Z213">
-        <v>-3.883505212277669</v>
+        <v>-18.93691522840982</v>
       </c>
       <c r="AA213">
-        <v>0.02279149553970393</v>
+        <v>0.02002411957748634</v>
       </c>
       <c r="AB213">
-        <v>-0.0006781079434954114</v>
+        <v>-0.003306619133942796</v>
       </c>
     </row>
     <row r="214" spans="1:28">
@@ -19042,16 +19042,16 @@
         <v>77</v>
       </c>
       <c r="I214">
-        <v>4.322669274515176</v>
+        <v>4.310973390168194</v>
       </c>
       <c r="J214">
-        <v>4.322669274515176</v>
+        <v>4.310973390168194</v>
       </c>
       <c r="K214">
-        <v>32.16007953133291</v>
+        <v>32.07548904091563</v>
       </c>
       <c r="L214">
-        <v>0.0003530479833020015</v>
+        <v>0.0003530479833020014</v>
       </c>
       <c r="M214">
         <v>0.0003180661577608016</v>
@@ -19081,7 +19081,7 @@
         <v>14.9</v>
       </c>
       <c r="V214">
-        <v>0.4595631265806359</v>
+        <v>0.4583196825794227</v>
       </c>
       <c r="W214">
         <v>3.972383487640188</v>
@@ -19090,16 +19090,16 @@
         <v>30.24809160305223</v>
       </c>
       <c r="Y214">
-        <v>0.3502857868749878</v>
+        <v>0.3385899025280059</v>
       </c>
       <c r="Z214">
-        <v>1.911987928280684</v>
+        <v>1.827397437863407</v>
       </c>
       <c r="AA214">
-        <v>0.08818025449075577</v>
+        <v>0.08523595558724535</v>
       </c>
       <c r="AB214">
-        <v>0.06321020027880873</v>
+        <v>0.06041364400255291</v>
       </c>
     </row>
     <row r="215" spans="1:28">
@@ -19128,13 +19128,13 @@
         <v>79</v>
       </c>
       <c r="I215">
-        <v>22.33117639104094</v>
+        <v>22.27075473029963</v>
       </c>
       <c r="J215">
-        <v>22.33117639104094</v>
+        <v>22.27075473029963</v>
       </c>
       <c r="K215">
-        <v>166.1409566996424</v>
+        <v>165.7039570028001</v>
       </c>
       <c r="L215">
         <v>0.001823867681966607</v>
@@ -19167,7 +19167,7 @@
         <v>7</v>
       </c>
       <c r="V215">
-        <v>1.788866293005825</v>
+        <v>1.78402614171353</v>
       </c>
       <c r="W215">
         <v>22.51017309662815</v>
@@ -19176,16 +19176,16 @@
         <v>171.4058524172991</v>
       </c>
       <c r="Y215">
-        <v>-0.1789967055872062</v>
+        <v>-0.2394183663285219</v>
       </c>
       <c r="Z215">
-        <v>-5.264895717656714</v>
+        <v>-5.701895414499063</v>
       </c>
       <c r="AA215">
-        <v>-0.007951813822969602</v>
+        <v>-0.01063600734213745</v>
       </c>
       <c r="AB215">
-        <v>-0.03071596239805727</v>
+        <v>-0.03326546517570132</v>
       </c>
     </row>
     <row r="216" spans="1:28">
@@ -19214,16 +19214,16 @@
         <v>83</v>
       </c>
       <c r="I216">
-        <v>40.72155694836876</v>
+        <v>40.61137627289931</v>
       </c>
       <c r="J216">
-        <v>40.72155694836876</v>
+        <v>40.61137627289931</v>
       </c>
       <c r="K216">
-        <v>302.9629210405243</v>
+        <v>302.1660392404</v>
       </c>
       <c r="L216">
-        <v>0.003325876361233225</v>
+        <v>0.003325876361233224</v>
       </c>
       <c r="M216">
         <v>0.003286683630195066</v>
@@ -19253,7 +19253,7 @@
         <v>351.3</v>
       </c>
       <c r="V216">
-        <v>5.787944228824222</v>
+        <v>5.772283737121511</v>
       </c>
       <c r="W216">
         <v>41.04796270561673</v>
@@ -19262,16 +19262,16 @@
         <v>312.5636132315507</v>
       </c>
       <c r="Y216">
-        <v>-0.3264057572479686</v>
+        <v>-0.4365864327174265</v>
       </c>
       <c r="Z216">
-        <v>-9.600692191026383</v>
+        <v>-10.39757399115069</v>
       </c>
       <c r="AA216">
-        <v>-0.007951813822986771</v>
+        <v>-0.01063600734215457</v>
       </c>
       <c r="AB216">
-        <v>-0.03071596239807376</v>
+        <v>-0.03326546517571785</v>
       </c>
     </row>
     <row r="217" spans="1:28">
@@ -19300,16 +19300,16 @@
         <v>84</v>
       </c>
       <c r="I217">
-        <v>240.738447989108</v>
+        <v>240.0870798490209</v>
       </c>
       <c r="J217">
-        <v>240.738447989108</v>
+        <v>240.0870798490209</v>
       </c>
       <c r="K217">
-        <v>1791.061758812838</v>
+        <v>1786.350738356623</v>
       </c>
       <c r="L217">
-        <v>0.01966197693330146</v>
+        <v>0.01966197693330145</v>
       </c>
       <c r="M217">
         <v>0.0198261238337574</v>
@@ -19330,7 +19330,7 @@
         <v>105</v>
       </c>
       <c r="S217">
-        <v>73162.52849628514</v>
+        <v>73162.52849628516</v>
       </c>
       <c r="T217">
         <v>1800</v>
@@ -19339,7 +19339,7 @@
         <v>300.2</v>
       </c>
       <c r="V217">
-        <v>21.26283019621609</v>
+        <v>21.20529916918828</v>
       </c>
       <c r="W217">
         <v>247.6119040629146</v>
@@ -19348,16 +19348,16 @@
         <v>1885.464376590328</v>
       </c>
       <c r="Y217">
-        <v>-6.873456073806636</v>
+        <v>-7.524824213893737</v>
       </c>
       <c r="Z217">
-        <v>-94.40261777749038</v>
+        <v>-99.11363823370561</v>
       </c>
       <c r="AA217">
-        <v>-0.02775898880879406</v>
+        <v>-0.03038958988006403</v>
       </c>
       <c r="AB217">
-        <v>-0.05006862974956226</v>
+        <v>-0.05256722930662981</v>
       </c>
     </row>
     <row r="218" spans="1:28">
@@ -19386,16 +19386,16 @@
         <v>85</v>
       </c>
       <c r="I218">
-        <v>502.8036680085476</v>
+        <v>501.4432276933616</v>
       </c>
       <c r="J218">
-        <v>502.8036680085476</v>
+        <v>501.4432276933616</v>
       </c>
       <c r="K218">
-        <v>3740.791840618995</v>
+        <v>3730.952455239409</v>
       </c>
       <c r="L218">
-        <v>0.04106578822345285</v>
+        <v>0.04106578822345284</v>
       </c>
       <c r="M218">
         <v>0.04293893129770996</v>
@@ -19416,7 +19416,7 @@
         <v>105</v>
       </c>
       <c r="S218">
-        <v>47812.95895669044</v>
+        <v>47812.95895669043</v>
       </c>
       <c r="T218">
         <v>4060</v>
@@ -19425,7 +19425,7 @@
         <v>1431.3</v>
       </c>
       <c r="V218">
-        <v>50.89956459243645</v>
+        <v>50.76184519199685</v>
       </c>
       <c r="W218">
         <v>536.2717708314473</v>
@@ -19434,16 +19434,16 @@
         <v>4083.492366412217</v>
       </c>
       <c r="Y218">
-        <v>-33.46810282289965</v>
+        <v>-34.82854313808571</v>
       </c>
       <c r="Z218">
-        <v>-342.7005257932219</v>
+        <v>-352.5399111728075</v>
       </c>
       <c r="AA218">
-        <v>-0.06240884686324247</v>
+        <v>-0.06494569550824349</v>
       </c>
       <c r="AB218">
-        <v>-0.08392339082399727</v>
+        <v>-0.08633294237857272</v>
       </c>
     </row>
     <row r="219" spans="1:28">
@@ -19472,13 +19472,13 @@
         <v>86</v>
       </c>
       <c r="I219">
-        <v>53.85754306074649</v>
+        <v>53.71182023189979</v>
       </c>
       <c r="J219">
-        <v>53.85754306074649</v>
+        <v>53.71182023189979</v>
       </c>
       <c r="K219">
-        <v>400.692895569731</v>
+        <v>399.6389551244053</v>
       </c>
       <c r="L219">
         <v>0.00439873970356658</v>
@@ -19511,7 +19511,7 @@
         <v>81</v>
       </c>
       <c r="V219">
-        <v>5.088011415815798</v>
+        <v>5.074244738492981</v>
       </c>
       <c r="W219">
         <v>54.28924099775153</v>
@@ -19520,16 +19520,16 @@
         <v>413.3905852417312</v>
       </c>
       <c r="Y219">
-        <v>-0.4316979370050333</v>
+        <v>-0.5774207658517412</v>
       </c>
       <c r="Z219">
-        <v>-12.69768967200019</v>
+        <v>-13.75163011732587</v>
       </c>
       <c r="AA219">
-        <v>-0.007951813822980372</v>
+        <v>-0.01063600734214825</v>
       </c>
       <c r="AB219">
-        <v>-0.03071596239806765</v>
+        <v>-0.03326546517571167</v>
       </c>
     </row>
     <row r="220" spans="1:28">
@@ -19558,13 +19558,13 @@
         <v>87</v>
       </c>
       <c r="I220">
-        <v>235.0676792942381</v>
+        <v>234.4316546029789</v>
       </c>
       <c r="J220">
-        <v>235.0676792942381</v>
+        <v>234.4316546029789</v>
       </c>
       <c r="K220">
-        <v>1748.872000436918</v>
+        <v>1744.271951483374</v>
       </c>
       <c r="L220">
         <v>0.01919882481030669</v>
@@ -19597,7 +19597,7 @@
         <v>287.8</v>
       </c>
       <c r="V220">
-        <v>21.97127967015184</v>
+        <v>21.91183178513961</v>
       </c>
       <c r="W220">
         <v>223.7776031370716</v>
@@ -19606,16 +19606,16 @@
         <v>1703.975826972</v>
       </c>
       <c r="Y220">
-        <v>11.29007615716648</v>
+        <v>10.65405146590734</v>
       </c>
       <c r="Z220">
-        <v>44.89617346491764</v>
+        <v>40.29612451137359</v>
       </c>
       <c r="AA220">
-        <v>0.05045221683892519</v>
+        <v>0.04760999901934496</v>
       </c>
       <c r="AB220">
-        <v>0.02634789341155094</v>
+        <v>0.02364829586988955</v>
       </c>
     </row>
     <row r="221" spans="1:28">
@@ -19644,13 +19644,13 @@
         <v>88</v>
       </c>
       <c r="I221">
-        <v>3104.203366648682</v>
+        <v>3095.804296245613</v>
       </c>
       <c r="J221">
-        <v>3104.203366648682</v>
+        <v>3095.804296245613</v>
       </c>
       <c r="K221">
-        <v>23094.85662977302</v>
+        <v>23034.11034814378</v>
       </c>
       <c r="L221">
         <v>0.2535314799158486</v>
@@ -19683,7 +19683,7 @@
         <v>563.3000000000001</v>
       </c>
       <c r="V221">
-        <v>303.4330378213306</v>
+        <v>302.612036377076</v>
       </c>
       <c r="W221">
         <v>3208.361730184193</v>
@@ -19692,16 +19692,16 @@
         <v>24430.3753180662</v>
       </c>
       <c r="Y221">
-        <v>-104.1583635355109</v>
+        <v>-112.5574339385798</v>
       </c>
       <c r="Z221">
-        <v>-1335.518688293174</v>
+        <v>-1396.264969922417</v>
       </c>
       <c r="AA221">
-        <v>-0.03246465713500803</v>
+        <v>-0.03508252603802187</v>
       </c>
       <c r="AB221">
-        <v>-0.05466631891265139</v>
+        <v>-0.05715282519175554</v>
       </c>
     </row>
     <row r="222" spans="1:28">
@@ -19730,13 +19730,13 @@
         <v>89</v>
       </c>
       <c r="I222">
-        <v>165.7582773799008</v>
+        <v>165.3097837481488</v>
       </c>
       <c r="J222">
-        <v>165.7582773799008</v>
+        <v>165.3097837481488</v>
       </c>
       <c r="K222">
-        <v>1233.219347809635</v>
+        <v>1229.975617354253</v>
       </c>
       <c r="L222">
         <v>0.01353807608868049</v>
@@ -19769,7 +19769,7 @@
         <v>1352.1</v>
       </c>
       <c r="V222">
-        <v>20.25473661679025</v>
+        <v>20.19993319744349</v>
       </c>
       <c r="W222">
         <v>166.8401064808935</v>
@@ -19778,16 +19778,16 @@
         <v>1270.419847328236</v>
       </c>
       <c r="Y222">
-        <v>-1.081829100992678</v>
+        <v>-1.530322732744736</v>
       </c>
       <c r="Z222">
-        <v>-37.20049951860165</v>
+        <v>-40.44422997398374</v>
       </c>
       <c r="AA222">
-        <v>-0.006484226867336415</v>
+        <v>-0.009172391249462479</v>
       </c>
       <c r="AB222">
-        <v>-0.02928205159643591</v>
+        <v>-0.03183532598222565</v>
       </c>
     </row>
     <row r="223" spans="1:28">
@@ -24374,13 +24374,13 @@
         <v>72</v>
       </c>
       <c r="I276">
-        <v>7561.026618857612</v>
+        <v>7470.890075979912</v>
       </c>
       <c r="J276">
-        <v>7561.026618857612</v>
+        <v>7470.890075979912</v>
       </c>
       <c r="K276">
-        <v>14056.73309370521</v>
+        <v>13903.93948369915</v>
       </c>
       <c r="L276">
         <v>0.4999999999999999</v>
@@ -24413,7 +24413,7 @@
         <v>4992.900000000001</v>
       </c>
       <c r="V276">
-        <v>715.0351868473472</v>
+        <v>706.5111063187076</v>
       </c>
       <c r="W276">
         <v>9023.139594640334</v>
@@ -24422,16 +24422,16 @@
         <v>16337</v>
       </c>
       <c r="Y276">
-        <v>-1462.112975782721</v>
+        <v>-1552.249518660422</v>
       </c>
       <c r="Z276">
-        <v>-2280.266906294788</v>
+        <v>-2433.060516300848</v>
       </c>
       <c r="AA276">
-        <v>-0.1620403807840016</v>
+        <v>-0.1720298685817123</v>
       </c>
       <c r="AB276">
-        <v>-0.1395768443591105</v>
+        <v>-0.148929455610017</v>
       </c>
     </row>
     <row r="277" spans="1:28">
@@ -24460,13 +24460,13 @@
         <v>73</v>
       </c>
       <c r="I277">
-        <v>472.0074188814673</v>
+        <v>466.3805220200686</v>
       </c>
       <c r="J277">
-        <v>472.0074188814673</v>
+        <v>466.3805220200686</v>
       </c>
       <c r="K277">
-        <v>877.5107720051852</v>
+        <v>867.9724221069491</v>
       </c>
       <c r="L277">
         <v>0.03121318325373006</v>
@@ -24499,7 +24499,7 @@
         <v>600.3</v>
       </c>
       <c r="V277">
-        <v>35.4688619943317</v>
+        <v>35.04603044497547</v>
       </c>
       <c r="W277">
         <v>544.1089202798177</v>
@@ -24508,16 +24508,16 @@
         <v>985.1457286432131</v>
       </c>
       <c r="Y277">
-        <v>-72.10150139835036</v>
+        <v>-77.72839825974904</v>
       </c>
       <c r="Z277">
-        <v>-107.6349566380279</v>
+        <v>-117.173306536264</v>
       </c>
       <c r="AA277">
-        <v>-0.1325129927318061</v>
+        <v>-0.1428544825542942</v>
       </c>
       <c r="AB277">
-        <v>-0.1092579031797332</v>
+        <v>-0.1189400746807687</v>
       </c>
     </row>
     <row r="278" spans="1:28">
@@ -24546,13 +24546,13 @@
         <v>74</v>
       </c>
       <c r="I278">
-        <v>226.3903146148116</v>
+        <v>223.6914694276408</v>
       </c>
       <c r="J278">
-        <v>226.3903146148116</v>
+        <v>223.6914694276408</v>
       </c>
       <c r="K278">
-        <v>420.8830874372941</v>
+        <v>416.3081804591685</v>
       </c>
       <c r="L278">
         <v>0.0149708714191127</v>
@@ -24585,7 +24585,7 @@
         <v>456.9</v>
       </c>
       <c r="V278">
-        <v>19.10076128237079</v>
+        <v>18.873057205251</v>
       </c>
       <c r="W278">
         <v>260.7188576340777</v>
@@ -24594,16 +24594,16 @@
         <v>472.0489949748701</v>
       </c>
       <c r="Y278">
-        <v>-34.32854301926605</v>
+        <v>-37.02738820643685</v>
       </c>
       <c r="Z278">
-        <v>-51.16590753757595</v>
+        <v>-55.74081451570157</v>
       </c>
       <c r="AA278">
-        <v>-0.1316688149479644</v>
+        <v>-0.142020368386261</v>
       </c>
       <c r="AB278">
-        <v>-0.1083910951665087</v>
+        <v>-0.1180826886807989</v>
       </c>
     </row>
     <row r="279" spans="1:28">
@@ -24632,13 +24632,13 @@
         <v>75</v>
       </c>
       <c r="I279">
-        <v>39.53038430045629</v>
+        <v>39.05913451400752</v>
       </c>
       <c r="J279">
-        <v>39.53038430045629</v>
+        <v>39.05913451400752</v>
       </c>
       <c r="K279">
-        <v>73.49108649045652</v>
+        <v>72.69225447641102</v>
       </c>
       <c r="L279">
         <v>0.002614088422983815</v>
@@ -24671,7 +24671,7 @@
         <v>55.09999999999999</v>
       </c>
       <c r="V279">
-        <v>2.074952520159365</v>
+        <v>2.050216587298597</v>
       </c>
       <c r="W279">
         <v>51.01021127623237</v>
@@ -24680,16 +24680,16 @@
         <v>92.35741206030028</v>
       </c>
       <c r="Y279">
-        <v>-11.47982697577608</v>
+        <v>-11.95107676222484</v>
       </c>
       <c r="Z279">
-        <v>-18.86632556984375</v>
+        <v>-19.66515758388925</v>
       </c>
       <c r="AA279">
-        <v>-0.2250495869074154</v>
+        <v>-0.2342879290875102</v>
       </c>
       <c r="AB279">
-        <v>-0.2042751648078435</v>
+        <v>-0.212924519485776</v>
       </c>
     </row>
     <row r="280" spans="1:28">
@@ -24718,13 +24718,13 @@
         <v>76</v>
       </c>
       <c r="I280">
-        <v>323.1420322137348</v>
+        <v>319.2897900367827</v>
       </c>
       <c r="J280">
-        <v>323.1420322137348</v>
+        <v>319.2897900367827</v>
       </c>
       <c r="K280">
-        <v>600.7545703988351</v>
+        <v>594.2244997965852</v>
       </c>
       <c r="L280">
         <v>0.02136892570962526</v>
@@ -24757,7 +24757,7 @@
         <v>52.89999999999999</v>
       </c>
       <c r="V280">
-        <v>22.42894954153197</v>
+        <v>22.1615694522978</v>
       </c>
       <c r="W280">
         <v>362.739280186546</v>
@@ -24766,16 +24766,16 @@
         <v>656.7638190954772</v>
       </c>
       <c r="Y280">
-        <v>-39.5972479728112</v>
+        <v>-43.44949014976328</v>
       </c>
       <c r="Z280">
-        <v>-56.00924869664209</v>
+        <v>-62.539319298892</v>
       </c>
       <c r="AA280">
-        <v>-0.1091617316780458</v>
+        <v>-0.1197815966537137</v>
       </c>
       <c r="AB280">
-        <v>-0.0852806550363575</v>
+        <v>-0.09522345397318595</v>
       </c>
     </row>
     <row r="281" spans="1:28">
@@ -24804,13 +24804,13 @@
         <v>77</v>
       </c>
       <c r="I281">
-        <v>25.54324689519487</v>
+        <v>25.23874063102405</v>
       </c>
       <c r="J281">
-        <v>25.54324689519487</v>
+        <v>25.23874063102405</v>
       </c>
       <c r="K281">
-        <v>47.4875466060213</v>
+        <v>46.97136737519318</v>
       </c>
       <c r="L281">
         <v>0.001689138802361085</v>
@@ -24843,7 +24843,7 @@
         <v>14.9</v>
       </c>
       <c r="V281">
-        <v>2.71562168204355</v>
+        <v>2.6832482012291</v>
       </c>
       <c r="W281">
         <v>28.33900626457364</v>
@@ -24852,16 +24852,16 @@
         <v>51.30967336683367</v>
       </c>
       <c r="Y281">
-        <v>-2.795759369378771</v>
+        <v>-3.100265633549586</v>
       </c>
       <c r="Z281">
-        <v>-3.822126760812367</v>
+        <v>-4.338305991640489</v>
       </c>
       <c r="AA281">
-        <v>-0.09865410746154948</v>
+        <v>-0.1093992359719827</v>
       </c>
       <c r="AB281">
-        <v>-0.0744913485121301</v>
+        <v>-0.08455142484778999</v>
       </c>
     </row>
     <row r="282" spans="1:28">
@@ -24890,13 +24890,13 @@
         <v>83</v>
       </c>
       <c r="I282">
-        <v>38.59761525837987</v>
+        <v>38.13748520222625</v>
       </c>
       <c r="J282">
-        <v>38.59761525837987</v>
+        <v>38.13748520222625</v>
       </c>
       <c r="K282">
-        <v>71.75697204760586</v>
+        <v>70.97698947774633</v>
       </c>
       <c r="L282">
         <v>0.002552405725045016</v>
@@ -24929,7 +24929,7 @@
         <v>351.3</v>
       </c>
       <c r="V282">
-        <v>5.48605852090502</v>
+        <v>5.420658096594142</v>
       </c>
       <c r="W282">
         <v>45.34241002331837</v>
@@ -24938,16 +24938,16 @@
         <v>82.09547738693486</v>
       </c>
       <c r="Y282">
-        <v>-6.744794764938497</v>
+        <v>-7.204924821092114</v>
       </c>
       <c r="Z282">
-        <v>-10.338505339329</v>
+        <v>-11.11848790918853</v>
       </c>
       <c r="AA282">
-        <v>-0.1487524540815063</v>
+        <v>-0.1589003499678737</v>
       </c>
       <c r="AB282">
-        <v>-0.1259327026091979</v>
+        <v>-0.1354336226925698</v>
       </c>
     </row>
     <row r="283" spans="1:28">
@@ -24976,16 +24976,16 @@
         <v>84</v>
       </c>
       <c r="I283">
-        <v>91.01521777644284</v>
+        <v>89.93020677288825</v>
       </c>
       <c r="J283">
-        <v>91.01521777644284</v>
+        <v>89.93020677288825</v>
       </c>
       <c r="K283">
-        <v>169.2067345138127</v>
+        <v>167.3674943695092</v>
       </c>
       <c r="L283">
-        <v>0.006018707667914164</v>
+        <v>0.006018707667914163</v>
       </c>
       <c r="M283">
         <v>0.005967336683417067</v>
@@ -25015,7 +25015,7 @@
         <v>114.8</v>
       </c>
       <c r="V283">
-        <v>7.959584825729898</v>
+        <v>7.864696989051247</v>
       </c>
       <c r="W283">
         <v>107.6882238053805</v>
@@ -25024,16 +25024,16 @@
         <v>194.9767587939693</v>
       </c>
       <c r="Y283">
-        <v>-16.67300602893769</v>
+        <v>-17.75801703249228</v>
       </c>
       <c r="Z283">
-        <v>-25.77002428015655</v>
+        <v>-27.60926442446006</v>
       </c>
       <c r="AA283">
-        <v>-0.1548266415747554</v>
+        <v>-0.1649021258311906</v>
       </c>
       <c r="AB283">
-        <v>-0.1321697234047653</v>
+        <v>-0.141602848438129</v>
       </c>
     </row>
     <row r="284" spans="1:28">
@@ -25062,13 +25062,13 @@
         <v>85</v>
       </c>
       <c r="I284">
-        <v>446.4055452942415</v>
+        <v>441.0838535977854</v>
       </c>
       <c r="J284">
-        <v>446.4055452942415</v>
+        <v>441.0838535977854</v>
       </c>
       <c r="K284">
-        <v>829.9142322949749</v>
+        <v>820.8932463587375</v>
       </c>
       <c r="L284">
         <v>0.02952016755111546</v>
@@ -25101,7 +25101,7 @@
         <v>1244.8</v>
       </c>
       <c r="V284">
-        <v>43.50774714722625</v>
+        <v>42.98908240579188</v>
       </c>
       <c r="W284">
         <v>549.7767215327334</v>
@@ -25110,16 +25110,16 @@
         <v>995.4076633165821</v>
       </c>
       <c r="Y284">
-        <v>-103.3711762384919</v>
+        <v>-108.692867934948</v>
       </c>
       <c r="Z284">
-        <v>-165.4934310216072</v>
+        <v>-174.5144169578446</v>
       </c>
       <c r="AA284">
-        <v>-0.1880239235126241</v>
+        <v>-0.1977036561895909</v>
       </c>
       <c r="AB284">
-        <v>-0.1662569388608105</v>
+        <v>-0.1753195433279898</v>
       </c>
     </row>
     <row r="285" spans="1:28">
@@ -25148,13 +25148,13 @@
         <v>86</v>
       </c>
       <c r="I285">
-        <v>39.31686213805047</v>
+        <v>38.84815779291771</v>
       </c>
       <c r="J285">
-        <v>39.31686213805047</v>
+        <v>38.84815779291771</v>
       </c>
       <c r="K285">
-        <v>73.09412663330647</v>
+        <v>72.29960948596559</v>
       </c>
       <c r="L285">
         <v>0.002599968504276395</v>
@@ -25178,7 +25178,7 @@
         <v>105</v>
       </c>
       <c r="S285">
-        <v>62350</v>
+        <v>62349.99999999999</v>
       </c>
       <c r="T285">
         <v>130</v>
@@ -25187,7 +25187,7 @@
         <v>81</v>
       </c>
       <c r="V285">
-        <v>3.71432917329378</v>
+        <v>3.670049896461784</v>
       </c>
       <c r="W285">
         <v>45.34241002331837</v>
@@ -25196,16 +25196,16 @@
         <v>82.09547738693486</v>
       </c>
       <c r="Y285">
-        <v>-6.025547885267898</v>
+        <v>-6.494252230400654</v>
       </c>
       <c r="Z285">
-        <v>-9.001350753628387</v>
+        <v>-9.79586790096927</v>
       </c>
       <c r="AA285">
-        <v>-0.1328898901088214</v>
+        <v>-0.143226886860686</v>
       </c>
       <c r="AB285">
-        <v>-0.1096449042034673</v>
+        <v>-0.1193228690881361</v>
       </c>
     </row>
     <row r="286" spans="1:28">
@@ -25234,16 +25234,16 @@
         <v>87</v>
       </c>
       <c r="I286">
-        <v>516.1103127057809</v>
+        <v>509.9576562378347</v>
       </c>
       <c r="J286">
-        <v>516.1103127057809</v>
+        <v>509.9576562378347</v>
       </c>
       <c r="K286">
-        <v>959.502628190723</v>
+        <v>949.0730447737045</v>
       </c>
       <c r="L286">
-        <v>0.03412964526659472</v>
+        <v>0.03412964526659473</v>
       </c>
       <c r="M286">
         <v>0.0317211055276382</v>
@@ -25264,7 +25264,7 @@
         <v>105</v>
       </c>
       <c r="S286">
-        <v>61948.98390631137</v>
+        <v>61948.98390631135</v>
       </c>
       <c r="T286">
         <v>760</v>
@@ -25273,7 +25273,7 @@
         <v>257.9</v>
       </c>
       <c r="V286">
-        <v>49.05931850738207</v>
+        <v>48.47447234969725</v>
       </c>
       <c r="W286">
         <v>572.4479265443931</v>
@@ -25282,16 +25282,16 @@
         <v>1036.45540201005</v>
       </c>
       <c r="Y286">
-        <v>-56.33761383861224</v>
+        <v>-62.49027030655844</v>
       </c>
       <c r="Z286">
-        <v>-76.95277381932738</v>
+        <v>-87.38235723634591</v>
       </c>
       <c r="AA286">
-        <v>-0.09841526403754609</v>
+        <v>-0.1091632398492273</v>
       </c>
       <c r="AB286">
-        <v>-0.07424610231186886</v>
+        <v>-0.08430884442001159</v>
       </c>
     </row>
     <row r="287" spans="1:28">
@@ -25320,16 +25320,16 @@
         <v>88</v>
       </c>
       <c r="I287">
-        <v>4855.521890911683</v>
+        <v>4797.638222571959</v>
       </c>
       <c r="J287">
-        <v>4855.521890911683</v>
+        <v>4797.638222571959</v>
       </c>
       <c r="K287">
-        <v>9026.919053685408</v>
+        <v>8928.79842065847</v>
       </c>
       <c r="L287">
-        <v>0.3210887975715987</v>
+        <v>0.3210887975715986</v>
       </c>
       <c r="M287">
         <v>0.3263190954773872</v>
@@ -25350,7 +25350,7 @@
         <v>105</v>
       </c>
       <c r="S287">
-        <v>49365.28178745839</v>
+        <v>49365.2817874584</v>
       </c>
       <c r="T287">
         <v>9330</v>
@@ -25359,7 +25359,7 @@
         <v>531.1</v>
       </c>
       <c r="V287">
-        <v>465.5433339294565</v>
+        <v>459.9934967452435</v>
       </c>
       <c r="W287">
         <v>5888.845501778464</v>
@@ -25368,16 +25368,16 @@
         <v>10662.15012562815</v>
       </c>
       <c r="Y287">
-        <v>-1033.323610866781</v>
+        <v>-1091.207279206505</v>
       </c>
       <c r="Z287">
-        <v>-1635.231071942744</v>
+        <v>-1733.351704969682</v>
       </c>
       <c r="AA287">
-        <v>-0.1754713399349178</v>
+        <v>-0.185300714524936</v>
       </c>
       <c r="AB287">
-        <v>-0.1533678528885285</v>
+        <v>-0.1625705588972433</v>
       </c>
     </row>
     <row r="288" spans="1:28">
@@ -25406,13 +25406,13 @@
         <v>89</v>
       </c>
       <c r="I288">
-        <v>487.4457778673709</v>
+        <v>481.6348371747782</v>
       </c>
       <c r="J288">
-        <v>487.4457778673709</v>
+        <v>481.6348371747782</v>
       </c>
       <c r="K288">
-        <v>906.2122834015888</v>
+        <v>896.361954360713</v>
       </c>
       <c r="L288">
         <v>0.0322341001056427</v>
@@ -25445,7 +25445,7 @@
         <v>1231.9</v>
       </c>
       <c r="V288">
-        <v>57.97566772291625</v>
+        <v>57.28452794481565</v>
       </c>
       <c r="W288">
         <v>566.7801252914782</v>
@@ -25454,16 +25454,16 @@
         <v>1026.193467336683</v>
       </c>
       <c r="Y288">
-        <v>-79.33434742410731</v>
+        <v>-85.14528811669999</v>
       </c>
       <c r="Z288">
-        <v>-119.9811839350944</v>
+        <v>-129.8315129759702</v>
       </c>
       <c r="AA288">
-        <v>-0.1399737638706156</v>
+        <v>-0.1502263123162837</v>
       </c>
       <c r="AB288">
-        <v>-0.1169186783526169</v>
+        <v>-0.1265175789053955</v>
       </c>
     </row>
     <row r="289" spans="1:28">
@@ -29964,13 +29964,13 @@
         <v>72</v>
       </c>
       <c r="I341">
-        <v>14280.44049245187</v>
+        <v>14206.88934078263</v>
       </c>
       <c r="J341">
-        <v>14280.44049245187</v>
+        <v>14206.88934078263</v>
       </c>
       <c r="K341">
-        <v>48545.34973127543</v>
+        <v>48317.30942158023</v>
       </c>
       <c r="L341">
         <v>0.5</v>
@@ -30003,7 +30003,7 @@
         <v>5975.7</v>
       </c>
       <c r="V341">
-        <v>1370.806477586603</v>
+        <v>1363.746163502072</v>
       </c>
       <c r="W341">
         <v>14936.44449464824</v>
@@ -30012,16 +30012,16 @@
         <v>50442.99999999999</v>
       </c>
       <c r="Y341">
-        <v>-656.0040021963614</v>
+        <v>-729.5551538656109</v>
       </c>
       <c r="Z341">
-        <v>-1897.650268724559</v>
+        <v>-2125.690578419766</v>
       </c>
       <c r="AA341">
-        <v>-0.04391968934985895</v>
+        <v>-0.04884396377779279</v>
       </c>
       <c r="AB341">
-        <v>-0.03761969487787323</v>
+        <v>-0.04214044720614885</v>
       </c>
     </row>
     <row r="342" spans="1:28">
@@ -30050,13 +30050,13 @@
         <v>73</v>
       </c>
       <c r="I342">
-        <v>995.4444031127547</v>
+        <v>990.3173846352539</v>
       </c>
       <c r="J342">
-        <v>995.4444031127547</v>
+        <v>990.3173846352539</v>
       </c>
       <c r="K342">
-        <v>3383.943003207206</v>
+        <v>3368.047033465225</v>
       </c>
       <c r="L342">
         <v>0.03485342079044798</v>
@@ -30089,7 +30089,7 @@
         <v>620.8999999999999</v>
       </c>
       <c r="V342">
-        <v>74.95815591734004</v>
+        <v>74.57208528474031</v>
       </c>
       <c r="W342">
         <v>1018.328193320971</v>
@@ -30098,16 +30098,16 @@
         <v>3439.073406933948</v>
       </c>
       <c r="Y342">
-        <v>-22.88379020821583</v>
+        <v>-28.0108086857166</v>
       </c>
       <c r="Z342">
-        <v>-55.13040372674186</v>
+        <v>-71.02637346872325</v>
       </c>
       <c r="AA342">
-        <v>-0.02247192050490839</v>
+        <v>-0.02750666128015938</v>
       </c>
       <c r="AB342">
-        <v>-0.01603059813017847</v>
+        <v>-0.02065276458639064</v>
       </c>
     </row>
     <row r="343" spans="1:28">
@@ -30136,13 +30136,13 @@
         <v>74</v>
       </c>
       <c r="I343">
-        <v>670.5949335250551</v>
+        <v>667.1410463924836</v>
       </c>
       <c r="J343">
-        <v>670.5949335250551</v>
+        <v>667.1410463924836</v>
       </c>
       <c r="K343">
-        <v>2279.640154881931</v>
+        <v>2268.931614315419</v>
       </c>
       <c r="L343">
         <v>0.0234794904918902</v>
@@ -30175,7 +30175,7 @@
         <v>634</v>
       </c>
       <c r="V343">
-        <v>58.80995538380574</v>
+        <v>58.50705576734206</v>
       </c>
       <c r="W343">
         <v>671.1708546888193</v>
@@ -30184,16 +30184,16 @@
         <v>2266.662018206458</v>
       </c>
       <c r="Y343">
-        <v>-0.5759211637641783</v>
+        <v>-4.029808296335659</v>
       </c>
       <c r="Z343">
-        <v>12.97813667547325</v>
+        <v>2.269596108961196</v>
       </c>
       <c r="AA343">
-        <v>-0.0008580842862004155</v>
+        <v>-0.006004146735787617</v>
       </c>
       <c r="AB343">
-        <v>0.005725660275431122</v>
+        <v>0.001001294454458217</v>
       </c>
     </row>
     <row r="344" spans="1:28">
@@ -30222,13 +30222,13 @@
         <v>75</v>
       </c>
       <c r="I344">
-        <v>119.3554330892872</v>
+        <v>118.7406950798862</v>
       </c>
       <c r="J344">
-        <v>119.3554330892872</v>
+        <v>118.7406950798862</v>
       </c>
       <c r="K344">
-        <v>405.7403722742214</v>
+        <v>403.8344191672517</v>
       </c>
       <c r="L344">
         <v>0.004178982894553362</v>
@@ -30252,7 +30252,7 @@
         <v>106</v>
       </c>
       <c r="S344">
-        <v>97024.64023247798</v>
+        <v>97024.64023247795</v>
       </c>
       <c r="T344">
         <v>320</v>
@@ -30261,7 +30261,7 @@
         <v>235.8</v>
       </c>
       <c r="V344">
-        <v>6.933534916064877</v>
+        <v>6.897823869302343</v>
       </c>
       <c r="W344">
         <v>121.5050685212495</v>
@@ -30270,16 +30270,16 @@
         <v>410.3439860546098</v>
       </c>
       <c r="Y344">
-        <v>-2.149635431962366</v>
+        <v>-2.764373441363347</v>
       </c>
       <c r="Z344">
-        <v>-4.603613780388457</v>
+        <v>-6.509566887358176</v>
       </c>
       <c r="AA344">
-        <v>-0.01769173465867743</v>
+        <v>-0.02275109569507297</v>
       </c>
       <c r="AB344">
-        <v>-0.01121891373296694</v>
+        <v>-0.01586368293086636</v>
       </c>
     </row>
     <row r="345" spans="1:28">
@@ -30308,13 +30308,13 @@
         <v>76</v>
       </c>
       <c r="I345">
-        <v>983.759598645195</v>
+        <v>978.6927625427458</v>
       </c>
       <c r="J345">
-        <v>983.759598645195</v>
+        <v>978.6927625427458</v>
       </c>
       <c r="K345">
-        <v>3344.221334977219</v>
+        <v>3328.511956568391</v>
       </c>
       <c r="L345">
         <v>0.03444430160138179</v>
@@ -30338,7 +30338,7 @@
         <v>106</v>
       </c>
       <c r="S345">
-        <v>94745.98731600546</v>
+        <v>94745.98731600544</v>
       </c>
       <c r="T345">
         <v>3200</v>
@@ -30347,7 +30347,7 @@
         <v>114.8</v>
       </c>
       <c r="V345">
-        <v>68.20165094260831</v>
+        <v>67.85037956724533</v>
       </c>
       <c r="W345">
         <v>960.4686368822777</v>
@@ -30356,16 +30356,16 @@
         <v>3243.671508812697</v>
       </c>
       <c r="Y345">
-        <v>23.29096176291728</v>
+        <v>18.22412566046808</v>
       </c>
       <c r="Z345">
-        <v>100.5498261645221</v>
+        <v>84.84044775569419</v>
       </c>
       <c r="AA345">
-        <v>0.02424958074479219</v>
+        <v>0.01897420171846982</v>
       </c>
       <c r="AB345">
-        <v>0.03099876972478234</v>
+        <v>0.02615568423781264</v>
       </c>
     </row>
     <row r="346" spans="1:28">
@@ -30394,16 +30394,16 @@
         <v>77</v>
       </c>
       <c r="I346">
-        <v>38.25202055064243</v>
+        <v>38.0550042074377</v>
       </c>
       <c r="J346">
-        <v>38.25202055064243</v>
+        <v>38.0550042074377</v>
       </c>
       <c r="K346">
-        <v>130.0350445450469</v>
+        <v>129.424208862671</v>
       </c>
       <c r="L346">
-        <v>0.001339315148256843</v>
+        <v>0.001339315148256844</v>
       </c>
       <c r="M346">
         <v>0.001258957970172306</v>
@@ -30424,7 +30424,7 @@
         <v>106</v>
       </c>
       <c r="S346">
-        <v>73440.0561318762</v>
+        <v>73440.05613187619</v>
       </c>
       <c r="T346">
         <v>0</v>
@@ -30433,7 +30433,7 @@
         <v>25.5</v>
       </c>
       <c r="V346">
-        <v>4.383929702527078</v>
+        <v>4.361350351516979</v>
       </c>
       <c r="W346">
         <v>37.60871168514731</v>
@@ -30442,16 +30442,16 @@
         <v>127.0112337788032</v>
       </c>
       <c r="Y346">
-        <v>0.6433088654951149</v>
+        <v>0.446292522290392</v>
       </c>
       <c r="Z346">
-        <v>3.023810766243656</v>
+        <v>2.412975083867764</v>
       </c>
       <c r="AA346">
-        <v>0.01710531514295861</v>
+        <v>0.01186673252800215</v>
       </c>
       <c r="AB346">
-        <v>0.0238074277076135</v>
+        <v>0.01899812333191005</v>
       </c>
     </row>
     <row r="347" spans="1:28">
@@ -30480,13 +30480,13 @@
         <v>83</v>
       </c>
       <c r="I347">
-        <v>50.52521127093135</v>
+        <v>50.26498207987289</v>
       </c>
       <c r="J347">
-        <v>50.52521127093135</v>
+        <v>50.26498207987289</v>
       </c>
       <c r="K347">
-        <v>171.7568903207421</v>
+        <v>170.9500675317863</v>
       </c>
       <c r="L347">
         <v>0.001769035461393406</v>
@@ -30519,7 +30519,7 @@
         <v>351.3</v>
       </c>
       <c r="V347">
-        <v>7.181383200954112</v>
+        <v>7.144395616062206</v>
       </c>
       <c r="W347">
         <v>52.07360079482165</v>
@@ -30528,16 +30528,16 @@
         <v>175.8617083091199</v>
       </c>
       <c r="Y347">
-        <v>-1.5483895238903</v>
+        <v>-1.808618714948757</v>
       </c>
       <c r="Z347">
-        <v>-4.104817988377818</v>
+        <v>-4.911640777333673</v>
       </c>
       <c r="AA347">
-        <v>-0.02973463521355482</v>
+        <v>-0.03473196950744784</v>
       </c>
       <c r="AB347">
-        <v>-0.02334116976256478</v>
+        <v>-0.02792899503000542</v>
       </c>
     </row>
     <row r="348" spans="1:28">
@@ -30566,13 +30566,13 @@
         <v>84</v>
       </c>
       <c r="I348">
-        <v>313.161269992745</v>
+        <v>311.5483385094097</v>
       </c>
       <c r="J348">
-        <v>313.161269992745</v>
+        <v>311.5483385094097</v>
       </c>
       <c r="K348">
-        <v>1064.569638599291</v>
+        <v>1059.568854972803</v>
       </c>
       <c r="L348">
         <v>0.01096469223614883</v>
@@ -30596,7 +30596,7 @@
         <v>105</v>
       </c>
       <c r="S348">
-        <v>76974.26055925702</v>
+        <v>76974.260559257</v>
       </c>
       <c r="T348">
         <v>930</v>
@@ -30605,7 +30605,7 @@
         <v>147</v>
       </c>
       <c r="V348">
-        <v>27.419691538242</v>
+        <v>27.27846691060399</v>
       </c>
       <c r="W348">
         <v>329.7994717005421</v>
@@ -30614,16 +30614,16 @@
         <v>1113.79081929111</v>
       </c>
       <c r="Y348">
-        <v>-16.63820170779718</v>
+        <v>-18.2511331911324</v>
       </c>
       <c r="Z348">
-        <v>-49.22118069181874</v>
+        <v>-54.22196431830639</v>
       </c>
       <c r="AA348">
-        <v>-0.05044944924261329</v>
+        <v>-0.055340092259773</v>
       </c>
       <c r="AB348">
-        <v>-0.04419248196276781</v>
+        <v>-0.0486823588228325</v>
       </c>
     </row>
     <row r="349" spans="1:28">
@@ -30652,13 +30652,13 @@
         <v>85</v>
       </c>
       <c r="I349">
-        <v>1055.926779993837</v>
+        <v>1050.488248123059</v>
       </c>
       <c r="J349">
-        <v>1055.926779993837</v>
+        <v>1050.488248123059</v>
       </c>
       <c r="K349">
-        <v>3589.548575375858</v>
+        <v>3572.686779687376</v>
       </c>
       <c r="L349">
         <v>0.03697108575018963</v>
@@ -30682,7 +30682,7 @@
         <v>105</v>
       </c>
       <c r="S349">
-        <v>47337.24937792137</v>
+        <v>47337.24937792136</v>
       </c>
       <c r="T349">
         <v>4100</v>
@@ -30691,7 +30691,7 @@
         <v>1435.9</v>
       </c>
       <c r="V349">
-        <v>104.0487708019225</v>
+        <v>103.5128694810707</v>
       </c>
       <c r="W349">
         <v>1160.084106595766</v>
@@ -30700,16 +30700,16 @@
         <v>3917.808057331007</v>
       </c>
       <c r="Y349">
-        <v>-104.1573266019286</v>
+        <v>-109.5958584727068</v>
       </c>
       <c r="Z349">
-        <v>-328.2594819551491</v>
+        <v>-345.1212776436305</v>
       </c>
       <c r="AA349">
-        <v>-0.0897842889233052</v>
+        <v>-0.09447233855682481</v>
       </c>
       <c r="AB349">
-        <v>-0.08378651458968482</v>
+        <v>-0.08809039968097446</v>
       </c>
     </row>
     <row r="350" spans="1:28">
@@ -30738,13 +30738,13 @@
         <v>86</v>
       </c>
       <c r="I350">
-        <v>32.40407621542192</v>
+        <v>32.2371796042367</v>
       </c>
       <c r="J350">
-        <v>32.40407621542192</v>
+        <v>32.2371796042367</v>
       </c>
       <c r="K350">
-        <v>110.1553704472931</v>
+        <v>109.6379189317423</v>
       </c>
       <c r="L350">
         <v>0.001134561508538534</v>
@@ -30777,7 +30777,7 @@
         <v>81</v>
       </c>
       <c r="V350">
-        <v>3.061266822310678</v>
+        <v>3.045499822653571</v>
       </c>
       <c r="W350">
         <v>34.71573386321394</v>
@@ -30786,16 +30786,16 @@
         <v>117.241138872745</v>
       </c>
       <c r="Y350">
-        <v>-2.311657647792025</v>
+        <v>-2.47855425897724</v>
       </c>
       <c r="Z350">
-        <v>-7.085768425451874</v>
+        <v>-7.603219941002621</v>
       </c>
       <c r="AA350">
-        <v>-0.06658818323992112</v>
+        <v>-0.07139570399816918</v>
       </c>
       <c r="AB350">
-        <v>-0.06043756051485356</v>
+        <v>-0.0648511266105599</v>
       </c>
     </row>
     <row r="351" spans="1:28">
@@ -30824,13 +30824,13 @@
         <v>87</v>
       </c>
       <c r="I351">
-        <v>505.5762612122205</v>
+        <v>502.9722997806072</v>
       </c>
       <c r="J351">
-        <v>505.5762612122205</v>
+        <v>502.9722997806072</v>
       </c>
       <c r="K351">
-        <v>1718.67082316898</v>
+        <v>1710.597419043785</v>
       </c>
       <c r="L351">
         <v>0.0177017040013384</v>
@@ -30854,7 +30854,7 @@
         <v>105</v>
       </c>
       <c r="S351">
-        <v>59723.2127390714</v>
+        <v>59723.21273907142</v>
       </c>
       <c r="T351">
         <v>1590</v>
@@ -30863,7 +30863,7 @@
         <v>262.7</v>
       </c>
       <c r="V351">
-        <v>48.02454120580856</v>
+        <v>47.77719167090159</v>
       </c>
       <c r="W351">
         <v>494.6992075508132</v>
@@ -30872,16 +30872,16 @@
         <v>1670.686228936665</v>
       </c>
       <c r="Y351">
-        <v>10.87705366140733</v>
+        <v>8.273092229794031</v>
       </c>
       <c r="Z351">
-        <v>47.98459423231543</v>
+        <v>39.91119010712009</v>
       </c>
       <c r="AA351">
-        <v>0.02198720655983685</v>
+        <v>0.01672347985102494</v>
       </c>
       <c r="AB351">
-        <v>0.02872148785403948</v>
+        <v>0.02388909982966833</v>
       </c>
     </row>
     <row r="352" spans="1:28">
@@ -30910,13 +30910,13 @@
         <v>88</v>
       </c>
       <c r="I352">
-        <v>8818.534066147409</v>
+        <v>8773.114365197534</v>
       </c>
       <c r="J352">
-        <v>8818.534066147409</v>
+        <v>8773.114365197534</v>
       </c>
       <c r="K352">
-        <v>29977.98426348051</v>
+        <v>29837.16359057727</v>
       </c>
       <c r="L352">
         <v>0.3087626768518999</v>
@@ -30949,7 +30949,7 @@
         <v>640.7</v>
       </c>
       <c r="V352">
-        <v>879.3815547419966</v>
+        <v>874.8523158755797</v>
       </c>
       <c r="W352">
         <v>9324.06752009517</v>
@@ -30958,16 +30958,16 @@
         <v>31489.01588223907</v>
       </c>
       <c r="Y352">
-        <v>-505.5334539477608</v>
+        <v>-550.9531548976356</v>
       </c>
       <c r="Z352">
-        <v>-1511.031618758556</v>
+        <v>-1651.852291661795</v>
       </c>
       <c r="AA352">
-        <v>-0.05421812453183531</v>
+        <v>-0.05908935705476445</v>
       </c>
       <c r="AB352">
-        <v>-0.04798599055649852</v>
+        <v>-0.05245804752486719</v>
       </c>
     </row>
     <row r="353" spans="1:28">
@@ -30996,13 +30996,13 @@
         <v>89</v>
       </c>
       <c r="I353">
-        <v>696.906438696376</v>
+        <v>693.317034630099</v>
       </c>
       <c r="J353">
-        <v>696.906438696376</v>
+        <v>693.317034630099</v>
       </c>
       <c r="K353">
-        <v>2369.084259997118</v>
+        <v>2357.955558456511</v>
       </c>
       <c r="L353">
         <v>0.02440073326396114</v>
@@ -31026,7 +31026,7 @@
         <v>105</v>
       </c>
       <c r="S353">
-        <v>41690.4224057699</v>
+        <v>41690.42240576991</v>
       </c>
       <c r="T353">
         <v>1970</v>
@@ -31035,7 +31035,7 @@
         <v>1426.1</v>
       </c>
       <c r="V353">
-        <v>88.40204241302293</v>
+        <v>87.94672928505405</v>
       </c>
       <c r="W353">
         <v>731.9233889494469</v>
@@ -31044,16 +31044,16 @@
         <v>2471.834011233773</v>
       </c>
       <c r="Y353">
-        <v>-35.01695025307095</v>
+        <v>-38.60635431934793</v>
       </c>
       <c r="Z353">
-        <v>-102.7497512366549</v>
+        <v>-113.8784527772618</v>
       </c>
       <c r="AA353">
-        <v>-0.04784237091170415</v>
+        <v>-0.0527464416388727</v>
       </c>
       <c r="AB353">
-        <v>-0.04156822455297844</v>
+        <v>-0.04607042878272453</v>
       </c>
     </row>
     <row r="354" spans="1:28">
@@ -35812,16 +35812,16 @@
         <v>72</v>
       </c>
       <c r="I409">
-        <v>5873.196339146475</v>
+        <v>5870.490278329624</v>
       </c>
       <c r="J409">
-        <v>5873.196339146475</v>
+        <v>5870.490278329624</v>
       </c>
       <c r="K409">
-        <v>17902.45038639405</v>
+        <v>17913.86604760865</v>
       </c>
       <c r="L409">
-        <v>0.4999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="M409">
         <v>0.4999999999999999</v>
@@ -35851,7 +35851,7 @@
         <v>5486.5</v>
       </c>
       <c r="V409">
-        <v>525.6521124145232</v>
+        <v>525.4099194922095</v>
       </c>
       <c r="W409">
         <v>5987.024880706002</v>
@@ -35860,16 +35860,16 @@
         <v>18283</v>
       </c>
       <c r="Y409">
-        <v>-113.8285415595274</v>
+        <v>-116.5346023763786</v>
       </c>
       <c r="Z409">
-        <v>-380.5496136059519</v>
+        <v>-369.1339523913484</v>
       </c>
       <c r="AA409">
-        <v>-0.01901253858596032</v>
+        <v>-0.0194645261542051</v>
       </c>
       <c r="AB409">
-        <v>-0.02081439663107542</v>
+        <v>-0.02019000997600768</v>
       </c>
     </row>
     <row r="410" spans="1:28">
@@ -35898,13 +35898,13 @@
         <v>73</v>
       </c>
       <c r="I410">
-        <v>654.0994969091066</v>
+        <v>653.7981221692378</v>
       </c>
       <c r="J410">
-        <v>654.0994969091066</v>
+        <v>653.7981221692378</v>
       </c>
       <c r="K410">
-        <v>1993.800839439049</v>
+        <v>1995.072204778495</v>
       </c>
       <c r="L410">
         <v>0.05568513796732392</v>
@@ -35937,7 +35937,7 @@
         <v>748.7</v>
       </c>
       <c r="V410">
-        <v>49.13430180704425</v>
+        <v>49.1116632979249</v>
       </c>
       <c r="W410">
         <v>666.8808050070775</v>
@@ -35946,16 +35946,16 @@
         <v>2036.500933416301</v>
       </c>
       <c r="Y410">
-        <v>-12.78130809797085</v>
+        <v>-13.08268283783968</v>
       </c>
       <c r="Z410">
-        <v>-42.70009397725289</v>
+        <v>-41.42872863780667</v>
       </c>
       <c r="AA410">
-        <v>-0.01916580594613936</v>
+        <v>-0.01961772289682388</v>
       </c>
       <c r="AB410">
-        <v>-0.02096738247284866</v>
+        <v>-0.02034309337060235</v>
       </c>
     </row>
     <row r="411" spans="1:28">
@@ -35984,16 +35984,16 @@
         <v>74</v>
       </c>
       <c r="I411">
-        <v>540.8601311073056</v>
+        <v>540.610931127657</v>
       </c>
       <c r="J411">
-        <v>540.8601311073056</v>
+        <v>540.610931127657</v>
       </c>
       <c r="K411">
-        <v>1648.628975433548</v>
+        <v>1649.680238777164</v>
       </c>
       <c r="L411">
-        <v>0.04604478548608391</v>
+        <v>0.04604478548608389</v>
       </c>
       <c r="M411">
         <v>0.04573739887990032</v>
@@ -36014,7 +36014,7 @@
         <v>106</v>
       </c>
       <c r="S411">
-        <v>81901.46197157679</v>
+        <v>81901.46197157681</v>
       </c>
       <c r="T411">
         <v>1110</v>
@@ -36023,7 +36023,7 @@
         <v>742.2</v>
       </c>
       <c r="V411">
-        <v>46.8877435069452</v>
+        <v>46.86614009405586</v>
       </c>
       <c r="W411">
         <v>547.6618901454763</v>
@@ -36032,16 +36032,16 @@
         <v>1672.433727442435</v>
       </c>
       <c r="Y411">
-        <v>-6.801759038170644</v>
+        <v>-7.050959017819309</v>
       </c>
       <c r="Z411">
-        <v>-23.80475200888736</v>
+        <v>-22.75348866527111</v>
       </c>
       <c r="AA411">
-        <v>-0.01241963182131202</v>
+        <v>-0.01287465705518847</v>
       </c>
       <c r="AB411">
-        <v>-0.01423359958501358</v>
+        <v>-0.01360501662452528</v>
       </c>
     </row>
     <row r="412" spans="1:28">
@@ -36070,13 +36070,13 @@
         <v>75</v>
       </c>
       <c r="I412">
-        <v>289.420236352409</v>
+        <v>289.2868866879381</v>
       </c>
       <c r="J412">
-        <v>289.420236352409</v>
+        <v>289.2868866879381</v>
       </c>
       <c r="K412">
-        <v>882.1995933598265</v>
+        <v>882.7621359986322</v>
       </c>
       <c r="L412">
         <v>0.02463907382282993</v>
@@ -36109,7 +36109,7 @@
         <v>193.7</v>
       </c>
       <c r="V412">
-        <v>18.03586538718188</v>
+        <v>18.02755540641434</v>
       </c>
       <c r="W412">
         <v>298.047287154001</v>
@@ -36118,16 +36118,16 @@
         <v>910.1680149346594</v>
       </c>
       <c r="Y412">
-        <v>-8.627050801591963</v>
+        <v>-8.76040046606289</v>
       </c>
       <c r="Z412">
-        <v>-27.96842157483286</v>
+        <v>-27.40587893602719</v>
       </c>
       <c r="AA412">
-        <v>-0.02894524182377264</v>
+        <v>-0.02939265292334767</v>
       </c>
       <c r="AB412">
-        <v>-0.03072885567928983</v>
+        <v>-0.03011079106970668</v>
       </c>
     </row>
     <row r="413" spans="1:28">
@@ -36156,16 +36156,16 @@
         <v>76</v>
       </c>
       <c r="I413">
-        <v>1006.852556723374</v>
+        <v>1006.388651875866</v>
       </c>
       <c r="J413">
-        <v>1006.852556723374</v>
+        <v>1006.388651875866</v>
       </c>
       <c r="K413">
-        <v>3069.049100744641</v>
+        <v>3071.006107971522</v>
       </c>
       <c r="L413">
-        <v>0.08571589459834873</v>
+        <v>0.08571589459834875</v>
       </c>
       <c r="M413">
         <v>0.08494088363410092</v>
@@ -36186,7 +36186,7 @@
         <v>106</v>
       </c>
       <c r="S413">
-        <v>99439.04289462327</v>
+        <v>99439.04289462326</v>
       </c>
       <c r="T413">
         <v>1580</v>
@@ -36195,7 +36195,7 @@
         <v>97.30000000000001</v>
       </c>
       <c r="V413">
-        <v>67.1032570158977</v>
+        <v>67.07233935471146</v>
       </c>
       <c r="W413">
         <v>1017.086367413031</v>
@@ -36204,16 +36204,16 @@
         <v>3105.948350964534</v>
       </c>
       <c r="Y413">
-        <v>-10.23381068965716</v>
+        <v>-10.6977155371651</v>
       </c>
       <c r="Z413">
-        <v>-36.89925021989302</v>
+        <v>-34.94224299301186</v>
       </c>
       <c r="AA413">
-        <v>-0.01006188954797119</v>
+        <v>-0.01051800110582038</v>
       </c>
       <c r="AB413">
-        <v>-0.0118801879652745</v>
+        <v>-0.01125010433034431</v>
       </c>
     </row>
     <row r="414" spans="1:28">
@@ -36242,13 +36242,13 @@
         <v>77</v>
       </c>
       <c r="I414">
-        <v>25.42402444752165</v>
+        <v>25.41231039057696</v>
       </c>
       <c r="J414">
-        <v>25.42402444752165</v>
+        <v>25.41231039057696</v>
       </c>
       <c r="K414">
-        <v>77.49653000028448</v>
+        <v>77.5459463713787</v>
       </c>
       <c r="L414">
         <v>0.002164411248953445</v>
@@ -36281,7 +36281,7 @@
         <v>6.3</v>
       </c>
       <c r="V414">
-        <v>1.801702519903109</v>
+        <v>1.800872389883406</v>
       </c>
       <c r="W414">
         <v>26.07913762597517</v>
@@ -36290,16 +36290,16 @@
         <v>79.63970130678295</v>
       </c>
       <c r="Y414">
-        <v>-0.6551131784535151</v>
+        <v>-0.666827235398209</v>
       </c>
       <c r="Z414">
-        <v>-2.143171306498473</v>
+        <v>-2.093754935404249</v>
       </c>
       <c r="AA414">
-        <v>-0.02512020097631655</v>
+        <v>-0.02556937445408625</v>
       </c>
       <c r="AB414">
-        <v>-0.02691084058995508</v>
+        <v>-0.02629034138813279</v>
       </c>
     </row>
     <row r="415" spans="1:28">
@@ -36328,13 +36328,13 @@
         <v>79</v>
       </c>
       <c r="I415">
-        <v>13.89618024923817</v>
+        <v>13.88977761825073</v>
       </c>
       <c r="J415">
-        <v>13.89618024923817</v>
+        <v>13.88977761825073</v>
       </c>
       <c r="K415">
-        <v>42.3578002686913</v>
+        <v>42.38481010741317</v>
       </c>
       <c r="L415">
         <v>0.001183016831619973</v>
@@ -36367,7 +36367,7 @@
         <v>4.5</v>
       </c>
       <c r="V415">
-        <v>1.103844856514948</v>
+        <v>1.103336262703059</v>
       </c>
       <c r="W415">
         <v>14.90236435769993</v>
@@ -36376,16 +36376,16 @@
         <v>45.5084007467326</v>
       </c>
       <c r="Y415">
-        <v>-1.006184108461751</v>
+        <v>-1.012586739449198</v>
       </c>
       <c r="Z415">
-        <v>-3.150600478041298</v>
+        <v>-3.123590639319424</v>
       </c>
       <c r="AA415">
-        <v>-0.06751842085661153</v>
+        <v>-0.06794805945849812</v>
       </c>
       <c r="AB415">
-        <v>-0.06923118427244455</v>
+        <v>-0.06863767102480944</v>
       </c>
     </row>
     <row r="416" spans="1:28">
@@ -36414,13 +36414,13 @@
         <v>83</v>
       </c>
       <c r="I416">
-        <v>14.44483791244975</v>
+        <v>14.43818248878886</v>
       </c>
       <c r="J416">
-        <v>14.44483791244975</v>
+        <v>14.43818248878886</v>
       </c>
       <c r="K416">
-        <v>44.03019738051468</v>
+        <v>44.05827363854971</v>
       </c>
       <c r="L416">
         <v>0.001229725440657493</v>
@@ -36453,7 +36453,7 @@
         <v>351.3</v>
       </c>
       <c r="V416">
-        <v>2.053111975499109</v>
+        <v>2.052166009188997</v>
       </c>
       <c r="W416">
         <v>14.90236435769993</v>
@@ -36462,16 +36462,16 @@
         <v>45.5084007467326</v>
       </c>
       <c r="Y416">
-        <v>-0.4575264452501706</v>
+        <v>-0.4641818689110693</v>
       </c>
       <c r="Z416">
-        <v>-1.478203366217919</v>
+        <v>-1.45012710818289</v>
       </c>
       <c r="AA416">
-        <v>-0.03070160105257194</v>
+        <v>-0.03114820291393764</v>
       </c>
       <c r="AB416">
-        <v>-0.03248198886277168</v>
+        <v>-0.03186504215459618</v>
       </c>
     </row>
     <row r="417" spans="1:28">
@@ -36500,13 +36500,13 @@
         <v>84</v>
       </c>
       <c r="I417">
-        <v>290.3718026635004</v>
+        <v>290.2380145671841</v>
       </c>
       <c r="J417">
-        <v>290.3718026635004</v>
+        <v>290.2380145671841</v>
       </c>
       <c r="K417">
-        <v>885.1001210605832</v>
+        <v>885.664513247404</v>
       </c>
       <c r="L417">
         <v>0.02472008306006153</v>
@@ -36530,7 +36530,7 @@
         <v>105</v>
       </c>
       <c r="S417">
-        <v>84339.50960210565</v>
+        <v>84339.50960210567</v>
       </c>
       <c r="T417">
         <v>540</v>
@@ -36539,7 +36539,7 @@
         <v>147</v>
       </c>
       <c r="V417">
-        <v>25.45494587775496</v>
+        <v>25.44321757383709</v>
       </c>
       <c r="W417">
         <v>305.4984693328521</v>
@@ -36548,16 +36548,16 @@
         <v>932.9222153080294</v>
       </c>
       <c r="Y417">
-        <v>-15.12666666935166</v>
+        <v>-15.26045476566799</v>
       </c>
       <c r="Z417">
-        <v>-47.82209424744622</v>
+        <v>-47.25770206062543</v>
       </c>
       <c r="AA417">
-        <v>-0.04951470526967057</v>
+        <v>-0.04995263903938303</v>
       </c>
       <c r="AB417">
-        <v>-0.05126053754830617</v>
+        <v>-0.05065556515343782</v>
       </c>
     </row>
     <row r="418" spans="1:28">
@@ -36586,13 +36586,13 @@
         <v>85</v>
       </c>
       <c r="I418">
-        <v>441.1910515464913</v>
+        <v>440.987773850941</v>
       </c>
       <c r="J418">
-        <v>441.1910515464913</v>
+        <v>440.987773850941</v>
       </c>
       <c r="K418">
-        <v>1344.821534159697</v>
+        <v>1345.679071909933</v>
       </c>
       <c r="L418">
         <v>0.03755970565855521</v>
@@ -36616,7 +36616,7 @@
         <v>105</v>
       </c>
       <c r="S418">
-        <v>46690.97929496437</v>
+        <v>46690.97929496438</v>
       </c>
       <c r="T418">
         <v>1620</v>
@@ -36625,7 +36625,7 @@
         <v>1302.8</v>
       </c>
       <c r="V418">
-        <v>45.81760858586973</v>
+        <v>45.79649823502216</v>
       </c>
       <c r="W418">
         <v>476.8756594464006</v>
@@ -36634,16 +36634,16 @@
         <v>1456.268823895452</v>
       </c>
       <c r="Y418">
-        <v>-35.68460789990934</v>
+        <v>-35.88788559545958</v>
       </c>
       <c r="Z418">
-        <v>-111.4472897357552</v>
+        <v>-110.5897519855193</v>
       </c>
       <c r="AA418">
-        <v>-0.07483000483047338</v>
+        <v>-0.07525627463796623</v>
       </c>
       <c r="AB418">
-        <v>-0.07652933847587209</v>
+        <v>-0.07594047896300961</v>
       </c>
     </row>
     <row r="419" spans="1:28">
@@ -36672,13 +36672,13 @@
         <v>86</v>
       </c>
       <c r="I419">
-        <v>54.31310613128363</v>
+        <v>54.2880815007662</v>
       </c>
       <c r="J419">
-        <v>54.31310613128363</v>
+        <v>54.2880815007662</v>
       </c>
       <c r="K419">
-        <v>165.5551137232311</v>
+        <v>165.6606814555704</v>
       </c>
       <c r="L419">
         <v>0.004623811549536644</v>
@@ -36711,7 +36711,7 @@
         <v>81</v>
       </c>
       <c r="V419">
-        <v>5.13104921464191</v>
+        <v>5.128685096293517</v>
       </c>
       <c r="W419">
         <v>55.88386634137503</v>
@@ -36720,16 +36720,16 @@
         <v>170.6565028002482</v>
       </c>
       <c r="Y419">
-        <v>-1.5707602100914</v>
+        <v>-1.595784840608822</v>
       </c>
       <c r="Z419">
-        <v>-5.101389077017046</v>
+        <v>-4.995821344677751</v>
       </c>
       <c r="AA419">
-        <v>-0.02810757939502923</v>
+        <v>-0.02855537644551523</v>
       </c>
       <c r="AB419">
-        <v>-0.02989273185205356</v>
+        <v>-0.0292741340804652</v>
       </c>
     </row>
     <row r="420" spans="1:28">
@@ -36758,13 +36758,13 @@
         <v>87</v>
       </c>
       <c r="I420">
-        <v>195.742375181963</v>
+        <v>195.6521873624027</v>
       </c>
       <c r="J420">
-        <v>195.742375181963</v>
+        <v>195.6521873624027</v>
       </c>
       <c r="K420">
-        <v>596.6543527334696</v>
+        <v>597.0348148381543</v>
       </c>
       <c r="L420">
         <v>0.01666404150984074</v>
@@ -36788,7 +36788,7 @@
         <v>105</v>
       </c>
       <c r="S420">
-        <v>63058.68969148883</v>
+        <v>63058.68969148882</v>
       </c>
       <c r="T420">
         <v>500</v>
@@ -36797,7 +36797,7 @@
         <v>257.9</v>
       </c>
       <c r="V420">
-        <v>18.51083917600656</v>
+        <v>18.50231035223008</v>
       </c>
       <c r="W420">
         <v>182.5539633818262</v>
@@ -36806,16 +36806,16 @@
         <v>557.4779091474808</v>
       </c>
       <c r="Y420">
-        <v>13.18841180013683</v>
+        <v>13.09822398057648</v>
       </c>
       <c r="Z420">
-        <v>39.17644358598886</v>
+        <v>39.55690569067349</v>
       </c>
       <c r="AA420">
-        <v>0.07224390835356566</v>
+        <v>0.07174987460108163</v>
       </c>
       <c r="AB420">
-        <v>0.07027443230154029</v>
+        <v>0.07095690258142356</v>
       </c>
     </row>
     <row r="421" spans="1:28">
@@ -36844,13 +36844,13 @@
         <v>88</v>
       </c>
       <c r="I421">
-        <v>2177.849940555872</v>
+        <v>2176.846501534118</v>
       </c>
       <c r="J421">
-        <v>2177.849940555872</v>
+        <v>2176.846501534118</v>
       </c>
       <c r="K421">
-        <v>6638.438127794447</v>
+        <v>6642.671188578046</v>
       </c>
       <c r="L421">
         <v>0.1854058518391341</v>
@@ -36874,7 +36874,7 @@
         <v>105</v>
       </c>
       <c r="S421">
-        <v>47443.47453207245</v>
+        <v>47443.47453207244</v>
       </c>
       <c r="T421">
         <v>6550</v>
@@ -36883,7 +36883,7 @@
         <v>546.8000000000001</v>
       </c>
       <c r="V421">
-        <v>223.3632803878394</v>
+        <v>223.2603663039099</v>
       </c>
       <c r="W421">
         <v>2213.001107118464</v>
@@ -36892,16 +36892,16 @@
         <v>6757.997510889867</v>
       </c>
       <c r="Y421">
-        <v>-35.15116656259124</v>
+        <v>-36.15460558434552</v>
       </c>
       <c r="Z421">
-        <v>-119.5593830954203</v>
+        <v>-115.3263223118211</v>
       </c>
       <c r="AA421">
-        <v>-0.01588393537152875</v>
+        <v>-0.01633736443603602</v>
       </c>
       <c r="AB421">
-        <v>-0.01769153997212367</v>
+        <v>-0.01706516199894772</v>
       </c>
     </row>
     <row r="422" spans="1:28">
@@ -36930,13 +36930,13 @@
         <v>89</v>
       </c>
       <c r="I422">
-        <v>168.7305993659603</v>
+        <v>168.6528571558957</v>
       </c>
       <c r="J422">
-        <v>168.7305993659603</v>
+        <v>168.6528571558957</v>
       </c>
       <c r="K422">
-        <v>514.3181002960678</v>
+        <v>514.6460599363847</v>
       </c>
       <c r="L422">
         <v>0.01436446098705438</v>
@@ -36969,7 +36969,7 @@
         <v>1007</v>
       </c>
       <c r="V422">
-        <v>21.25456210342448</v>
+        <v>21.24476911603462</v>
       </c>
       <c r="W422">
         <v>167.6515990241251</v>
@@ -36978,16 +36978,16 @@
         <v>511.9695084007445</v>
       </c>
       <c r="Y422">
-        <v>1.079000341835211</v>
+        <v>1.001258131770669</v>
       </c>
       <c r="Z422">
-        <v>2.348591895323239</v>
+        <v>2.676551535640215</v>
       </c>
       <c r="AA422">
-        <v>0.006435968091660989</v>
+        <v>0.005972255186343841</v>
       </c>
       <c r="AB422">
-        <v>0.004587366741155367</v>
+        <v>0.005227951062947174</v>
       </c>
     </row>
     <row r="423" spans="1:28">
@@ -42606,13 +42606,13 @@
         <v>72</v>
       </c>
       <c r="I488">
-        <v>1035.358805508031</v>
+        <v>1047.992311069022</v>
       </c>
       <c r="J488">
-        <v>1035.358805508031</v>
+        <v>1047.992311069022</v>
       </c>
       <c r="K488">
-        <v>123162.8839330377</v>
+        <v>124658.8870158994</v>
       </c>
       <c r="L488">
         <v>0.5</v>
@@ -42645,7 +42645,7 @@
         <v>8545.199999999999</v>
       </c>
       <c r="V488">
-        <v>80.19385058958056</v>
+        <v>81.17238040165245</v>
       </c>
       <c r="W488">
         <v>1032.025505425746</v>
@@ -42654,16 +42654,16 @@
         <v>120207</v>
       </c>
       <c r="Y488">
-        <v>3.333300082285177</v>
+        <v>15.96680564327585</v>
       </c>
       <c r="Z488">
-        <v>2955.88393303768</v>
+        <v>4451.887015899425</v>
       </c>
       <c r="AA488">
-        <v>0.003229862115578312</v>
+        <v>0.01547132852757257</v>
       </c>
       <c r="AB488">
-        <v>0.02458994844757526</v>
+        <v>0.03703517279276102</v>
       </c>
     </row>
     <row r="489" spans="1:28">
@@ -42692,16 +42692,16 @@
         <v>73</v>
       </c>
       <c r="I489">
-        <v>124.3821307987305</v>
+        <v>125.8998484563908</v>
       </c>
       <c r="J489">
-        <v>124.3821307987305</v>
+        <v>125.8998484563908</v>
       </c>
       <c r="K489">
-        <v>14796.08987474741</v>
+        <v>14975.81119467815</v>
       </c>
       <c r="L489">
-        <v>0.06006716229051554</v>
+        <v>0.06006716229051555</v>
       </c>
       <c r="M489">
         <v>0.05991064175467111</v>
@@ -42731,7 +42731,7 @@
         <v>879.3</v>
       </c>
       <c r="V489">
-        <v>9.274323984964688</v>
+        <v>9.387489800540081</v>
       </c>
       <c r="W489">
         <v>123.6586206744905</v>
@@ -42740,16 +42740,16 @@
         <v>14403.3570268075</v>
       </c>
       <c r="Y489">
-        <v>0.7235101242399367</v>
+        <v>2.241227781900278</v>
       </c>
       <c r="Z489">
-        <v>392.7328479399075</v>
+        <v>572.4541678706446</v>
       </c>
       <c r="AA489">
-        <v>0.005850866848534962</v>
+        <v>0.01812431490562971</v>
       </c>
       <c r="AB489">
-        <v>0.02726675782659236</v>
+        <v>0.03974449614802952</v>
       </c>
     </row>
     <row r="490" spans="1:28">
@@ -42778,16 +42778,16 @@
         <v>74</v>
       </c>
       <c r="I490">
-        <v>102.4763439700166</v>
+        <v>103.726766002</v>
       </c>
       <c r="J490">
-        <v>102.4763439700166</v>
+        <v>103.726766002</v>
       </c>
       <c r="K490">
-        <v>12190.24940061062</v>
+        <v>12338.31877103947</v>
       </c>
       <c r="L490">
-        <v>0.04948832396307933</v>
+        <v>0.04948832396307935</v>
       </c>
       <c r="M490">
         <v>0.04939073923639327</v>
@@ -42808,7 +42808,7 @@
         <v>106</v>
       </c>
       <c r="S490">
-        <v>86917.79605913746</v>
+        <v>86917.79605913744</v>
       </c>
       <c r="T490">
         <v>11950</v>
@@ -42817,7 +42817,7 @@
         <v>787.1000000000001</v>
       </c>
       <c r="V490">
-        <v>8.359368693394604</v>
+        <v>8.461370173763097</v>
       </c>
       <c r="W490">
         <v>101.94500524758</v>
@@ -42826,16 +42826,16 @@
         <v>11874.22518277825</v>
       </c>
       <c r="Y490">
-        <v>0.5313387224366011</v>
+        <v>1.781760754419977</v>
       </c>
       <c r="Z490">
-        <v>316.0242178323697</v>
+        <v>464.0935882612212</v>
       </c>
       <c r="AA490">
-        <v>0.005212013292325709</v>
+        <v>0.01747766602289987</v>
       </c>
       <c r="AB490">
-        <v>0.02661430223596522</v>
+        <v>0.03908411547848344</v>
       </c>
     </row>
     <row r="491" spans="1:28">
@@ -42864,16 +42864,16 @@
         <v>75</v>
       </c>
       <c r="I491">
-        <v>102.4227815613948</v>
+        <v>103.6725500218978</v>
       </c>
       <c r="J491">
-        <v>102.4227815613948</v>
+        <v>103.6725500218978</v>
       </c>
       <c r="K491">
-        <v>12183.87779235156</v>
+        <v>12331.86976977617</v>
       </c>
       <c r="L491">
-        <v>0.04946245737058169</v>
+        <v>0.04946245737058171</v>
       </c>
       <c r="M491">
         <v>0.0471161657189277</v>
@@ -42903,7 +42903,7 @@
         <v>335.8</v>
       </c>
       <c r="V491">
-        <v>6.519988332547168</v>
+        <v>6.599545591749123</v>
       </c>
       <c r="W491">
         <v>97.25016947959914</v>
@@ -42912,16 +42912,16 @@
         <v>11327.38586515028</v>
       </c>
       <c r="Y491">
-        <v>5.17261208179562</v>
+        <v>6.422380542298669</v>
       </c>
       <c r="Z491">
-        <v>856.4919272012776</v>
+        <v>1004.483904625891</v>
       </c>
       <c r="AA491">
-        <v>0.05318872048732744</v>
+        <v>0.06603978765965994</v>
       </c>
       <c r="AB491">
-        <v>0.07561249677530203</v>
+        <v>0.0886774686219771</v>
       </c>
     </row>
     <row r="492" spans="1:28">
@@ -42950,13 +42950,13 @@
         <v>76</v>
       </c>
       <c r="I492">
-        <v>414.586268996416</v>
+        <v>419.6450736417357</v>
       </c>
       <c r="J492">
-        <v>414.586268996416</v>
+        <v>419.6450736417357</v>
       </c>
       <c r="K492">
-        <v>49317.8212779885</v>
+        <v>49916.86224159575</v>
       </c>
       <c r="L492">
         <v>0.2002138132166589</v>
@@ -42980,7 +42980,7 @@
         <v>106</v>
       </c>
       <c r="S492">
-        <v>98014.18628124002</v>
+        <v>98014.18628124001</v>
       </c>
       <c r="T492">
         <v>51120</v>
@@ -42989,7 +42989,7 @@
         <v>177.1</v>
       </c>
       <c r="V492">
-        <v>27.61209793003626</v>
+        <v>27.94902228021704</v>
       </c>
       <c r="W492">
         <v>412.9778748763001</v>
@@ -42998,16 +42998,16 @@
         <v>48102.32997562984</v>
       </c>
       <c r="Y492">
-        <v>1.608394120115975</v>
+        <v>6.667198765435614</v>
       </c>
       <c r="Z492">
-        <v>1215.491302358656</v>
+        <v>1814.532265965907</v>
       </c>
       <c r="AA492">
-        <v>0.00389462539754155</v>
+        <v>0.01614420328796706</v>
       </c>
       <c r="AB492">
-        <v>0.02526886541617552</v>
+        <v>0.03772233625450588</v>
       </c>
     </row>
     <row r="493" spans="1:28">
@@ -43036,13 +43036,13 @@
         <v>77</v>
       </c>
       <c r="I493">
-        <v>48.20378068192074</v>
+        <v>48.79196588695892</v>
       </c>
       <c r="J493">
-        <v>48.20378068192074</v>
+        <v>48.79196588695892</v>
       </c>
       <c r="K493">
-        <v>5734.163474224642</v>
+        <v>5803.813728920994</v>
       </c>
       <c r="L493">
         <v>0.02327878046986235</v>
@@ -43075,7 +43075,7 @@
         <v>95.29999999999998</v>
       </c>
       <c r="V493">
-        <v>3.866619604805567</v>
+        <v>3.913800311648137</v>
       </c>
       <c r="W493">
         <v>47.53521215080336</v>
@@ -43084,16 +43084,16 @@
         <v>5536.748090982858</v>
       </c>
       <c r="Y493">
-        <v>0.6685685311173799</v>
+        <v>1.256753736155559</v>
       </c>
       <c r="Z493">
-        <v>197.4153832417842</v>
+        <v>267.0656379381353</v>
       </c>
       <c r="AA493">
-        <v>0.01406470068959355</v>
+        <v>0.02643837440271779</v>
       </c>
       <c r="AB493">
-        <v>0.03565547501850313</v>
+        <v>0.04823510724157346</v>
       </c>
     </row>
     <row r="494" spans="1:28">
@@ -43122,16 +43122,16 @@
         <v>78</v>
       </c>
       <c r="I494">
-        <v>2.179177542064209</v>
+        <v>2.205767987279524</v>
       </c>
       <c r="J494">
-        <v>2.179177542064209</v>
+        <v>2.205767987279524</v>
       </c>
       <c r="K494">
-        <v>259.2278051385682</v>
+        <v>262.3765264356566</v>
       </c>
       <c r="L494">
-        <v>0.001052377943989633</v>
+        <v>0.001052377943989634</v>
       </c>
       <c r="M494">
         <v>0.001056051990251759</v>
@@ -43161,7 +43161,7 @@
         <v>70.8</v>
       </c>
       <c r="V494">
-        <v>0.1112743982311805</v>
+        <v>0.1126321746091578</v>
       </c>
       <c r="W494">
         <v>2.179745177990873</v>
@@ -43170,16 +43170,16 @@
         <v>253.8896831843864</v>
       </c>
       <c r="Y494">
-        <v>-0.0005676359266639786</v>
+        <v>0.02602280928865053</v>
       </c>
       <c r="Z494">
-        <v>5.338121954181787</v>
+        <v>8.486843251270187</v>
       </c>
       <c r="AA494">
-        <v>-0.0002604138925941715</v>
+        <v>0.01193846397799417</v>
       </c>
       <c r="AB494">
-        <v>0.02102535986192474</v>
+        <v>0.03342728678386924</v>
       </c>
     </row>
     <row r="495" spans="1:28">
@@ -43208,13 +43208,13 @@
         <v>79</v>
       </c>
       <c r="I495">
-        <v>27.05039458181936</v>
+        <v>27.38046499659574</v>
       </c>
       <c r="J495">
-        <v>27.05039458181936</v>
+        <v>27.38046499659574</v>
       </c>
       <c r="K495">
-        <v>3217.82612027792</v>
+        <v>3256.911578837547</v>
       </c>
       <c r="L495">
         <v>0.0130632947910972</v>
@@ -43238,7 +43238,7 @@
         <v>106</v>
       </c>
       <c r="S495">
-        <v>73419.37729817639</v>
+        <v>73419.37729817638</v>
       </c>
       <c r="T495">
         <v>3940</v>
@@ -43247,7 +43247,7 @@
         <v>89.5</v>
       </c>
       <c r="V495">
-        <v>2.214189456032623</v>
+        <v>2.241207118563778</v>
       </c>
       <c r="W495">
         <v>27.07914201888812</v>
@@ -43256,16 +43256,16 @@
         <v>3154.091064175437</v>
       </c>
       <c r="Y495">
-        <v>-0.02874743706875904</v>
+        <v>0.3013229777076205</v>
       </c>
       <c r="Z495">
-        <v>63.73505610248367</v>
+        <v>102.8205146621099</v>
       </c>
       <c r="AA495">
-        <v>-0.001061608120697002</v>
+        <v>0.01112749353348947</v>
       </c>
       <c r="AB495">
-        <v>0.02020710715248347</v>
+        <v>0.03259909513392249</v>
       </c>
     </row>
     <row r="496" spans="1:28">
@@ -43294,16 +43294,16 @@
         <v>80</v>
       </c>
       <c r="I496">
-        <v>7.533444835621533</v>
+        <v>7.625368347275585</v>
       </c>
       <c r="J496">
-        <v>7.533444835621533</v>
+        <v>7.625368347275585</v>
       </c>
       <c r="K496">
-        <v>896.153861800908</v>
+        <v>907.0390318875511</v>
       </c>
       <c r="L496">
-        <v>0.00363808410936584</v>
+        <v>0.003638084109365841</v>
       </c>
       <c r="M496">
         <v>0.003614947197400481</v>
@@ -43324,7 +43324,7 @@
         <v>106</v>
       </c>
       <c r="S496">
-        <v>65544.23699572352</v>
+        <v>65544.23699572354</v>
       </c>
       <c r="T496">
         <v>320</v>
@@ -43333,7 +43333,7 @@
         <v>225.9</v>
       </c>
       <c r="V496">
-        <v>0.4737125283303786</v>
+        <v>0.4794927948709585</v>
       </c>
       <c r="W496">
         <v>7.461435416969231</v>
@@ -43342,16 +43342,16 @@
         <v>869.0839155158392</v>
       </c>
       <c r="Y496">
-        <v>0.0720094186523017</v>
+        <v>0.1639329303063537</v>
       </c>
       <c r="Z496">
-        <v>27.0699462850688</v>
+        <v>37.95511637171194</v>
       </c>
       <c r="AA496">
-        <v>0.009650880109279468</v>
+        <v>0.02197069613891288</v>
       </c>
       <c r="AB496">
-        <v>0.03114767837925248</v>
+        <v>0.0436725564633007</v>
       </c>
     </row>
     <row r="497" spans="1:28">
@@ -43380,13 +43380,13 @@
         <v>81</v>
       </c>
       <c r="I497">
-        <v>0.4786187414631096</v>
+        <v>0.4844588738884109</v>
       </c>
       <c r="J497">
-        <v>0.4786187414631096</v>
+        <v>0.4844588738884109</v>
       </c>
       <c r="K497">
-        <v>56.93491395388561</v>
+        <v>57.62647624990809</v>
       </c>
       <c r="L497">
         <v>0.0002311366547118225</v>
@@ -43419,7 +43419,7 @@
         <v>161</v>
       </c>
       <c r="V497">
-        <v>0.06093438033809951</v>
+        <v>0.06167790502612221</v>
       </c>
       <c r="W497">
         <v>0.50301811799787</v>
@@ -43428,16 +43428,16 @@
         <v>58.58992688870177</v>
       </c>
       <c r="Y497">
-        <v>-0.02439937653476043</v>
+        <v>-0.01855924410945914</v>
       </c>
       <c r="Z497">
-        <v>-1.655012934816156</v>
+        <v>-0.963450638793681</v>
       </c>
       <c r="AA497">
-        <v>-0.04850595964987438</v>
+        <v>-0.03689577660408989</v>
       </c>
       <c r="AB497">
-        <v>-0.02824739716709395</v>
+        <v>-0.01644396383398575</v>
       </c>
     </row>
     <row r="498" spans="1:28">
@@ -43466,16 +43466,16 @@
         <v>83</v>
       </c>
       <c r="I498">
-        <v>2.784714035569362</v>
+        <v>2.818693270658663</v>
       </c>
       <c r="J498">
-        <v>2.784714035569362</v>
+        <v>2.818693270658663</v>
       </c>
       <c r="K498">
-        <v>331.2604381446679</v>
+        <v>335.2841068090358</v>
       </c>
       <c r="L498">
-        <v>0.001344806274286214</v>
+        <v>0.001344806274286215</v>
       </c>
       <c r="M498">
         <v>0.001340373679935011</v>
@@ -43505,7 +43505,7 @@
         <v>509.5</v>
       </c>
       <c r="V498">
-        <v>0.3841160463101787</v>
+        <v>0.3888030516085441</v>
       </c>
       <c r="W498">
         <v>2.766599648988595</v>
@@ -43514,16 +43514,16 @@
         <v>322.2445978878958</v>
       </c>
       <c r="Y498">
-        <v>0.01811438658076714</v>
+        <v>0.05209362167006804</v>
       </c>
       <c r="Z498">
-        <v>9.015840256772094</v>
+        <v>13.03950892114005</v>
       </c>
       <c r="AA498">
-        <v>0.00654752724608685</v>
+        <v>0.01882947599198614</v>
       </c>
       <c r="AB498">
-        <v>0.02797825104242267</v>
+        <v>0.04046463154574374</v>
       </c>
     </row>
     <row r="499" spans="1:28">
@@ -43552,13 +43552,13 @@
         <v>84</v>
       </c>
       <c r="I499">
-        <v>29.92841564736462</v>
+        <v>30.29360383478445</v>
       </c>
       <c r="J499">
-        <v>29.92841564736462</v>
+        <v>30.29360383478445</v>
       </c>
       <c r="K499">
-        <v>3560.186056337632</v>
+        <v>3603.430004073853</v>
       </c>
       <c r="L499">
         <v>0.01445316130415258</v>
@@ -43582,7 +43582,7 @@
         <v>105</v>
       </c>
       <c r="S499">
-        <v>75014.0925372987</v>
+        <v>75014.09253729868</v>
       </c>
       <c r="T499">
         <v>3000</v>
@@ -43591,7 +43591,7 @@
         <v>975.6999999999999</v>
       </c>
       <c r="V499">
-        <v>2.810479474822366</v>
+        <v>2.844773101230264</v>
       </c>
       <c r="W499">
         <v>30.43259613887434</v>
@@ -43600,16 +43600,16 @@
         <v>3544.69057676683</v>
       </c>
       <c r="Y499">
-        <v>-0.5041804915097146</v>
+        <v>-0.1389923040898928</v>
       </c>
       <c r="Z499">
-        <v>15.49547957080176</v>
+        <v>58.73942730702265</v>
       </c>
       <c r="AA499">
-        <v>-0.01656712063633897</v>
+        <v>-0.004567218105731875</v>
       </c>
       <c r="AB499">
-        <v>0.004371461834317691</v>
+        <v>0.01657110149247493</v>
       </c>
     </row>
     <row r="500" spans="1:28">
@@ -43638,13 +43638,13 @@
         <v>85</v>
       </c>
       <c r="I500">
-        <v>55.86346560393575</v>
+        <v>56.54511470916285</v>
       </c>
       <c r="J500">
-        <v>55.86346560393575</v>
+        <v>56.54511470916285</v>
       </c>
       <c r="K500">
-        <v>6645.334442197307</v>
+        <v>6726.05227288386</v>
       </c>
       <c r="L500">
         <v>0.02697782899355581</v>
@@ -43668,7 +43668,7 @@
         <v>105</v>
       </c>
       <c r="S500">
-        <v>47187.18703291744</v>
+        <v>47187.18703291745</v>
       </c>
       <c r="T500">
         <v>5660</v>
@@ -43677,7 +43677,7 @@
         <v>1492.6</v>
       </c>
       <c r="V500">
-        <v>6.093860696136286</v>
+        <v>6.1682183222877</v>
       </c>
       <c r="W500">
         <v>59.18846521775588</v>
@@ -43686,16 +43686,16 @@
         <v>6894.081397237998</v>
       </c>
       <c r="Y500">
-        <v>-3.324999613820125</v>
+        <v>-2.643350508593031</v>
       </c>
       <c r="Z500">
-        <v>-248.7469550406913</v>
+        <v>-168.0291243541378</v>
       </c>
       <c r="AA500">
-        <v>-0.05617647968379256</v>
+        <v>-0.04465989274883335</v>
       </c>
       <c r="AB500">
-        <v>-0.03608123268465437</v>
+        <v>-0.02437295335988577</v>
       </c>
     </row>
     <row r="501" spans="1:28">
@@ -43724,16 +43724,16 @@
         <v>86</v>
       </c>
       <c r="I501">
-        <v>11.98005255671626</v>
+        <v>12.12623382237128</v>
       </c>
       <c r="J501">
-        <v>11.98005255671626</v>
+        <v>12.12623382237128</v>
       </c>
       <c r="K501">
-        <v>1425.107715996617</v>
+        <v>1442.417846033034</v>
       </c>
       <c r="L501">
-        <v>0.005785459346548884</v>
+        <v>0.005785459346548885</v>
       </c>
       <c r="M501">
         <v>0.00593013809910635</v>
@@ -43763,7 +43763,7 @@
         <v>345.3</v>
       </c>
       <c r="V501">
-        <v>1.152275395219323</v>
+        <v>1.166335523491622</v>
       </c>
       <c r="W501">
         <v>12.24010753794941</v>
@@ -43772,16 +43772,16 @@
         <v>1425.688220958554</v>
       </c>
       <c r="Y501">
-        <v>-0.2600549812331536</v>
+        <v>-0.11387371557813</v>
       </c>
       <c r="Z501">
-        <v>-0.5805049619370948</v>
+        <v>16.7296250744796</v>
       </c>
       <c r="AA501">
-        <v>-0.02124613533229797</v>
+        <v>-0.00930332639848745</v>
       </c>
       <c r="AB501">
-        <v>-0.0004071752529082378</v>
+        <v>0.01173442049148132</v>
       </c>
     </row>
     <row r="502" spans="1:28">
@@ -43810,16 +43810,16 @@
         <v>87</v>
       </c>
       <c r="I502">
-        <v>13.7979699859547</v>
+        <v>13.96633358089453</v>
       </c>
       <c r="J502">
-        <v>13.7979699859547</v>
+        <v>13.96633358089453</v>
       </c>
       <c r="K502">
-        <v>1641.361204300391</v>
+        <v>1661.298066310362</v>
       </c>
       <c r="L502">
-        <v>0.00666337597775309</v>
+        <v>0.006663375977753091</v>
       </c>
       <c r="M502">
         <v>0.006661251015434406</v>
@@ -43849,7 +43849,7 @@
         <v>428</v>
       </c>
       <c r="V502">
-        <v>1.261527232483284</v>
+        <v>1.276920457732475</v>
       </c>
       <c r="W502">
         <v>13.74916189194292</v>
@@ -43858,16 +43858,16 @@
         <v>1601.458001624647</v>
       </c>
       <c r="Y502">
-        <v>0.04880809401178432</v>
+        <v>0.2171716889516162</v>
       </c>
       <c r="Z502">
-        <v>39.90320267574384</v>
+        <v>59.84006468571488</v>
       </c>
       <c r="AA502">
-        <v>0.003549895942412762</v>
+        <v>0.01579526742490973</v>
       </c>
       <c r="AB502">
-        <v>0.024916796216487</v>
+        <v>0.0373659906316671</v>
       </c>
     </row>
     <row r="503" spans="1:28">
@@ -43896,16 +43896,16 @@
         <v>88</v>
       </c>
       <c r="I503">
-        <v>81.91452542200217</v>
+        <v>82.91405100379986</v>
       </c>
       <c r="J503">
-        <v>81.91452542200217</v>
+        <v>82.91405100379986</v>
       </c>
       <c r="K503">
-        <v>9744.282980265492</v>
+        <v>9862.642318024098</v>
       </c>
       <c r="L503">
-        <v>0.03955852067236162</v>
+        <v>0.03955852067236161</v>
       </c>
       <c r="M503">
         <v>0.04033306255077158</v>
@@ -43926,7 +43926,7 @@
         <v>105</v>
       </c>
       <c r="S503">
-        <v>48875.40310900981</v>
+        <v>48875.40310900983</v>
       </c>
       <c r="T503">
         <v>7120</v>
@@ -43935,7 +43935,7 @@
         <v>563.9999999999999</v>
       </c>
       <c r="V503">
-        <v>8.775578430009086</v>
+        <v>8.882658524664803</v>
       </c>
       <c r="W503">
         <v>83.24949852865655</v>
@@ -43944,16 +43944,16 @@
         <v>9696.6329000812</v>
       </c>
       <c r="Y503">
-        <v>-1.334973106654374</v>
+        <v>-0.3354475248566899</v>
       </c>
       <c r="Z503">
-        <v>47.65008018429216</v>
+        <v>166.0094179428979</v>
       </c>
       <c r="AA503">
-        <v>-0.01603580958742764</v>
+        <v>-0.004029423969938036</v>
       </c>
       <c r="AB503">
-        <v>0.004914085195892395</v>
+        <v>0.01712031585123819</v>
       </c>
     </row>
     <row r="504" spans="1:28">
@@ -43982,16 +43982,16 @@
         <v>89</v>
       </c>
       <c r="I504">
-        <v>9.776720547041444</v>
+        <v>9.896016633327875</v>
       </c>
       <c r="J504">
-        <v>9.776720547041444</v>
+        <v>9.896016633327875</v>
       </c>
       <c r="K504">
-        <v>1163.006574701576</v>
+        <v>1177.133082343992</v>
       </c>
       <c r="L504">
-        <v>0.004721416621479444</v>
+        <v>0.004721416621479445</v>
       </c>
       <c r="M504">
         <v>0.004752233956133091</v>
@@ -44012,7 +44012,7 @@
         <v>105</v>
       </c>
       <c r="S504">
-        <v>42350.02008283715</v>
+        <v>42350.02008283714</v>
       </c>
       <c r="T504">
         <v>1160</v>
@@ -44021,7 +44021,7 @@
         <v>1408.3</v>
       </c>
       <c r="V504">
-        <v>1.223504005919482</v>
+        <v>1.238433269649551</v>
       </c>
       <c r="W504">
         <v>9.808853300959292</v>
@@ -44030,16 +44030,16 @@
         <v>1142.503574329781</v>
       </c>
       <c r="Y504">
-        <v>-0.03213275391784798</v>
+        <v>0.08716333236858276</v>
       </c>
       <c r="Z504">
-        <v>20.503000371795</v>
+        <v>34.62950801421084</v>
       </c>
       <c r="AA504">
-        <v>-0.003275893005220645</v>
+        <v>0.008886189822010927</v>
       </c>
       <c r="AB504">
-        <v>0.01794567722365555</v>
+        <v>0.03031019665257968</v>
       </c>
     </row>
     <row r="505" spans="1:28">
@@ -49916,13 +49916,13 @@
         <v>72</v>
       </c>
       <c r="I573">
-        <v>175395.124593147</v>
+        <v>175004.8842921995</v>
       </c>
       <c r="J573">
-        <v>175395.124593147</v>
+        <v>175004.8842921995</v>
       </c>
       <c r="K573">
-        <v>175395.124593147</v>
+        <v>175004.8842921995</v>
       </c>
       <c r="L573">
         <v>0.5</v>
@@ -49955,7 +49955,7 @@
         <v>6966</v>
       </c>
       <c r="V573">
-        <v>16971.57885026987</v>
+        <v>16933.81842760448</v>
       </c>
       <c r="W573">
         <v>173082</v>
@@ -49964,16 +49964,16 @@
         <v>173082</v>
       </c>
       <c r="Y573">
-        <v>2313.124593146989</v>
+        <v>1922.884292199451</v>
       </c>
       <c r="Z573">
-        <v>2313.124593146989</v>
+        <v>1922.884292199451</v>
       </c>
       <c r="AA573">
-        <v>0.0133643278512323</v>
+        <v>0.01110967224898863</v>
       </c>
       <c r="AB573">
-        <v>0.0133643278512323</v>
+        <v>0.01110967224898863</v>
       </c>
     </row>
     <row r="574" spans="1:28">
@@ -50002,13 +50002,13 @@
         <v>73</v>
       </c>
       <c r="I574">
-        <v>9080.578752170984</v>
+        <v>9060.375181557236</v>
       </c>
       <c r="J574">
-        <v>9080.578752170984</v>
+        <v>9060.375181557236</v>
       </c>
       <c r="K574">
-        <v>9080.578752170984</v>
+        <v>9060.375181557236</v>
       </c>
       <c r="L574">
         <v>0.02588606374673934</v>
@@ -50041,7 +50041,7 @@
         <v>761.9</v>
       </c>
       <c r="V574">
-        <v>671.770393100694</v>
+        <v>670.2757570269757</v>
       </c>
       <c r="W574">
         <v>8931.665635738758</v>
@@ -50050,16 +50050,16 @@
         <v>8931.665635738758</v>
       </c>
       <c r="Y574">
-        <v>148.9131164322262</v>
+        <v>128.7095458184776</v>
       </c>
       <c r="Z574">
-        <v>148.9131164322262</v>
+        <v>128.7095458184776</v>
       </c>
       <c r="AA574">
-        <v>0.01667249116854218</v>
+        <v>0.01441047516416928</v>
       </c>
       <c r="AB574">
-        <v>0.01667249116854218</v>
+        <v>0.01441047516416928</v>
       </c>
     </row>
     <row r="575" spans="1:28">
@@ -50088,16 +50088,16 @@
         <v>74</v>
       </c>
       <c r="I575">
-        <v>6214.53959010927</v>
+        <v>6200.712730294777</v>
       </c>
       <c r="J575">
-        <v>6214.53959010927</v>
+        <v>6200.712730294777</v>
       </c>
       <c r="K575">
-        <v>6214.53959010927</v>
+        <v>6200.712730294777</v>
       </c>
       <c r="L575">
-        <v>0.01771582763353527</v>
+        <v>0.01771582763353526</v>
       </c>
       <c r="M575">
         <v>0.01723940435280622</v>
@@ -50118,7 +50118,7 @@
         <v>106</v>
       </c>
       <c r="S575">
-        <v>82697.59450439614</v>
+        <v>82697.59450439618</v>
       </c>
       <c r="T575">
         <v>5340</v>
@@ -50127,7 +50127,7 @@
         <v>784.0000000000001</v>
       </c>
       <c r="V575">
-        <v>534.7009292856475</v>
+        <v>533.5112619442924</v>
       </c>
       <c r="W575">
         <v>5967.661168384812</v>
@@ -50136,16 +50136,16 @@
         <v>5967.661168384812</v>
       </c>
       <c r="Y575">
-        <v>246.8784217244574</v>
+        <v>233.0515619099651</v>
       </c>
       <c r="Z575">
-        <v>246.8784217244574</v>
+        <v>233.0515619099651</v>
       </c>
       <c r="AA575">
-        <v>0.04136937650420872</v>
+        <v>0.03905241188032164</v>
       </c>
       <c r="AB575">
-        <v>0.04136937650420872</v>
+        <v>0.03905241188032164</v>
       </c>
     </row>
     <row r="576" spans="1:28">
@@ -50174,13 +50174,13 @@
         <v>75</v>
       </c>
       <c r="I576">
-        <v>2566.824889086517</v>
+        <v>2561.113906415133</v>
       </c>
       <c r="J576">
-        <v>2566.824889086517</v>
+        <v>2561.113906415133</v>
       </c>
       <c r="K576">
-        <v>2566.824889086517</v>
+        <v>2561.113906415133</v>
       </c>
       <c r="L576">
         <v>0.00731726407743835</v>
@@ -50213,7 +50213,7 @@
         <v>305.8</v>
       </c>
       <c r="V576">
-        <v>159.4566630881712</v>
+        <v>159.101884605383</v>
       </c>
       <c r="W576">
         <v>2438.612371133951</v>
@@ -50222,16 +50222,16 @@
         <v>2438.612371133951</v>
       </c>
       <c r="Y576">
-        <v>128.2125179525656</v>
+        <v>122.5015352811811</v>
       </c>
       <c r="Z576">
-        <v>128.2125179525656</v>
+        <v>122.5015352811811</v>
       </c>
       <c r="AA576">
-        <v>0.0525760139127593</v>
+        <v>0.05023411540564687</v>
       </c>
       <c r="AB576">
-        <v>0.0525760139127593</v>
+        <v>0.05023411540564687</v>
       </c>
     </row>
     <row r="577" spans="1:28">
@@ -50260,13 +50260,13 @@
         <v>76</v>
       </c>
       <c r="I577">
-        <v>13886.36747359556</v>
+        <v>13855.47140259852</v>
       </c>
       <c r="J577">
-        <v>13886.36747359556</v>
+        <v>13855.47140259852</v>
       </c>
       <c r="K577">
-        <v>13886.36747359556</v>
+        <v>13855.47140259852</v>
       </c>
       <c r="L577">
         <v>0.03958595629669549</v>
@@ -50290,7 +50290,7 @@
         <v>106</v>
       </c>
       <c r="S577">
-        <v>96289.15374747863</v>
+        <v>96289.15374747862</v>
       </c>
       <c r="T577">
         <v>12260</v>
@@ -50299,7 +50299,7 @@
         <v>98.5</v>
       </c>
       <c r="V577">
-        <v>941.7493361369043</v>
+        <v>939.6540182356586</v>
       </c>
       <c r="W577">
         <v>13352.8896907216</v>
@@ -50308,16 +50308,16 @@
         <v>13352.8896907216</v>
       </c>
       <c r="Y577">
-        <v>533.477782873957</v>
+        <v>502.5817118769228</v>
       </c>
       <c r="Z577">
-        <v>533.477782873957</v>
+        <v>502.5817118769228</v>
       </c>
       <c r="AA577">
-        <v>0.03995223470202483</v>
+        <v>0.03763842310673376</v>
       </c>
       <c r="AB577">
-        <v>0.03995223470202483</v>
+        <v>0.03763842310673376</v>
       </c>
     </row>
     <row r="578" spans="1:28">
@@ -50346,16 +50346,16 @@
         <v>77</v>
       </c>
       <c r="I578">
-        <v>318.3168429730527</v>
+        <v>317.6086131354982</v>
       </c>
       <c r="J578">
-        <v>318.3168429730527</v>
+        <v>317.6086131354982</v>
       </c>
       <c r="K578">
-        <v>318.3168429730527</v>
+        <v>317.6086131354982</v>
       </c>
       <c r="L578">
-        <v>0.0009074278538569192</v>
+        <v>0.0009074278538569196</v>
       </c>
       <c r="M578">
         <v>0.0009163802978235566</v>
@@ -50376,7 +50376,7 @@
         <v>106</v>
       </c>
       <c r="S578">
-        <v>80202.06517098683</v>
+        <v>80202.06517098681</v>
       </c>
       <c r="T578">
         <v>230</v>
@@ -50385,7 +50385,7 @@
         <v>25.5</v>
       </c>
       <c r="V578">
-        <v>34.77650209596924</v>
+        <v>34.69912712516938</v>
       </c>
       <c r="W578">
         <v>317.2178694157936</v>
@@ -50394,16 +50394,16 @@
         <v>317.2178694157936</v>
       </c>
       <c r="Y578">
-        <v>1.098973557259058</v>
+        <v>0.3907437197045738</v>
       </c>
       <c r="Z578">
-        <v>1.098973557259058</v>
+        <v>0.3907437197045738</v>
       </c>
       <c r="AA578">
-        <v>0.003464412516492181</v>
+        <v>0.001231783444054364</v>
       </c>
       <c r="AB578">
-        <v>0.003464412516492181</v>
+        <v>0.001231783444054364</v>
       </c>
     </row>
     <row r="579" spans="1:28">
@@ -50432,13 +50432,13 @@
         <v>78</v>
       </c>
       <c r="I579">
-        <v>42.98924418620486</v>
+        <v>42.89359651282943</v>
       </c>
       <c r="J579">
-        <v>42.98924418620486</v>
+        <v>42.89359651282943</v>
       </c>
       <c r="K579">
-        <v>42.98924418620486</v>
+        <v>42.89359651282943</v>
       </c>
       <c r="L579">
         <v>0.0001225497125017708</v>
@@ -50471,7 +50471,7 @@
         <v>31.5</v>
       </c>
       <c r="V579">
-        <v>1.534025705879868</v>
+        <v>1.530612619829087</v>
       </c>
       <c r="W579">
         <v>39.65223367695906</v>
@@ -50480,16 +50480,16 @@
         <v>39.65223367695906</v>
       </c>
       <c r="Y579">
-        <v>3.337010509245808</v>
+        <v>3.241362835870369</v>
       </c>
       <c r="Z579">
-        <v>3.337010509245808</v>
+        <v>3.241362835870369</v>
       </c>
       <c r="AA579">
-        <v>0.08415693643974621</v>
+        <v>0.08174477287401455</v>
       </c>
       <c r="AB579">
-        <v>0.08415693643974621</v>
+        <v>0.08174477287401455</v>
       </c>
     </row>
     <row r="580" spans="1:28">
@@ -50518,16 +50518,16 @@
         <v>79</v>
       </c>
       <c r="I580">
-        <v>193.451598837992</v>
+        <v>193.0211843078024</v>
       </c>
       <c r="J580">
-        <v>193.451598837992</v>
+        <v>193.0211843078024</v>
       </c>
       <c r="K580">
-        <v>193.451598837992</v>
+        <v>193.0211843078024</v>
       </c>
       <c r="L580">
-        <v>0.0005514737062581685</v>
+        <v>0.0005514737062581686</v>
       </c>
       <c r="M580">
         <v>0.0005154639175257036</v>
@@ -50557,7 +50557,7 @@
         <v>30.1</v>
       </c>
       <c r="V580">
-        <v>15.76331832101278</v>
+        <v>15.72824618260647</v>
       </c>
       <c r="W580">
         <v>178.4350515463677</v>
@@ -50566,16 +50566,16 @@
         <v>178.4350515463677</v>
       </c>
       <c r="Y580">
-        <v>15.01654729162436</v>
+        <v>14.58613276143473</v>
       </c>
       <c r="Z580">
-        <v>15.01654729162436</v>
+        <v>14.58613276143473</v>
       </c>
       <c r="AA580">
-        <v>0.08415693643982389</v>
+        <v>0.08174477287409201</v>
       </c>
       <c r="AB580">
-        <v>0.08415693643982389</v>
+        <v>0.08174477287409201</v>
       </c>
     </row>
     <row r="581" spans="1:28">
@@ -50604,16 +50604,16 @@
         <v>80</v>
       </c>
       <c r="I581">
-        <v>96.7257994189891</v>
+        <v>96.51059215389429</v>
       </c>
       <c r="J581">
-        <v>96.7257994189891</v>
+        <v>96.51059215389429</v>
       </c>
       <c r="K581">
-        <v>96.7257994189891</v>
+        <v>96.51059215389429</v>
       </c>
       <c r="L581">
-        <v>0.0002757368531290645</v>
+        <v>0.0002757368531290646</v>
       </c>
       <c r="M581">
         <v>0.0002577319587628519</v>
@@ -50634,7 +50634,7 @@
         <v>106</v>
       </c>
       <c r="S581">
-        <v>93600.00000000001</v>
+        <v>93600</v>
       </c>
       <c r="T581">
         <v>110</v>
@@ -50643,7 +50643,7 @@
         <v>189.1</v>
       </c>
       <c r="V581">
-        <v>5.264992924722107</v>
+        <v>5.253278731250676</v>
       </c>
       <c r="W581">
         <v>89.21752577318385</v>
@@ -50652,16 +50652,16 @@
         <v>89.21752577318385</v>
       </c>
       <c r="Y581">
-        <v>7.508273645805247</v>
+        <v>7.293066380710442</v>
       </c>
       <c r="Z581">
-        <v>7.508273645805247</v>
+        <v>7.293066380710442</v>
       </c>
       <c r="AA581">
-        <v>0.08415693643974614</v>
+        <v>0.08174477287401442</v>
       </c>
       <c r="AB581">
-        <v>0.08415693643974614</v>
+        <v>0.08174477287401442</v>
       </c>
     </row>
     <row r="582" spans="1:28">
@@ -50690,16 +50690,16 @@
         <v>81</v>
       </c>
       <c r="I582">
-        <v>117.5655090518452</v>
+        <v>117.3039350785671</v>
       </c>
       <c r="J582">
-        <v>117.5655090518452</v>
+        <v>117.3039350785671</v>
       </c>
       <c r="K582">
-        <v>117.5655090518452</v>
+        <v>117.3039350785671</v>
       </c>
       <c r="L582">
-        <v>0.0003351447462537926</v>
+        <v>0.0003351447462537927</v>
       </c>
       <c r="M582">
         <v>0.0003722794959908027</v>
@@ -50729,7 +50729,7 @@
         <v>161</v>
       </c>
       <c r="V582">
-        <v>14.96761581317972</v>
+        <v>14.93431405001526</v>
       </c>
       <c r="W582">
         <v>128.8697594501602</v>
@@ -50738,16 +50738,16 @@
         <v>128.8697594501602</v>
       </c>
       <c r="Y582">
-        <v>-11.30425039831501</v>
+        <v>-11.56582437159312</v>
       </c>
       <c r="Z582">
-        <v>-11.30425039831501</v>
+        <v>-11.56582437159312</v>
       </c>
       <c r="AA582">
-        <v>-0.08771841001757183</v>
+        <v>-0.08974816451074508</v>
       </c>
       <c r="AB582">
-        <v>-0.08771841001757183</v>
+        <v>-0.08974816451074508</v>
       </c>
     </row>
     <row r="583" spans="1:28">
@@ -50776,13 +50776,13 @@
         <v>83</v>
       </c>
       <c r="I583">
-        <v>452.747647196148</v>
+        <v>451.7403194354424</v>
       </c>
       <c r="J583">
-        <v>452.747647196148</v>
+        <v>451.7403194354424</v>
       </c>
       <c r="K583">
-        <v>452.747647196148</v>
+        <v>451.7403194354424</v>
       </c>
       <c r="L583">
         <v>0.001290650604588805</v>
@@ -50815,7 +50815,7 @@
         <v>351.3</v>
       </c>
       <c r="V583">
-        <v>64.3511282003588</v>
+        <v>64.20795202203873</v>
       </c>
       <c r="W583">
         <v>456.0006872852196</v>
@@ -50824,16 +50824,16 @@
         <v>456.0006872852196</v>
       </c>
       <c r="Y583">
-        <v>-3.253040089071533</v>
+        <v>-4.260367849777197</v>
       </c>
       <c r="Z583">
-        <v>-3.253040089071533</v>
+        <v>-4.260367849777197</v>
       </c>
       <c r="AA583">
-        <v>-0.007133849092286169</v>
+        <v>-0.009342897869608735</v>
       </c>
       <c r="AB583">
-        <v>-0.007133849092286169</v>
+        <v>-0.009342897869608735</v>
       </c>
     </row>
     <row r="584" spans="1:28">
@@ -50862,16 +50862,16 @@
         <v>84</v>
       </c>
       <c r="I584">
-        <v>1109.423105235419</v>
+        <v>1106.954726439432</v>
       </c>
       <c r="J584">
-        <v>1109.423105235419</v>
+        <v>1106.954726439432</v>
       </c>
       <c r="K584">
-        <v>1109.423105235419</v>
+        <v>1106.954726439432</v>
       </c>
       <c r="L584">
-        <v>0.003162639519795313</v>
+        <v>0.003162639519795314</v>
       </c>
       <c r="M584">
         <v>0.003235967926689523</v>
@@ -50901,7 +50901,7 @@
         <v>171.8</v>
       </c>
       <c r="V584">
-        <v>96.27401849816924</v>
+        <v>96.05981640994528</v>
       </c>
       <c r="W584">
         <v>1120.175601374552</v>
@@ -50910,16 +50910,16 @@
         <v>1120.175601374552</v>
       </c>
       <c r="Y584">
-        <v>-10.75249613913297</v>
+        <v>-13.22087493511981</v>
       </c>
       <c r="Z584">
-        <v>-10.75249613913297</v>
+        <v>-13.22087493511981</v>
       </c>
       <c r="AA584">
-        <v>-0.0095989379932385</v>
+        <v>-0.01180250214242897</v>
       </c>
       <c r="AB584">
-        <v>-0.0095989379932385</v>
+        <v>-0.01180250214242897</v>
       </c>
     </row>
     <row r="585" spans="1:28">
@@ -50948,16 +50948,16 @@
         <v>85</v>
       </c>
       <c r="I585">
-        <v>5370.435203007058</v>
+        <v>5358.48640879341</v>
       </c>
       <c r="J585">
-        <v>5370.435203007058</v>
+        <v>5358.48640879341</v>
       </c>
       <c r="K585">
-        <v>5370.435203007058</v>
+        <v>5358.48640879341</v>
       </c>
       <c r="L585">
-        <v>0.01530953387519897</v>
+        <v>0.01530953387519898</v>
       </c>
       <c r="M585">
         <v>0.01629438717067567</v>
@@ -50987,7 +50987,7 @@
         <v>1316.8</v>
       </c>
       <c r="V585">
-        <v>513.8944943668249</v>
+        <v>512.7511197000424</v>
       </c>
       <c r="W585">
         <v>5640.530240549771</v>
@@ -50996,16 +50996,16 @@
         <v>5640.530240549771</v>
       </c>
       <c r="Y585">
-        <v>-270.0950375427137</v>
+        <v>-282.0438317563612</v>
       </c>
       <c r="Z585">
-        <v>-270.0950375427137</v>
+        <v>-282.0438317563612</v>
       </c>
       <c r="AA585">
-        <v>-0.04788468920900388</v>
+        <v>-0.05000307058523473</v>
       </c>
       <c r="AB585">
-        <v>-0.04788468920900388</v>
+        <v>-0.05000307058523473</v>
       </c>
     </row>
     <row r="586" spans="1:28">
@@ -51034,16 +51034,16 @@
         <v>86</v>
       </c>
       <c r="I586">
-        <v>4686.837730025487</v>
+        <v>4676.409886204287</v>
       </c>
       <c r="J586">
-        <v>4686.837730025487</v>
+        <v>4676.409886204287</v>
       </c>
       <c r="K586">
-        <v>4686.837730025487</v>
+        <v>4676.409886204287</v>
       </c>
       <c r="L586">
-        <v>0.01336079820034122</v>
+        <v>0.01336079820034123</v>
       </c>
       <c r="M586">
         <v>0.01274341351660939</v>
@@ -51073,7 +51073,7 @@
         <v>209.7</v>
       </c>
       <c r="V586">
-        <v>431.5627215558474</v>
+        <v>430.6025285816792</v>
       </c>
       <c r="W586">
         <v>4411.310996563572</v>
@@ -51082,16 +51082,16 @@
         <v>4411.310996563572</v>
       </c>
       <c r="Y586">
-        <v>275.5267334619148</v>
+        <v>265.0988896407143</v>
       </c>
       <c r="Z586">
-        <v>275.5267334619148</v>
+        <v>265.0988896407143</v>
       </c>
       <c r="AA586">
-        <v>0.06245914959896302</v>
+        <v>0.06009526189543819</v>
       </c>
       <c r="AB586">
-        <v>0.06245914959896302</v>
+        <v>0.06009526189543819</v>
       </c>
     </row>
     <row r="587" spans="1:28">
@@ -51120,13 +51120,13 @@
         <v>87</v>
       </c>
       <c r="I587">
-        <v>9176.730555694599</v>
+        <v>9156.313054911294</v>
       </c>
       <c r="J587">
-        <v>9176.730555694599</v>
+        <v>9156.313054911294</v>
       </c>
       <c r="K587">
-        <v>9176.730555694599</v>
+        <v>9156.313054911294</v>
       </c>
       <c r="L587">
         <v>0.02616016430610965</v>
@@ -51159,7 +51159,7 @@
         <v>450.5000000000001</v>
       </c>
       <c r="V587">
-        <v>846.1894993617839</v>
+        <v>844.3067945508287</v>
       </c>
       <c r="W587">
         <v>8554.969415807507</v>
@@ -51168,16 +51168,16 @@
         <v>8554.969415807507</v>
       </c>
       <c r="Y587">
-        <v>621.7611398870922</v>
+        <v>601.3436391037867</v>
       </c>
       <c r="Z587">
-        <v>621.7611398870922</v>
+        <v>601.3436391037867</v>
       </c>
       <c r="AA587">
-        <v>0.07267835916961066</v>
+        <v>0.07029173453182072</v>
       </c>
       <c r="AB587">
-        <v>0.07267835916961066</v>
+        <v>0.07029173453182072</v>
       </c>
     </row>
     <row r="588" spans="1:28">
@@ -51206,13 +51206,13 @@
         <v>88</v>
       </c>
       <c r="I588">
-        <v>113679.2063412054</v>
+        <v>113426.2790845501</v>
       </c>
       <c r="J588">
-        <v>113679.2063412054</v>
+        <v>113426.2790845501</v>
       </c>
       <c r="K588">
-        <v>113679.2063412054</v>
+        <v>113426.2790845501</v>
       </c>
       <c r="L588">
         <v>0.3240660383374392</v>
@@ -51245,7 +51245,7 @@
         <v>647.7000000000002</v>
       </c>
       <c r="V588">
-        <v>11643.60200890187</v>
+        <v>11617.69591394851</v>
       </c>
       <c r="W588">
         <v>112929.561512028</v>
@@ -51254,16 +51254,16 @@
         <v>112929.561512028</v>
       </c>
       <c r="Y588">
-        <v>749.6448291774432</v>
+        <v>496.7175725220877</v>
       </c>
       <c r="Z588">
-        <v>749.6448291774432</v>
+        <v>496.7175725220877</v>
       </c>
       <c r="AA588">
-        <v>0.006638162932188481</v>
+        <v>0.004398472515712221</v>
       </c>
       <c r="AB588">
-        <v>0.006638162932188481</v>
+        <v>0.004398472515712221</v>
       </c>
     </row>
     <row r="589" spans="1:28">
@@ -51292,13 +51292,13 @@
         <v>89</v>
       </c>
       <c r="I589">
-        <v>8402.384311352464</v>
+        <v>8383.689669811285</v>
       </c>
       <c r="J589">
-        <v>8402.384311352464</v>
+        <v>8383.689669811285</v>
       </c>
       <c r="K589">
-        <v>8402.384311352464</v>
+        <v>8383.689669811285</v>
       </c>
       <c r="L589">
         <v>0.02395273053011862</v>
@@ -51331,7 +51331,7 @@
         <v>1430.8</v>
       </c>
       <c r="V589">
-        <v>995.7212029128314</v>
+        <v>993.5058018702659</v>
       </c>
       <c r="W589">
         <v>8525.230240549816</v>
@@ -51340,16 +51340,16 @@
         <v>8525.230240549816</v>
       </c>
       <c r="Y589">
-        <v>-122.8459291973522</v>
+        <v>-141.5405707385307</v>
       </c>
       <c r="Z589">
-        <v>-122.8459291973522</v>
+        <v>-141.5405707385307</v>
       </c>
       <c r="AA589">
-        <v>-0.01440969049880224</v>
+        <v>-0.01660255110358197</v>
       </c>
       <c r="AB589">
-        <v>-0.01440969049880224</v>
+        <v>-0.01660255110358197</v>
       </c>
     </row>
     <row r="590" spans="1:28">
@@ -56968,13 +56968,13 @@
         <v>72</v>
       </c>
       <c r="I655">
-        <v>117867.4213358047</v>
+        <v>116941.3295385387</v>
       </c>
       <c r="J655">
-        <v>117867.4213358047</v>
+        <v>116941.3295385387</v>
       </c>
       <c r="K655">
-        <v>117867.4213358047</v>
+        <v>116941.3295385387</v>
       </c>
       <c r="L655">
         <v>0.5</v>
@@ -57007,7 +57007,7 @@
         <v>9805.299999999999</v>
       </c>
       <c r="V655">
-        <v>13377.37529810892</v>
+        <v>13272.26841282947</v>
       </c>
       <c r="W655">
         <v>115340</v>
@@ -57016,16 +57016,16 @@
         <v>115340</v>
       </c>
       <c r="Y655">
-        <v>2527.421335804684</v>
+        <v>1601.329538538746</v>
       </c>
       <c r="Z655">
-        <v>2527.421335804684</v>
+        <v>1601.329538538746</v>
       </c>
       <c r="AA655">
-        <v>0.02191279118956722</v>
+        <v>0.01388355764295775</v>
       </c>
       <c r="AB655">
-        <v>0.02191279118956722</v>
+        <v>0.01388355764295775</v>
       </c>
     </row>
     <row r="656" spans="1:28">
@@ -57054,16 +57054,16 @@
         <v>73</v>
       </c>
       <c r="I656">
-        <v>9145.551970929693</v>
+        <v>9073.694789651268</v>
       </c>
       <c r="J656">
-        <v>9145.551970929693</v>
+        <v>9073.694789651268</v>
       </c>
       <c r="K656">
-        <v>9145.551970929693</v>
+        <v>9073.694789651268</v>
       </c>
       <c r="L656">
-        <v>0.03879592794718901</v>
+        <v>0.038795927947189</v>
       </c>
       <c r="M656">
         <v>0.03793352601156049</v>
@@ -57093,7 +57093,7 @@
         <v>808.6999999999999</v>
       </c>
       <c r="V656">
-        <v>717.4011962628354</v>
+        <v>711.7645296107759</v>
       </c>
       <c r="W656">
         <v>8750.505780346773</v>
@@ -57102,16 +57102,16 @@
         <v>8750.505780346773</v>
       </c>
       <c r="Y656">
-        <v>395.0461905829197</v>
+        <v>323.1890093044949</v>
       </c>
       <c r="Z656">
-        <v>395.0461905829197</v>
+        <v>323.1890093044949</v>
       </c>
       <c r="AA656">
-        <v>0.04514552649861394</v>
+        <v>0.03693375187870424</v>
       </c>
       <c r="AB656">
-        <v>0.04514552649861394</v>
+        <v>0.03693375187870424</v>
       </c>
     </row>
     <row r="657" spans="1:28">
@@ -57140,13 +57140,13 @@
         <v>74</v>
       </c>
       <c r="I657">
-        <v>5355.705682070097</v>
+        <v>5313.625563199888</v>
       </c>
       <c r="J657">
-        <v>5355.705682070097</v>
+        <v>5313.625563199888</v>
       </c>
       <c r="K657">
-        <v>5355.705682070097</v>
+        <v>5313.625563199888</v>
       </c>
       <c r="L657">
         <v>0.02271919424966325</v>
@@ -57179,7 +57179,7 @@
         <v>742.2</v>
       </c>
       <c r="V657">
-        <v>463.2372487495758</v>
+        <v>459.597564336418</v>
       </c>
       <c r="W657">
         <v>5041.958092485519</v>
@@ -57188,16 +57188,16 @@
         <v>5041.958092485519</v>
       </c>
       <c r="Y657">
-        <v>313.7475895845782</v>
+        <v>271.6674707143693</v>
       </c>
       <c r="Z657">
-        <v>313.7475895845782</v>
+        <v>271.6674707143693</v>
       </c>
       <c r="AA657">
-        <v>0.06222732990426563</v>
+        <v>0.05388134247273091</v>
       </c>
       <c r="AB657">
-        <v>0.06222732990426563</v>
+        <v>0.05388134247273091</v>
       </c>
     </row>
     <row r="658" spans="1:28">
@@ -57226,13 +57226,13 @@
         <v>75</v>
       </c>
       <c r="I658">
-        <v>1473.966850251154</v>
+        <v>1462.385799321309</v>
       </c>
       <c r="J658">
-        <v>1473.966850251154</v>
+        <v>1462.385799321309</v>
       </c>
       <c r="K658">
-        <v>1473.966850251154</v>
+        <v>1462.385799321309</v>
       </c>
       <c r="L658">
         <v>0.006252647396314107</v>
@@ -57265,7 +57265,7 @@
         <v>260.5</v>
       </c>
       <c r="V658">
-        <v>89.3980300013626</v>
+        <v>88.69562401557181</v>
       </c>
       <c r="W658">
         <v>1406.331286127118</v>
@@ -57274,16 +57274,16 @@
         <v>1406.331286127118</v>
       </c>
       <c r="Y658">
-        <v>67.63556412403614</v>
+        <v>56.0545131941908</v>
       </c>
       <c r="Z658">
-        <v>67.63556412403614</v>
+        <v>56.0545131941908</v>
       </c>
       <c r="AA658">
-        <v>0.04809362117676914</v>
+        <v>0.03985868319018827</v>
       </c>
       <c r="AB658">
-        <v>0.04809362117676914</v>
+        <v>0.03985868319018827</v>
       </c>
     </row>
     <row r="659" spans="1:28">
@@ -57312,13 +57312,13 @@
         <v>76</v>
       </c>
       <c r="I659">
-        <v>5973.557080000475</v>
+        <v>5926.622463550969</v>
       </c>
       <c r="J659">
-        <v>5973.557080000475</v>
+        <v>5926.622463550969</v>
       </c>
       <c r="K659">
-        <v>5973.557080000475</v>
+        <v>5926.622463550969</v>
       </c>
       <c r="L659">
         <v>0.02534015342111282</v>
@@ -57342,7 +57342,7 @@
         <v>106</v>
       </c>
       <c r="S659">
-        <v>98940.99766867327</v>
+        <v>98940.9976686733</v>
       </c>
       <c r="T659">
         <v>2900</v>
@@ -57351,7 +57351,7 @@
         <v>91.2</v>
       </c>
       <c r="V659">
-        <v>380.1917842133832</v>
+        <v>377.2045932766712</v>
       </c>
       <c r="W659">
         <v>5458.648843930622</v>
@@ -57360,16 +57360,16 @@
         <v>5458.648843930622</v>
       </c>
       <c r="Y659">
-        <v>514.908236069853</v>
+        <v>467.9736196203467</v>
       </c>
       <c r="Z659">
-        <v>514.908236069853</v>
+        <v>467.9736196203467</v>
       </c>
       <c r="AA659">
-        <v>0.09432888078931304</v>
+        <v>0.08573066943858799</v>
       </c>
       <c r="AB659">
-        <v>0.09432888078931304</v>
+        <v>0.08573066943858799</v>
       </c>
     </row>
     <row r="660" spans="1:28">
@@ -57398,13 +57398,13 @@
         <v>77</v>
       </c>
       <c r="I660">
-        <v>71.70167614627512</v>
+        <v>71.13831153392729</v>
       </c>
       <c r="J660">
-        <v>71.70167614627512</v>
+        <v>71.13831153392729</v>
       </c>
       <c r="K660">
-        <v>71.70167614627512</v>
+        <v>71.13831153392729</v>
       </c>
       <c r="L660">
         <v>0.0003041624026964873</v>
@@ -57437,7 +57437,7 @@
         <v>14.9</v>
       </c>
       <c r="V660">
-        <v>7.622939526075627</v>
+        <v>7.563045607245926</v>
       </c>
       <c r="W660">
         <v>62.50361271675567</v>
@@ -57446,16 +57446,16 @@
         <v>62.50361271675567</v>
       </c>
       <c r="Y660">
-        <v>9.198063429519451</v>
+        <v>8.634698817171625</v>
       </c>
       <c r="Z660">
-        <v>9.198063429519451</v>
+        <v>8.634698817171625</v>
       </c>
       <c r="AA660">
-        <v>0.1471605084845548</v>
+        <v>0.1381471956877282</v>
       </c>
       <c r="AB660">
-        <v>0.1471605084845548</v>
+        <v>0.1381471956877282</v>
       </c>
     </row>
     <row r="661" spans="1:28">
@@ -57484,13 +57484,13 @@
         <v>78</v>
       </c>
       <c r="I661">
-        <v>75.94298908676014</v>
+        <v>75.3463002099183</v>
       </c>
       <c r="J661">
-        <v>75.94298908676014</v>
+        <v>75.3463002099183</v>
       </c>
       <c r="K661">
-        <v>75.94298908676014</v>
+        <v>75.3463002099183</v>
       </c>
       <c r="L661">
         <v>0.0003221542824390732</v>
@@ -57523,7 +57523,7 @@
         <v>36.2</v>
       </c>
       <c r="V661">
-        <v>5.117043146595266</v>
+        <v>5.076838214387437</v>
       </c>
       <c r="W661">
         <v>72.92088150287776</v>
@@ -57532,16 +57532,16 @@
         <v>72.92088150287776</v>
       </c>
       <c r="Y661">
-        <v>3.022107583882374</v>
+        <v>2.425418707040535</v>
       </c>
       <c r="Z661">
-        <v>3.022107583882374</v>
+        <v>2.425418707040535</v>
       </c>
       <c r="AA661">
-        <v>0.04144365127790054</v>
+        <v>0.03326096252614305</v>
       </c>
       <c r="AB661">
-        <v>0.04144365127790054</v>
+        <v>0.03326096252614305</v>
       </c>
     </row>
     <row r="662" spans="1:28">
@@ -57570,16 +57570,16 @@
         <v>79</v>
       </c>
       <c r="I662">
-        <v>132.1901890922957</v>
+        <v>131.1515624013067</v>
       </c>
       <c r="J662">
-        <v>132.1901890922957</v>
+        <v>131.1515624013067</v>
       </c>
       <c r="K662">
-        <v>132.1901890922957</v>
+        <v>131.1515624013067</v>
       </c>
       <c r="L662">
-        <v>0.0005607579583661433</v>
+        <v>0.0005607579583661434</v>
       </c>
       <c r="M662">
         <v>0.0005419075144508534</v>
@@ -57609,7 +57609,7 @@
         <v>22.5</v>
       </c>
       <c r="V662">
-        <v>10.16750355661949</v>
+        <v>10.08761683698361</v>
       </c>
       <c r="W662">
         <v>125.0072254335229</v>
@@ -57618,16 +57618,16 @@
         <v>125.0072254335229</v>
       </c>
       <c r="Y662">
-        <v>7.182963658772792</v>
+        <v>6.144336967783858</v>
       </c>
       <c r="Z662">
-        <v>7.182963658772792</v>
+        <v>6.144336967783858</v>
       </c>
       <c r="AA662">
-        <v>0.05746038786048085</v>
+        <v>0.04915185459460766</v>
       </c>
       <c r="AB662">
-        <v>0.05746038786048085</v>
+        <v>0.04915185459460766</v>
       </c>
     </row>
     <row r="663" spans="1:28">
@@ -57656,13 +57656,13 @@
         <v>82</v>
       </c>
       <c r="I663">
-        <v>1737.170360124582</v>
+        <v>1723.521302541643</v>
       </c>
       <c r="J663">
-        <v>1737.170360124582</v>
+        <v>1723.521302541643</v>
       </c>
       <c r="K663">
-        <v>1737.170360124582</v>
+        <v>1723.521302541643</v>
       </c>
       <c r="L663">
         <v>0.007369170973781541</v>
@@ -57695,7 +57695,7 @@
         <v>1236.2</v>
       </c>
       <c r="V663">
-        <v>374.9632118539056</v>
+        <v>372.0171021414935</v>
       </c>
       <c r="W663">
         <v>1854.273843930634</v>
@@ -57704,16 +57704,16 @@
         <v>1854.273843930634</v>
       </c>
       <c r="Y663">
-        <v>-117.1034838060516</v>
+        <v>-130.7525413889903</v>
       </c>
       <c r="Z663">
-        <v>-117.1034838060516</v>
+        <v>-130.7525413889903</v>
       </c>
       <c r="AA663">
-        <v>-0.06315328460753088</v>
+        <v>-0.07051414860699592</v>
       </c>
       <c r="AB663">
-        <v>-0.06315328460753088</v>
+        <v>-0.07051414860699592</v>
       </c>
     </row>
     <row r="664" spans="1:28">
@@ -57742,13 +57742,13 @@
         <v>83</v>
       </c>
       <c r="I664">
-        <v>251.932616699519</v>
+        <v>249.9531661681931</v>
       </c>
       <c r="J664">
-        <v>251.932616699519</v>
+        <v>249.9531661681931</v>
       </c>
       <c r="K664">
-        <v>251.932616699519</v>
+        <v>249.9531661681931</v>
       </c>
       <c r="L664">
         <v>0.001068711836758361</v>
@@ -57781,7 +57781,7 @@
         <v>509.5</v>
       </c>
       <c r="V664">
-        <v>35.05424347288159</v>
+        <v>34.77882006095244</v>
       </c>
       <c r="W664">
         <v>250.0144508670457</v>
@@ -57790,16 +57790,16 @@
         <v>250.0144508670457</v>
       </c>
       <c r="Y664">
-        <v>1.91816583247325</v>
+        <v>-0.06128469885260301</v>
       </c>
       <c r="Z664">
-        <v>1.91816583247325</v>
+        <v>-0.06128469885260301</v>
       </c>
       <c r="AA664">
-        <v>0.007672219848977066</v>
+        <v>-0.0002451246263568716</v>
       </c>
       <c r="AB664">
-        <v>0.007672219848977066</v>
+        <v>-0.0002451246263568716</v>
       </c>
     </row>
     <row r="665" spans="1:28">
@@ -57828,16 +57828,16 @@
         <v>84</v>
       </c>
       <c r="I665">
-        <v>41484.36025006042</v>
+        <v>41158.41500321437</v>
       </c>
       <c r="J665">
-        <v>41484.36025006042</v>
+        <v>41158.41500321437</v>
       </c>
       <c r="K665">
-        <v>41484.36025006042</v>
+        <v>41158.41500321437</v>
       </c>
       <c r="L665">
-        <v>0.1759789082509549</v>
+        <v>0.1759789082509548</v>
       </c>
       <c r="M665">
         <v>0.1830292630057814</v>
@@ -57858,7 +57858,7 @@
         <v>105</v>
       </c>
       <c r="S665">
-        <v>42805.77069934421</v>
+        <v>42805.77069934423</v>
       </c>
       <c r="T665">
         <v>39410</v>
@@ -57867,7 +57867,7 @@
         <v>1594.4</v>
       </c>
       <c r="V665">
-        <v>5621.448438709805</v>
+        <v>5577.28036216378</v>
       </c>
       <c r="W665">
         <v>42221.19039017365</v>
@@ -57876,16 +57876,16 @@
         <v>42221.19039017365</v>
       </c>
       <c r="Y665">
-        <v>-736.8301401132267</v>
+        <v>-1062.775386959285</v>
       </c>
       <c r="Z665">
-        <v>-736.8301401132267</v>
+        <v>-1062.775386959285</v>
       </c>
       <c r="AA665">
-        <v>-0.01745166664663043</v>
+        <v>-0.02517161115397235</v>
       </c>
       <c r="AB665">
-        <v>-0.01745166664663043</v>
+        <v>-0.02517161115397235</v>
       </c>
     </row>
     <row r="666" spans="1:28">
@@ -57914,16 +57914,16 @@
         <v>85</v>
       </c>
       <c r="I666">
-        <v>9367.911162997189</v>
+        <v>9294.306891458484</v>
       </c>
       <c r="J666">
-        <v>9367.911162997189</v>
+        <v>9294.306891458484</v>
       </c>
       <c r="K666">
-        <v>9367.911162997189</v>
+        <v>9294.306891458484</v>
       </c>
       <c r="L666">
-        <v>0.03973918771119959</v>
+        <v>0.0397391877111996</v>
       </c>
       <c r="M666">
         <v>0.04123013005780325</v>
@@ -57944,7 +57944,7 @@
         <v>105</v>
       </c>
       <c r="S666">
-        <v>46855.86956888072</v>
+        <v>46855.86956888071</v>
       </c>
       <c r="T666">
         <v>10940</v>
@@ -57953,7 +57953,7 @@
         <v>1538.1</v>
       </c>
       <c r="V666">
-        <v>976.2153578660559</v>
+        <v>968.5451719483622</v>
       </c>
       <c r="W666">
         <v>9510.966401734055</v>
@@ -57962,16 +57962,16 @@
         <v>9510.966401734055</v>
       </c>
       <c r="Y666">
-        <v>-143.0552387368662</v>
+        <v>-216.6595102755709</v>
       </c>
       <c r="Z666">
-        <v>-143.0552387368662</v>
+        <v>-216.6595102755709</v>
       </c>
       <c r="AA666">
-        <v>-0.01504108338672967</v>
+        <v>-0.02277996799947366</v>
       </c>
       <c r="AB666">
-        <v>-0.01504108338672967</v>
+        <v>-0.02277996799947366</v>
       </c>
     </row>
     <row r="667" spans="1:28">
@@ -58000,13 +58000,13 @@
         <v>86</v>
       </c>
       <c r="I667">
-        <v>407.1081184868674</v>
+        <v>403.9094442064068</v>
       </c>
       <c r="J667">
-        <v>407.1081184868674</v>
+        <v>403.9094442064068</v>
       </c>
       <c r="K667">
-        <v>407.1081184868674</v>
+        <v>403.9094442064068</v>
       </c>
       <c r="L667">
         <v>0.001726974739385428</v>
@@ -58039,7 +58039,7 @@
         <v>370.7</v>
       </c>
       <c r="V667">
-        <v>34.9606492226459</v>
+        <v>34.68596118667078</v>
       </c>
       <c r="W667">
         <v>385.4389450866907</v>
@@ -58048,16 +58048,16 @@
         <v>385.4389450866907</v>
       </c>
       <c r="Y667">
-        <v>21.6691734001767</v>
+        <v>18.47049911971607</v>
       </c>
       <c r="Z667">
-        <v>21.6691734001767</v>
+        <v>18.47049911971607</v>
       </c>
       <c r="AA667">
-        <v>0.05621947049305824</v>
+        <v>0.04792068719356263</v>
       </c>
       <c r="AB667">
-        <v>0.05621947049305824</v>
+        <v>0.04792068719356263</v>
       </c>
     </row>
     <row r="668" spans="1:28">
@@ -58086,16 +58086,16 @@
         <v>87</v>
       </c>
       <c r="I668">
-        <v>13325.15229782141</v>
+        <v>13220.45573196397</v>
       </c>
       <c r="J668">
-        <v>13325.15229782141</v>
+        <v>13220.45573196397</v>
       </c>
       <c r="K668">
-        <v>13325.15229782141</v>
+        <v>13220.45573196397</v>
       </c>
       <c r="L668">
-        <v>0.05652601943270655</v>
+        <v>0.05652601943270656</v>
       </c>
       <c r="M668">
         <v>0.05373916184971109</v>
@@ -58116,7 +58116,7 @@
         <v>105</v>
       </c>
       <c r="S668">
-        <v>54761.3102425817</v>
+        <v>54761.31024258168</v>
       </c>
       <c r="T668">
         <v>10970</v>
@@ -58125,7 +58125,7 @@
         <v>421.5</v>
       </c>
       <c r="V668">
-        <v>1327.914945510247</v>
+        <v>1317.481433649491</v>
       </c>
       <c r="W668">
         <v>12396.54985549135</v>
@@ -58134,16 +58134,16 @@
         <v>12396.54985549135</v>
       </c>
       <c r="Y668">
-        <v>928.6024423300587</v>
+        <v>823.9058764726124</v>
       </c>
       <c r="Z668">
-        <v>928.6024423300587</v>
+        <v>823.9058764726124</v>
       </c>
       <c r="AA668">
-        <v>0.07490813598581315</v>
+        <v>0.06646251465746683</v>
       </c>
       <c r="AB668">
-        <v>0.07490813598581315</v>
+        <v>0.06646251465746683</v>
       </c>
     </row>
     <row r="669" spans="1:28">
@@ -58172,16 +58172,16 @@
         <v>88</v>
       </c>
       <c r="I669">
-        <v>7840.07407585062</v>
+        <v>7778.474117106151</v>
       </c>
       <c r="J669">
-        <v>7840.07407585062</v>
+        <v>7778.474117106151</v>
       </c>
       <c r="K669">
-        <v>7840.07407585062</v>
+        <v>7778.474117106151</v>
       </c>
       <c r="L669">
-        <v>0.03325801984551024</v>
+        <v>0.03325801984551025</v>
       </c>
       <c r="M669">
         <v>0.03274024566473956</v>
@@ -58202,7 +58202,7 @@
         <v>105</v>
       </c>
       <c r="S669">
-        <v>48300.29652166987</v>
+        <v>48300.29652166986</v>
       </c>
       <c r="T669">
         <v>7080</v>
@@ -58211,7 +58211,7 @@
         <v>607.1000000000001</v>
       </c>
       <c r="V669">
-        <v>794.538872402936</v>
+        <v>788.2961301421636</v>
       </c>
       <c r="W669">
         <v>7552.519869942121</v>
@@ -58220,16 +58220,16 @@
         <v>7552.519869942121</v>
       </c>
       <c r="Y669">
-        <v>287.5542059084992</v>
+        <v>225.9542471640307</v>
       </c>
       <c r="Z669">
-        <v>287.5542059084992</v>
+        <v>225.9542471640307</v>
       </c>
       <c r="AA669">
-        <v>0.03807394232128023</v>
+        <v>0.02991772958629267</v>
       </c>
       <c r="AB669">
-        <v>0.03807394232128023</v>
+        <v>0.02991772958629267</v>
       </c>
     </row>
     <row r="670" spans="1:28">
@@ -58258,16 +58258,16 @@
         <v>89</v>
       </c>
       <c r="I670">
-        <v>21225.09601618732</v>
+        <v>21058.32909201095</v>
       </c>
       <c r="J670">
-        <v>21225.09601618732</v>
+        <v>21058.32909201095</v>
       </c>
       <c r="K670">
-        <v>21225.09601618732</v>
+        <v>21058.32909201095</v>
       </c>
       <c r="L670">
-        <v>0.09003800955192255</v>
+        <v>0.09003800955192254</v>
       </c>
       <c r="M670">
         <v>0.08778901734104071</v>
@@ -58288,7 +58288,7 @@
         <v>105</v>
       </c>
       <c r="S670">
-        <v>44800.52692100649</v>
+        <v>44800.5269210065</v>
       </c>
       <c r="T670">
         <v>14660</v>
@@ -58297,7 +58297,7 @@
         <v>1551.6</v>
       </c>
       <c r="V670">
-        <v>2539.143833613994</v>
+        <v>2519.193619638507</v>
       </c>
       <c r="W670">
         <v>20251.17052023127</v>
@@ -58306,16 +58306,16 @@
         <v>20251.17052023127</v>
       </c>
       <c r="Y670">
-        <v>973.9254959560531</v>
+        <v>807.158571779677</v>
       </c>
       <c r="Z670">
-        <v>973.9254959560531</v>
+        <v>807.158571779677</v>
       </c>
       <c r="AA670">
-        <v>0.04809230631795257</v>
+        <v>0.03985737866230062</v>
       </c>
       <c r="AB670">
-        <v>0.04809230631795257</v>
+        <v>0.03985737866230062</v>
       </c>
     </row>
     <row r="671" spans="1:28">
@@ -62816,13 +62816,13 @@
         <v>72</v>
       </c>
       <c r="I723">
-        <v>71386.84768836701</v>
+        <v>71700.708618174</v>
       </c>
       <c r="J723">
-        <v>71386.84768836701</v>
+        <v>71700.708618174</v>
       </c>
       <c r="K723">
-        <v>71386.84768836701</v>
+        <v>71700.708618174</v>
       </c>
       <c r="L723">
         <v>0.5</v>
@@ -62855,7 +62855,7 @@
         <v>6510.3</v>
       </c>
       <c r="V723">
-        <v>7561.367874229596</v>
+        <v>7594.612344723356</v>
       </c>
       <c r="W723">
         <v>69600.00000000001</v>
@@ -62864,16 +62864,16 @@
         <v>69600.00000000001</v>
       </c>
       <c r="Y723">
-        <v>1786.847688366994</v>
+        <v>2100.708618173987</v>
       </c>
       <c r="Z723">
-        <v>1786.847688366994</v>
+        <v>2100.708618173987</v>
       </c>
       <c r="AA723">
-        <v>0.02567309897079013</v>
+        <v>0.0301825950887067</v>
       </c>
       <c r="AB723">
-        <v>0.02567309897079013</v>
+        <v>0.0301825950887067</v>
       </c>
     </row>
     <row r="724" spans="1:28">
@@ -62902,16 +62902,16 @@
         <v>73</v>
       </c>
       <c r="I724">
-        <v>4319.925330031267</v>
+        <v>4338.918405432205</v>
       </c>
       <c r="J724">
-        <v>4319.925330031267</v>
+        <v>4338.918405432205</v>
       </c>
       <c r="K724">
-        <v>4319.925330031267</v>
+        <v>4338.918405432205</v>
       </c>
       <c r="L724">
-        <v>0.03025715149161313</v>
+        <v>0.03025715149161314</v>
       </c>
       <c r="M724">
         <v>0.03046203177379395</v>
@@ -62941,7 +62941,7 @@
         <v>539</v>
       </c>
       <c r="V724">
-        <v>346.9327349958842</v>
+        <v>348.4580668225764</v>
       </c>
       <c r="W724">
         <v>4240.314822912118</v>
@@ -62950,16 +62950,16 @@
         <v>4240.314822912118</v>
       </c>
       <c r="Y724">
-        <v>79.61050711914868</v>
+        <v>98.603582520087</v>
       </c>
       <c r="Z724">
-        <v>79.61050711914868</v>
+        <v>98.603582520087</v>
       </c>
       <c r="AA724">
-        <v>0.01877466896773354</v>
+        <v>0.02325383530187249</v>
       </c>
       <c r="AB724">
-        <v>0.01877466896773354</v>
+        <v>0.02325383530187249</v>
       </c>
     </row>
     <row r="725" spans="1:28">
@@ -62988,13 +62988,13 @@
         <v>74</v>
       </c>
       <c r="I725">
-        <v>1634.949064535729</v>
+        <v>1642.137316296366</v>
       </c>
       <c r="J725">
-        <v>1634.949064535729</v>
+        <v>1642.137316296366</v>
       </c>
       <c r="K725">
-        <v>1634.949064535729</v>
+        <v>1642.137316296366</v>
       </c>
       <c r="L725">
         <v>0.01145133254568793</v>
@@ -63027,7 +63027,7 @@
         <v>362.3</v>
       </c>
       <c r="V725">
-        <v>133.5252625969383</v>
+        <v>134.112322600685</v>
       </c>
       <c r="W725">
         <v>1592.654132050711</v>
@@ -63036,16 +63036,16 @@
         <v>1592.654132050711</v>
       </c>
       <c r="Y725">
-        <v>42.29493248501808</v>
+        <v>49.48318424565559</v>
       </c>
       <c r="Z725">
-        <v>42.29493248501808</v>
+        <v>49.48318424565559</v>
       </c>
       <c r="AA725">
-        <v>0.02655625702647622</v>
+        <v>0.03106963605584645</v>
       </c>
       <c r="AB725">
-        <v>0.02655625702647622</v>
+        <v>0.03106963605584645</v>
       </c>
     </row>
     <row r="726" spans="1:28">
@@ -63074,13 +63074,13 @@
         <v>75</v>
       </c>
       <c r="I726">
-        <v>153.861257473059</v>
+        <v>154.5377271435308</v>
       </c>
       <c r="J726">
-        <v>153.861257473059</v>
+        <v>154.5377271435308</v>
       </c>
       <c r="K726">
-        <v>153.861257473059</v>
+        <v>154.5377271435308</v>
       </c>
       <c r="L726">
         <v>0.00107765829739903</v>
@@ -63104,7 +63104,7 @@
         <v>107</v>
       </c>
       <c r="S726">
-        <v>70062.66666666651</v>
+        <v>70062.6666666665</v>
       </c>
       <c r="T726">
         <v>90</v>
@@ -63113,7 +63113,7 @@
         <v>55.09999999999999</v>
       </c>
       <c r="V726">
-        <v>8.237039603574395</v>
+        <v>8.27325474673523</v>
       </c>
       <c r="W726">
         <v>152.1644075207587</v>
@@ -63122,16 +63122,16 @@
         <v>152.1644075207587</v>
       </c>
       <c r="Y726">
-        <v>1.696849952300255</v>
+        <v>2.373319622772016</v>
       </c>
       <c r="Z726">
-        <v>1.696849952300255</v>
+        <v>2.373319622772016</v>
       </c>
       <c r="AA726">
-        <v>0.01115142483020391</v>
+        <v>0.01559707464735628</v>
       </c>
       <c r="AB726">
-        <v>0.01115142483020391</v>
+        <v>0.01559707464735628</v>
       </c>
     </row>
     <row r="727" spans="1:28">
@@ -63160,13 +63160,13 @@
         <v>78</v>
       </c>
       <c r="I727">
-        <v>51.28708582435567</v>
+        <v>51.51257571451293</v>
       </c>
       <c r="J727">
-        <v>51.28708582435567</v>
+        <v>51.51257571451293</v>
       </c>
       <c r="K727">
-        <v>51.28708582435567</v>
+        <v>51.51257571451293</v>
       </c>
       <c r="L727">
         <v>0.0003592194324663622</v>
@@ -63199,7 +63199,7 @@
         <v>4.7</v>
       </c>
       <c r="V727">
-        <v>4.726456928911209</v>
+        <v>4.74723736976884</v>
       </c>
       <c r="W727">
         <v>50.72146917358625</v>
@@ -63208,16 +63208,16 @@
         <v>50.72146917358625</v>
       </c>
       <c r="Y727">
-        <v>0.5656166507694209</v>
+        <v>0.791106540926684</v>
       </c>
       <c r="Z727">
-        <v>0.5656166507694209</v>
+        <v>0.791106540926684</v>
       </c>
       <c r="AA727">
-        <v>0.01115142483025653</v>
+        <v>0.01559707464740909</v>
       </c>
       <c r="AB727">
-        <v>0.01115142483025653</v>
+        <v>0.01559707464740909</v>
       </c>
     </row>
     <row r="728" spans="1:28">
@@ -63246,13 +63246,13 @@
         <v>79</v>
       </c>
       <c r="I728">
-        <v>53.81028429358948</v>
+        <v>54.0468677316941</v>
       </c>
       <c r="J728">
-        <v>53.81028429358948</v>
+        <v>54.0468677316941</v>
       </c>
       <c r="K728">
-        <v>53.81028429358948</v>
+        <v>54.0468677316941</v>
       </c>
       <c r="L728">
         <v>0.0003768921449543026</v>
@@ -63285,7 +63285,7 @@
         <v>12.7</v>
       </c>
       <c r="V728">
-        <v>4.478313306216163</v>
+        <v>4.498002753555145</v>
       </c>
       <c r="W728">
         <v>50.72146917358625</v>
@@ -63294,16 +63294,16 @@
         <v>50.72146917358625</v>
       </c>
       <c r="Y728">
-        <v>3.088815120003233</v>
+        <v>3.32539855810785</v>
       </c>
       <c r="Z728">
-        <v>3.088815120003233</v>
+        <v>3.32539855810785</v>
       </c>
       <c r="AA728">
-        <v>0.06089758775386116</v>
+        <v>0.06556195260683786</v>
       </c>
       <c r="AB728">
-        <v>0.06089758775386116</v>
+        <v>0.06556195260683786</v>
       </c>
     </row>
     <row r="729" spans="1:28">
@@ -63332,13 +63332,13 @@
         <v>83</v>
       </c>
       <c r="I729">
-        <v>345.4505690504524</v>
+        <v>346.9693843548884</v>
       </c>
       <c r="J729">
-        <v>345.4505690504524</v>
+        <v>346.9693843548884</v>
       </c>
       <c r="K729">
-        <v>345.4505690504524</v>
+        <v>346.9693843548884</v>
       </c>
       <c r="L729">
         <v>0.00241956733093529</v>
@@ -63371,7 +63371,7 @@
         <v>351.3</v>
       </c>
       <c r="V729">
-        <v>49.10049559290498</v>
+        <v>49.31637187403799</v>
       </c>
       <c r="W729">
         <v>334.7616965456914</v>
@@ -63380,16 +63380,16 @@
         <v>334.7616965456914</v>
       </c>
       <c r="Y729">
-        <v>10.68887250476098</v>
+        <v>12.20768780919695</v>
       </c>
       <c r="Z729">
-        <v>10.68887250476098</v>
+        <v>12.20768780919695</v>
       </c>
       <c r="AA729">
-        <v>0.03192979547856384</v>
+        <v>0.03646679992115148</v>
       </c>
       <c r="AB729">
-        <v>0.03192979547856384</v>
+        <v>0.03646679992115148</v>
       </c>
     </row>
     <row r="730" spans="1:28">
@@ -63418,16 +63418,16 @@
         <v>84</v>
       </c>
       <c r="I730">
-        <v>14323.31452430451</v>
+        <v>14386.28871296936</v>
       </c>
       <c r="J730">
-        <v>14323.31452430451</v>
+        <v>14386.28871296936</v>
       </c>
       <c r="K730">
-        <v>14323.31452430451</v>
+        <v>14386.28871296936</v>
       </c>
       <c r="L730">
-        <v>0.1003218028818955</v>
+        <v>0.1003218028818956</v>
       </c>
       <c r="M730">
         <v>0.1000583005392801</v>
@@ -63448,7 +63448,7 @@
         <v>105</v>
       </c>
       <c r="S730">
-        <v>37802.55837140328</v>
+        <v>37802.55837140327</v>
       </c>
       <c r="T730">
         <v>13470</v>
@@ -63457,7 +63457,7 @@
         <v>1575.5</v>
       </c>
       <c r="V730">
-        <v>1795.253457678571</v>
+        <v>1803.146507136728</v>
       </c>
       <c r="W730">
         <v>13928.11543506779</v>
@@ -63466,16 +63466,16 @@
         <v>13928.11543506779</v>
       </c>
       <c r="Y730">
-        <v>395.1990892367248</v>
+        <v>458.1732779015783</v>
       </c>
       <c r="Z730">
-        <v>395.1990892367248</v>
+        <v>458.1732779015783</v>
       </c>
       <c r="AA730">
-        <v>0.02837419685951946</v>
+        <v>0.03289556868174739</v>
       </c>
       <c r="AB730">
-        <v>0.02837419685951946</v>
+        <v>0.03289556868174739</v>
       </c>
     </row>
     <row r="731" spans="1:28">
@@ -63504,13 +63504,13 @@
         <v>85</v>
       </c>
       <c r="I731">
-        <v>7783.60442711733</v>
+        <v>7817.825987556719</v>
       </c>
       <c r="J731">
-        <v>7783.60442711733</v>
+        <v>7817.825987556719</v>
       </c>
       <c r="K731">
-        <v>7783.60442711733</v>
+        <v>7817.825987556719</v>
       </c>
       <c r="L731">
         <v>0.05451707617834569</v>
@@ -63543,7 +63543,7 @@
         <v>1455.2</v>
       </c>
       <c r="V731">
-        <v>854.213475171397</v>
+        <v>857.9691282679075</v>
       </c>
       <c r="W731">
         <v>8003.847835592455</v>
@@ -63552,16 +63552,16 @@
         <v>8003.847835592455</v>
       </c>
       <c r="Y731">
-        <v>-220.2434084751249</v>
+        <v>-186.0218480357362</v>
       </c>
       <c r="Z731">
-        <v>-220.2434084751249</v>
+        <v>-186.0218480357362</v>
       </c>
       <c r="AA731">
-        <v>-0.02751719085609305</v>
+        <v>-0.02324155229544873</v>
       </c>
       <c r="AB731">
-        <v>-0.02751719085609305</v>
+        <v>-0.02324155229544873</v>
       </c>
     </row>
     <row r="732" spans="1:28">
@@ -63590,13 +63590,13 @@
         <v>87</v>
       </c>
       <c r="I732">
-        <v>26926.4405939552</v>
+        <v>27044.82595421237</v>
       </c>
       <c r="J732">
-        <v>26926.4405939552</v>
+        <v>27044.82595421237</v>
       </c>
       <c r="K732">
-        <v>26926.4405939552</v>
+        <v>27044.82595421237</v>
       </c>
       <c r="L732">
         <v>0.1885952487459609</v>
@@ -63629,7 +63629,7 @@
         <v>376.1000000000001</v>
       </c>
       <c r="V732">
-        <v>2312.924017923195</v>
+        <v>2323.093068754622</v>
       </c>
       <c r="W732">
         <v>25949.10362920861</v>
@@ -63638,16 +63638,16 @@
         <v>25949.10362920861</v>
       </c>
       <c r="Y732">
-        <v>977.3369647465843</v>
+        <v>1095.722325003757</v>
       </c>
       <c r="Z732">
-        <v>977.3369647465843</v>
+        <v>1095.722325003757</v>
       </c>
       <c r="AA732">
-        <v>0.0376636117652435</v>
+        <v>0.04222582562622314</v>
       </c>
       <c r="AB732">
-        <v>0.0376636117652435</v>
+        <v>0.04222582562622314</v>
       </c>
     </row>
     <row r="733" spans="1:28">
@@ -63676,16 +63676,16 @@
         <v>88</v>
       </c>
       <c r="I733">
-        <v>1053.076290526233</v>
+        <v>1057.706268097804</v>
       </c>
       <c r="J733">
-        <v>1053.076290526233</v>
+        <v>1057.706268097804</v>
       </c>
       <c r="K733">
-        <v>1053.076290526233</v>
+        <v>1057.706268097804</v>
       </c>
       <c r="L733">
-        <v>0.007375842501992419</v>
+        <v>0.00737584250199242</v>
       </c>
       <c r="M733">
         <v>0.007360443084098374</v>
@@ -63715,7 +63715,7 @@
         <v>314.9</v>
       </c>
       <c r="V733">
-        <v>101.2726849682798</v>
+        <v>101.7179426046298</v>
       </c>
       <c r="W733">
         <v>1024.573677306494</v>
@@ -63724,16 +63724,16 @@
         <v>1024.573677306494</v>
       </c>
       <c r="Y733">
-        <v>28.50261321973971</v>
+        <v>33.13259079131035</v>
       </c>
       <c r="Z733">
-        <v>28.50261321973971</v>
+        <v>33.13259079131035</v>
       </c>
       <c r="AA733">
-        <v>0.02781899813654237</v>
+        <v>0.03233792896028011</v>
       </c>
       <c r="AB733">
-        <v>0.02781899813654237</v>
+        <v>0.03233792896028011</v>
       </c>
     </row>
     <row r="734" spans="1:28">
@@ -63762,13 +63762,13 @@
         <v>89</v>
       </c>
       <c r="I734">
-        <v>14741.12826125529</v>
+        <v>14805.93941866455</v>
       </c>
       <c r="J734">
-        <v>14741.12826125529</v>
+        <v>14805.93941866455</v>
       </c>
       <c r="K734">
-        <v>14741.12826125529</v>
+        <v>14805.93941866455</v>
       </c>
       <c r="L734">
         <v>0.1032482084487494</v>
@@ -63801,7 +63801,7 @@
         <v>1463.5</v>
       </c>
       <c r="V734">
-        <v>1950.703935463724</v>
+        <v>1959.28044179211</v>
       </c>
       <c r="W734">
         <v>14273.0214254482</v>
@@ -63810,16 +63810,16 @@
         <v>14273.0214254482</v>
       </c>
       <c r="Y734">
-        <v>468.1068358070861</v>
+        <v>532.9179932163479</v>
       </c>
       <c r="Z734">
-        <v>468.1068358070861</v>
+        <v>532.9179932163479</v>
       </c>
       <c r="AA734">
-        <v>0.03279661830903379</v>
+        <v>0.03733743384327703</v>
       </c>
       <c r="AB734">
-        <v>0.03279661830903379</v>
+        <v>0.03733743384327703</v>
       </c>
     </row>
     <row r="735" spans="1:28">
@@ -67718,16 +67718,16 @@
         <v>72</v>
       </c>
       <c r="I780">
-        <v>42092.6682197545</v>
+        <v>41734.77862917184</v>
       </c>
       <c r="J780">
-        <v>42092.6682197545</v>
+        <v>41734.77862917184</v>
       </c>
       <c r="K780">
-        <v>42092.6682197545</v>
+        <v>41734.77862917184</v>
       </c>
       <c r="L780">
-        <v>0.5</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="M780">
         <v>0.5</v>
@@ -67748,7 +67748,7 @@
         <v>107</v>
       </c>
       <c r="S780">
-        <v>58908.87714687985</v>
+        <v>58908.87714687987</v>
       </c>
       <c r="T780">
         <v>45070</v>
@@ -67757,7 +67757,7 @@
         <v>5282.5</v>
       </c>
       <c r="V780">
-        <v>4306.625280865705</v>
+        <v>4270.008539191948</v>
       </c>
       <c r="W780">
         <v>46889</v>
@@ -67766,16 +67766,16 @@
         <v>46889</v>
       </c>
       <c r="Y780">
-        <v>-4796.331780245499</v>
+        <v>-5154.221370828156</v>
       </c>
       <c r="Z780">
-        <v>-4796.331780245499</v>
+        <v>-5154.221370828156</v>
       </c>
       <c r="AA780">
-        <v>-0.1022911936753929</v>
+        <v>-0.109923891975264</v>
       </c>
       <c r="AB780">
-        <v>-0.1022911936753929</v>
+        <v>-0.109923891975264</v>
       </c>
     </row>
     <row r="781" spans="1:28">
@@ -67804,13 +67804,13 @@
         <v>73</v>
       </c>
       <c r="I781">
-        <v>2266.840395877812</v>
+        <v>2247.566764257183</v>
       </c>
       <c r="J781">
-        <v>2266.840395877812</v>
+        <v>2247.566764257183</v>
       </c>
       <c r="K781">
-        <v>2266.840395877812</v>
+        <v>2247.566764257183</v>
       </c>
       <c r="L781">
         <v>0.02692678430413638</v>
@@ -67843,7 +67843,7 @@
         <v>654.2</v>
       </c>
       <c r="V781">
-        <v>184.9596925071282</v>
+        <v>183.3870873142218</v>
       </c>
       <c r="W781">
         <v>2466.265545144796</v>
@@ -67852,16 +67852,16 @@
         <v>2466.265545144796</v>
       </c>
       <c r="Y781">
-        <v>-199.4251492669846</v>
+        <v>-218.6987808876138</v>
       </c>
       <c r="Z781">
-        <v>-199.4251492669846</v>
+        <v>-218.6987808876138</v>
       </c>
       <c r="AA781">
-        <v>-0.08086118287610274</v>
+        <v>-0.08867608815204601</v>
       </c>
       <c r="AB781">
-        <v>-0.08086118287610274</v>
+        <v>-0.08867608815204601</v>
       </c>
     </row>
     <row r="782" spans="1:28">
@@ -67890,16 +67890,16 @@
         <v>74</v>
       </c>
       <c r="I782">
-        <v>2171.019954295974</v>
+        <v>2152.561028420016</v>
       </c>
       <c r="J782">
-        <v>2171.019954295974</v>
+        <v>2152.561028420016</v>
       </c>
       <c r="K782">
-        <v>2171.019954295974</v>
+        <v>2152.561028420016</v>
       </c>
       <c r="L782">
-        <v>0.02578857608837795</v>
+        <v>0.02578857608837794</v>
       </c>
       <c r="M782">
         <v>0.02480834752981249</v>
@@ -67920,7 +67920,7 @@
         <v>106</v>
       </c>
       <c r="S782">
-        <v>80051.75317497581</v>
+        <v>80051.75317497582</v>
       </c>
       <c r="T782">
         <v>440</v>
@@ -67929,7 +67929,7 @@
         <v>583.2</v>
       </c>
       <c r="V782">
-        <v>200.5379534736004</v>
+        <v>198.8328953458938</v>
       </c>
       <c r="W782">
         <v>2326.477214650756</v>
@@ -67938,16 +67938,16 @@
         <v>2326.477214650756</v>
       </c>
       <c r="Y782">
-        <v>-155.4572603547817</v>
+        <v>-173.9161862307401</v>
       </c>
       <c r="Z782">
-        <v>-155.4572603547817</v>
+        <v>-173.9161862307401</v>
       </c>
       <c r="AA782">
-        <v>-0.06682088239498125</v>
+        <v>-0.07475516421803764</v>
       </c>
       <c r="AB782">
-        <v>-0.06682088239498125</v>
+        <v>-0.07475516421803764</v>
       </c>
     </row>
     <row r="783" spans="1:28">
@@ -67976,13 +67976,13 @@
         <v>75</v>
       </c>
       <c r="I783">
-        <v>163.1897789884422</v>
+        <v>161.8022707676628</v>
       </c>
       <c r="J783">
-        <v>163.1897789884422</v>
+        <v>161.8022707676628</v>
       </c>
       <c r="K783">
-        <v>163.1897789884422</v>
+        <v>161.8022707676628</v>
       </c>
       <c r="L783">
         <v>0.00193845847614687</v>
@@ -68015,7 +68015,7 @@
         <v>170.3</v>
       </c>
       <c r="V783">
-        <v>9.311282559431545</v>
+        <v>9.232114114095726</v>
       </c>
       <c r="W783">
         <v>179.727853492331</v>
@@ -68024,16 +68024,16 @@
         <v>179.727853492331</v>
       </c>
       <c r="Y783">
-        <v>-16.53807450388877</v>
+        <v>-17.92558272466812</v>
       </c>
       <c r="Z783">
-        <v>-16.53807450388877</v>
+        <v>-17.92558272466812</v>
       </c>
       <c r="AA783">
-        <v>-0.09201731497112911</v>
+        <v>-0.09973736611411213</v>
       </c>
       <c r="AB783">
-        <v>-0.09201731497112911</v>
+        <v>-0.09973736611411213</v>
       </c>
     </row>
     <row r="784" spans="1:28">
@@ -68062,13 +68062,13 @@
         <v>77</v>
       </c>
       <c r="I784">
-        <v>142.9612683590425</v>
+        <v>141.745751453935</v>
       </c>
       <c r="J784">
-        <v>142.9612683590425</v>
+        <v>141.745751453935</v>
       </c>
       <c r="K784">
-        <v>142.9612683590425</v>
+        <v>141.745751453935</v>
       </c>
       <c r="L784">
         <v>0.001698173035891668</v>
@@ -68101,7 +68101,7 @@
         <v>14.9</v>
       </c>
       <c r="V784">
-        <v>15.19887904780402</v>
+        <v>15.0696517778354</v>
       </c>
       <c r="W784">
         <v>149.7732112436091</v>
@@ -68110,16 +68110,16 @@
         <v>149.7732112436091</v>
       </c>
       <c r="Y784">
-        <v>-6.811942884566633</v>
+        <v>-8.027459789674168</v>
       </c>
       <c r="Z784">
-        <v>-6.811942884566633</v>
+        <v>-8.027459789674168</v>
       </c>
       <c r="AA784">
-        <v>-0.04548171751146386</v>
+        <v>-0.05359743390036115</v>
       </c>
       <c r="AB784">
-        <v>-0.04548171751146386</v>
+        <v>-0.05359743390036115</v>
       </c>
     </row>
     <row r="785" spans="1:28">
@@ -68148,16 +68148,16 @@
         <v>83</v>
       </c>
       <c r="I785">
-        <v>71.50802940150022</v>
+        <v>70.90003802323295</v>
       </c>
       <c r="J785">
-        <v>71.50802940150022</v>
+        <v>70.90003802323295</v>
       </c>
       <c r="K785">
-        <v>71.50802940150022</v>
+        <v>70.90003802323295</v>
       </c>
       <c r="L785">
-        <v>0.0008494119335483324</v>
+        <v>0.0008494119335483322</v>
       </c>
       <c r="M785">
         <v>0.0008517887563884016</v>
@@ -68187,7 +68187,7 @@
         <v>351.3</v>
       </c>
       <c r="V785">
-        <v>10.16376870397598</v>
+        <v>10.07735206245417</v>
       </c>
       <c r="W785">
         <v>79.87904599659153</v>
@@ -68196,16 +68196,16 @@
         <v>79.87904599659153</v>
       </c>
       <c r="Y785">
-        <v>-8.371016595091305</v>
+        <v>-8.979007973358577</v>
       </c>
       <c r="Z785">
-        <v>-8.371016595091305</v>
+        <v>-8.979007973358577</v>
       </c>
       <c r="AA785">
-        <v>-0.1047961513642577</v>
+        <v>-0.1124075514590111</v>
       </c>
       <c r="AB785">
-        <v>-0.1047961513642577</v>
+        <v>-0.1124075514590111</v>
       </c>
     </row>
     <row r="786" spans="1:28">
@@ -68234,13 +68234,13 @@
         <v>84</v>
       </c>
       <c r="I786">
-        <v>448.7220788651542</v>
+        <v>444.9068547921153</v>
       </c>
       <c r="J786">
-        <v>448.7220788651542</v>
+        <v>444.9068547921153</v>
       </c>
       <c r="K786">
-        <v>448.7220788651542</v>
+        <v>444.9068547921153</v>
       </c>
       <c r="L786">
         <v>0.005330169098838032</v>
@@ -68264,7 +68264,7 @@
         <v>105</v>
       </c>
       <c r="S786">
-        <v>66381.02722221268</v>
+        <v>66381.02722221267</v>
       </c>
       <c r="T786">
         <v>420</v>
@@ -68273,7 +68273,7 @@
         <v>237.8</v>
       </c>
       <c r="V786">
-        <v>43.12795015065099</v>
+        <v>42.7612581571308</v>
       </c>
       <c r="W786">
         <v>509.2289182282757</v>
@@ -68282,16 +68282,16 @@
         <v>509.2289182282757</v>
       </c>
       <c r="Y786">
-        <v>-60.50683936312151</v>
+        <v>-64.32206343616042</v>
       </c>
       <c r="Z786">
-        <v>-60.50683936312151</v>
+        <v>-64.32206343616042</v>
       </c>
       <c r="AA786">
-        <v>-0.1188205091997499</v>
+        <v>-0.1263126682984769</v>
       </c>
       <c r="AB786">
-        <v>-0.1188205091997499</v>
+        <v>-0.1263126682984769</v>
       </c>
     </row>
     <row r="787" spans="1:28">
@@ -68320,16 +68320,16 @@
         <v>85</v>
       </c>
       <c r="I787">
-        <v>4131.122311874196</v>
+        <v>4095.997770347755</v>
       </c>
       <c r="J787">
-        <v>4131.122311874196</v>
+        <v>4095.997770347755</v>
       </c>
       <c r="K787">
-        <v>4131.122311874196</v>
+        <v>4095.997770347755</v>
       </c>
       <c r="L787">
-        <v>0.04907175627720625</v>
+        <v>0.04907175627720626</v>
       </c>
       <c r="M787">
         <v>0.05163969335604755</v>
@@ -68359,7 +68359,7 @@
         <v>1302.2</v>
       </c>
       <c r="V787">
-        <v>402.7037073395165</v>
+        <v>399.2797508396952</v>
       </c>
       <c r="W787">
         <v>4842.667163543427</v>
@@ -68368,16 +68368,16 @@
         <v>4842.667163543427</v>
       </c>
       <c r="Y787">
-        <v>-711.5448516692304</v>
+        <v>-746.669393195672</v>
       </c>
       <c r="Z787">
-        <v>-711.5448516692304</v>
+        <v>-746.669393195672</v>
       </c>
       <c r="AA787">
-        <v>-0.1469324295144385</v>
+        <v>-0.1541855692286163</v>
       </c>
       <c r="AB787">
-        <v>-0.1469324295144385</v>
+        <v>-0.1541855692286163</v>
       </c>
     </row>
     <row r="788" spans="1:28">
@@ -68406,16 +68406,16 @@
         <v>86</v>
       </c>
       <c r="I788">
-        <v>251.2883238193671</v>
+        <v>249.1517646718121</v>
       </c>
       <c r="J788">
-        <v>251.2883238193671</v>
+        <v>249.1517646718121</v>
       </c>
       <c r="K788">
-        <v>251.2883238193671</v>
+        <v>249.1517646718121</v>
       </c>
       <c r="L788">
-        <v>0.002984941730320568</v>
+        <v>0.002984941730320567</v>
       </c>
       <c r="M788">
         <v>0.002981260647359406</v>
@@ -68445,7 +68445,7 @@
         <v>248.8</v>
       </c>
       <c r="V788">
-        <v>21.36728839933254</v>
+        <v>21.18561471551723</v>
       </c>
       <c r="W788">
         <v>279.5766609880703</v>
@@ -68454,16 +68454,16 @@
         <v>279.5766609880703</v>
       </c>
       <c r="Y788">
-        <v>-28.28833716870321</v>
+        <v>-30.42489631625821</v>
       </c>
       <c r="Z788">
-        <v>-28.28833716870321</v>
+        <v>-30.42489631625821</v>
       </c>
       <c r="AA788">
-        <v>-0.1011827563457104</v>
+        <v>-0.1088248790465255</v>
       </c>
       <c r="AB788">
-        <v>-0.1011827563457104</v>
+        <v>-0.1088248790465255</v>
       </c>
     </row>
     <row r="789" spans="1:28">
@@ -68492,13 +68492,13 @@
         <v>87</v>
       </c>
       <c r="I789">
-        <v>2236.530467375763</v>
+        <v>2217.514543530881</v>
       </c>
       <c r="J789">
-        <v>2236.530467375763</v>
+        <v>2217.514543530881</v>
       </c>
       <c r="K789">
-        <v>2236.530467375763</v>
+        <v>2217.514543530881</v>
       </c>
       <c r="L789">
         <v>0.02656674620505689</v>
@@ -68522,7 +68522,7 @@
         <v>105</v>
       </c>
       <c r="S789">
-        <v>60242.97525198595</v>
+        <v>60242.97525198594</v>
       </c>
       <c r="T789">
         <v>1970</v>
@@ -68531,7 +68531,7 @@
         <v>260.2</v>
       </c>
       <c r="V789">
-        <v>186.7742949316191</v>
+        <v>185.186261224764</v>
       </c>
       <c r="W789">
         <v>2486.235306643949</v>
@@ -68540,16 +68540,16 @@
         <v>2486.235306643949</v>
       </c>
       <c r="Y789">
-        <v>-249.7048392681859</v>
+        <v>-268.7207631130677</v>
       </c>
       <c r="Z789">
-        <v>-249.7048392681859</v>
+        <v>-268.7207631130677</v>
       </c>
       <c r="AA789">
-        <v>-0.1004349180469368</v>
+        <v>-0.1080833991838854</v>
       </c>
       <c r="AB789">
-        <v>-0.1004349180469368</v>
+        <v>-0.1080833991838854</v>
       </c>
     </row>
     <row r="790" spans="1:28">
@@ -68578,13 +68578,13 @@
         <v>89</v>
       </c>
       <c r="I790">
-        <v>30209.48561089725</v>
+        <v>29952.63184290725</v>
       </c>
       <c r="J790">
-        <v>30209.48561089725</v>
+        <v>29952.63184290725</v>
       </c>
       <c r="K790">
-        <v>30209.48561089725</v>
+        <v>29952.63184290725</v>
       </c>
       <c r="L790">
         <v>0.358844982850477</v>
@@ -68617,7 +68617,7 @@
         <v>1459.6</v>
       </c>
       <c r="V790">
-        <v>3232.480463752646</v>
+        <v>3204.996553640341</v>
       </c>
       <c r="W790">
         <v>33569.16908006819</v>
@@ -68626,16 +68626,16 @@
         <v>33569.16908006819</v>
       </c>
       <c r="Y790">
-        <v>-3359.683469170945</v>
+        <v>-3616.537237160937</v>
       </c>
       <c r="Z790">
-        <v>-3359.683469170945</v>
+        <v>-3616.537237160937</v>
       </c>
       <c r="AA790">
-        <v>-0.1000824137516638</v>
+        <v>-0.1077338920285718</v>
       </c>
       <c r="AB790">
-        <v>-0.1000824137516638</v>
+        <v>-0.1077338920285718</v>
       </c>
     </row>
     <row r="791" spans="1:28">
